--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport Groups" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Secondary'!$A$1:$K$251</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -48,9 +46,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -108,34 +104,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -508,13 +499,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G140"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="51.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="51.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="20.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4455,83 +4446,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K251"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K253"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="37.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="63.42578125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="12.5703125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="37.140625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="37.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13.88671875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="63.44140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="37.109375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="11" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Mode.Operation</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Fuel.I</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Fuel.I.Name</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Value.Fuel.I</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Unit.Fuel.I</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Tech.Name</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Fuel.O</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Fuel.O.Name</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Value.Fuel.O</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Unit.Fuel.O</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
+    <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -4548,6 +4539,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PWRBIOBGDXX</t>
@@ -4571,8 +4563,9 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" hidden="1">
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
       <c r="A3" t="n">
         <v>1</v>
       </c>
@@ -4589,6 +4582,7 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>PWRBIOINDEA</t>
@@ -4612,8 +4606,9 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" hidden="1">
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
       <c r="A4" t="n">
         <v>1</v>
       </c>
@@ -4630,6 +4625,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>PWRBIOINDNE</t>
@@ -4653,8 +4649,9 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" hidden="1">
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
       <c r="A5" t="n">
         <v>1</v>
       </c>
@@ -4671,6 +4668,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRBIOINDNO</t>
@@ -4694,8 +4692,9 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" hidden="1">
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
       <c r="A6" t="n">
         <v>1</v>
       </c>
@@ -4712,6 +4711,7 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>PWRBIOINDSO</t>
@@ -4735,8 +4735,9 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" hidden="1">
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
       <c r="A7" t="n">
         <v>1</v>
       </c>
@@ -4753,6 +4754,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>PWRBIOINDWE</t>
@@ -4776,8 +4778,9 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" hidden="1">
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="A8" t="n">
         <v>1</v>
       </c>
@@ -4794,6 +4797,7 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>PWRBIOLKAXX</t>
@@ -4817,8 +4821,9 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" hidden="1">
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="A9" t="n">
         <v>1</v>
       </c>
@@ -4835,6 +4840,7 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PWRBIONPLXX</t>
@@ -4858,8 +4864,9 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" hidden="1">
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
       <c r="A10" t="n">
         <v>1</v>
       </c>
@@ -4876,6 +4883,7 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4899,8 +4907,9 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" hidden="1">
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
       <c r="A11" t="n">
         <v>2</v>
       </c>
@@ -4917,6 +4926,7 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4940,8 +4950,9 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" hidden="1">
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
       <c r="A12" t="n">
         <v>1</v>
       </c>
@@ -4958,6 +4969,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -4981,8 +4993,9 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" hidden="1">
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
       <c r="A13" t="n">
         <v>2</v>
       </c>
@@ -4999,6 +5012,7 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -5022,8 +5036,9 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" hidden="1">
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
       <c r="A14" t="n">
         <v>1</v>
       </c>
@@ -5040,6 +5055,7 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5063,8 +5079,9 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" hidden="1">
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
       <c r="A15" t="n">
         <v>2</v>
       </c>
@@ -5081,6 +5098,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5104,8 +5122,9 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" hidden="1">
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
       <c r="A16" t="n">
         <v>1</v>
       </c>
@@ -5122,6 +5141,7 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5145,8 +5165,9 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" hidden="1">
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
       <c r="A17" t="n">
         <v>2</v>
       </c>
@@ -5163,6 +5184,7 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5186,8 +5208,9 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" hidden="1">
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
       <c r="A18" t="n">
         <v>1</v>
       </c>
@@ -5204,6 +5227,7 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5227,8 +5251,9 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" hidden="1">
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
       <c r="A19" t="n">
         <v>2</v>
       </c>
@@ -5245,6 +5270,7 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5268,8 +5294,9 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" hidden="1">
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
       <c r="A20" t="n">
         <v>1</v>
       </c>
@@ -5286,6 +5313,7 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5309,8 +5337,9 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" hidden="1">
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="A21" t="n">
         <v>2</v>
       </c>
@@ -5327,6 +5356,7 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5350,8 +5380,9 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" hidden="1">
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
       <c r="A22" t="n">
         <v>1</v>
       </c>
@@ -5368,6 +5399,7 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5391,8 +5423,9 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" hidden="1">
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
       <c r="A23" t="n">
         <v>2</v>
       </c>
@@ -5409,6 +5442,7 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5432,8 +5466,9 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" hidden="1">
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
       <c r="A24" t="n">
         <v>1</v>
       </c>
@@ -5450,6 +5485,7 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5473,8 +5509,9 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" hidden="1">
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
       <c r="A25" t="n">
         <v>2</v>
       </c>
@@ -5491,6 +5528,7 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5514,8 +5552,9 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" hidden="1">
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
       <c r="A26" t="n">
         <v>1</v>
       </c>
@@ -5532,6 +5571,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5555,8 +5595,9 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" hidden="1">
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
       <c r="A27" t="n">
         <v>2</v>
       </c>
@@ -5573,6 +5614,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5596,8 +5638,9 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" hidden="1">
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
       <c r="A28" t="n">
         <v>1</v>
       </c>
@@ -5614,6 +5657,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5637,8 +5681,9 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" hidden="1">
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
       <c r="A29" t="n">
         <v>2</v>
       </c>
@@ -5655,6 +5700,7 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5678,8 +5724,9 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" hidden="1">
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
       <c r="A30" t="n">
         <v>1</v>
       </c>
@@ -5696,6 +5743,7 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5719,8 +5767,9 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" hidden="1">
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
       <c r="A31" t="n">
         <v>2</v>
       </c>
@@ -5737,6 +5786,7 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5760,8 +5810,9 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" hidden="1">
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
       <c r="A32" t="n">
         <v>1</v>
       </c>
@@ -5778,6 +5829,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5801,8 +5853,9 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" hidden="1">
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
       <c r="A33" t="n">
         <v>2</v>
       </c>
@@ -5819,6 +5872,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5842,8 +5896,9 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" hidden="1">
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
       <c r="A34" t="n">
         <v>1</v>
       </c>
@@ -5860,6 +5915,7 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5883,8 +5939,9 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" hidden="1">
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
       <c r="A35" t="n">
         <v>2</v>
       </c>
@@ -5901,6 +5958,7 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5924,8 +5982,9 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" hidden="1">
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
       <c r="A36" t="n">
         <v>1</v>
       </c>
@@ -5942,6 +6001,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -5965,8 +6025,9 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" hidden="1">
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
       <c r="A37" t="n">
         <v>2</v>
       </c>
@@ -5983,6 +6044,7 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -6006,8 +6068,9 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" hidden="1">
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
       <c r="A38" t="n">
         <v>1</v>
       </c>
@@ -6024,6 +6087,7 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6047,8 +6111,9 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" hidden="1">
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
       <c r="A39" t="n">
         <v>2</v>
       </c>
@@ -6065,6 +6130,7 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6088,8 +6154,9 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" hidden="1">
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
       <c r="A40" t="n">
         <v>1</v>
       </c>
@@ -6106,6 +6173,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6129,8 +6197,9 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" hidden="1">
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
       <c r="A41" t="n">
         <v>2</v>
       </c>
@@ -6147,6 +6216,7 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6170,8 +6240,9 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" hidden="1">
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
       <c r="A42" t="n">
         <v>1</v>
       </c>
@@ -6188,6 +6259,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6211,8 +6283,9 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" hidden="1">
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
       <c r="A43" t="n">
         <v>2</v>
       </c>
@@ -6229,6 +6302,7 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6252,8 +6326,9 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" hidden="1">
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
       <c r="A44" t="n">
         <v>1</v>
       </c>
@@ -6270,6 +6345,7 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6293,8 +6369,9 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" hidden="1">
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
       <c r="A45" t="n">
         <v>2</v>
       </c>
@@ -6311,6 +6388,7 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6334,8 +6412,9 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" hidden="1">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
       <c r="A46" t="n">
         <v>1</v>
       </c>
@@ -6352,6 +6431,7 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6375,8 +6455,9 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" hidden="1">
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
       <c r="A47" t="n">
         <v>2</v>
       </c>
@@ -6393,6 +6474,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6416,8 +6498,9 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" hidden="1">
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
       <c r="A48" t="n">
         <v>1</v>
       </c>
@@ -6434,6 +6517,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6457,8 +6541,9 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" hidden="1">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
       <c r="A49" t="n">
         <v>2</v>
       </c>
@@ -6475,6 +6560,7 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6498,8 +6584,9 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" hidden="1">
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
       <c r="A50" t="n">
         <v>1</v>
       </c>
@@ -6516,6 +6603,7 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>PWRCSPINDEA</t>
@@ -6539,8 +6627,9 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" hidden="1">
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
       <c r="A51" t="n">
         <v>1</v>
       </c>
@@ -6557,6 +6646,7 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>PWRCSPINDNE</t>
@@ -6580,8 +6670,9 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" hidden="1">
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
       <c r="A52" t="n">
         <v>1</v>
       </c>
@@ -6598,6 +6689,7 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>PWRCSPINDNO</t>
@@ -6621,8 +6713,9 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" hidden="1">
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
       <c r="A53" t="n">
         <v>1</v>
       </c>
@@ -6639,6 +6732,7 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRCSPINDSO</t>
@@ -6662,8 +6756,9 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" hidden="1">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
       <c r="A54" t="n">
         <v>1</v>
       </c>
@@ -6680,6 +6775,7 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>PWRCSPINDWE</t>
@@ -6703,8 +6799,9 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" hidden="1">
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
       <c r="A55" t="n">
         <v>1</v>
       </c>
@@ -6721,6 +6818,7 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>PWRHYDBGDXX</t>
@@ -6744,8 +6842,9 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" hidden="1">
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
       <c r="A56" t="n">
         <v>1</v>
       </c>
@@ -6762,6 +6861,7 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>PWRHYDBTNXX</t>
@@ -6785,8 +6885,9 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" hidden="1">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
       <c r="A57" t="n">
         <v>1</v>
       </c>
@@ -6803,6 +6904,7 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>PWRHYDINDEA</t>
@@ -6826,8 +6928,9 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" hidden="1">
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
       <c r="A58" t="n">
         <v>1</v>
       </c>
@@ -6844,6 +6947,7 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>PWRHYDINDNE</t>
@@ -6867,8 +6971,9 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" hidden="1">
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
       <c r="A59" t="n">
         <v>1</v>
       </c>
@@ -6885,6 +6990,7 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>PWRHYDINDNO</t>
@@ -6908,8 +7014,9 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" hidden="1">
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
       <c r="A60" t="n">
         <v>1</v>
       </c>
@@ -6926,6 +7033,7 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>PWRHYDINDSO</t>
@@ -6949,8 +7057,9 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" hidden="1">
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
       <c r="A61" t="n">
         <v>1</v>
       </c>
@@ -6967,6 +7076,7 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRHYDINDWE</t>
@@ -6990,8 +7100,9 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" hidden="1">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
       <c r="A62" t="n">
         <v>1</v>
       </c>
@@ -7008,6 +7119,7 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>PWRHYDLKAXX</t>
@@ -7031,8 +7143,9 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" hidden="1">
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
       <c r="A63" t="n">
         <v>1</v>
       </c>
@@ -7049,6 +7162,7 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>PWRHYDNPLXX</t>
@@ -7072,8 +7186,9 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" hidden="1">
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
       <c r="A64" t="n">
         <v>1</v>
       </c>
@@ -7090,6 +7205,7 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7113,8 +7229,9 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" hidden="1">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
       <c r="A65" t="n">
         <v>2</v>
       </c>
@@ -7131,6 +7248,7 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7154,8 +7272,9 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" hidden="1">
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
       <c r="A66" t="n">
         <v>1</v>
       </c>
@@ -7172,6 +7291,7 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7195,8 +7315,9 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" hidden="1">
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
       <c r="A67" t="n">
         <v>2</v>
       </c>
@@ -7213,6 +7334,7 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7236,8 +7358,9 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" hidden="1">
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
       <c r="A68" t="n">
         <v>1</v>
       </c>
@@ -7254,6 +7377,7 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7277,8 +7401,9 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" hidden="1">
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
       <c r="A69" t="n">
         <v>2</v>
       </c>
@@ -7295,6 +7420,7 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7318,8 +7444,9 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" hidden="1">
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
       <c r="A70" t="n">
         <v>1</v>
       </c>
@@ -7336,6 +7463,7 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7359,8 +7487,9 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" hidden="1">
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
       <c r="A71" t="n">
         <v>2</v>
       </c>
@@ -7377,6 +7506,7 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7400,8 +7530,9 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" hidden="1">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
       <c r="A72" t="n">
         <v>1</v>
       </c>
@@ -7418,6 +7549,7 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7441,8 +7573,9 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" hidden="1">
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
       <c r="A73" t="n">
         <v>2</v>
       </c>
@@ -7459,6 +7592,7 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7482,8 +7616,9 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" hidden="1">
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
       <c r="A74" t="n">
         <v>1</v>
       </c>
@@ -7500,6 +7635,7 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7523,8 +7659,9 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" hidden="1">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
       <c r="A75" t="n">
         <v>2</v>
       </c>
@@ -7541,6 +7678,7 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7564,8 +7702,9 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" hidden="1">
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
       <c r="A76" t="n">
         <v>1</v>
       </c>
@@ -7582,6 +7721,7 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7605,8 +7745,9 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" hidden="1">
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
       <c r="A77" t="n">
         <v>2</v>
       </c>
@@ -7623,6 +7764,7 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7646,8 +7788,9 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" hidden="1">
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
       <c r="A78" t="n">
         <v>1</v>
       </c>
@@ -7664,6 +7807,7 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7687,8 +7831,9 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" hidden="1">
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
       <c r="A79" t="n">
         <v>2</v>
       </c>
@@ -7705,6 +7850,7 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7728,8 +7874,9 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" hidden="1">
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
       <c r="A80" t="n">
         <v>1</v>
       </c>
@@ -7746,6 +7893,7 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7769,8 +7917,9 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" hidden="1">
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
       <c r="A81" t="n">
         <v>2</v>
       </c>
@@ -7787,6 +7936,7 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7810,8 +7960,9 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" hidden="1">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
       <c r="A82" t="n">
         <v>1</v>
       </c>
@@ -7828,6 +7979,7 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -7851,8 +8003,9 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" hidden="1">
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
       <c r="A83" t="n">
         <v>2</v>
       </c>
@@ -7869,6 +8022,7 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -7892,8 +8046,9 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" hidden="1">
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
       <c r="A84" t="n">
         <v>1</v>
       </c>
@@ -7910,6 +8065,7 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -7933,8 +8089,9 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" hidden="1">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
       <c r="A85" t="n">
         <v>2</v>
       </c>
@@ -7951,6 +8108,7 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -7974,8 +8132,9 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" hidden="1">
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
       <c r="A86" t="n">
         <v>1</v>
       </c>
@@ -7992,6 +8151,7 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8015,8 +8175,9 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" hidden="1">
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
       <c r="A87" t="n">
         <v>2</v>
       </c>
@@ -8033,6 +8194,7 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8056,8 +8218,9 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" hidden="1">
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
       <c r="A88" t="n">
         <v>1</v>
       </c>
@@ -8074,6 +8237,7 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8097,8 +8261,9 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" hidden="1">
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
       <c r="A89" t="n">
         <v>2</v>
       </c>
@@ -8115,6 +8280,7 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8138,8 +8304,9 @@
       <c r="J89" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" hidden="1">
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
       <c r="A90" t="n">
         <v>1</v>
       </c>
@@ -8156,6 +8323,7 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8179,8 +8347,9 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" hidden="1">
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
       <c r="A91" t="n">
         <v>2</v>
       </c>
@@ -8197,6 +8366,7 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8220,8 +8390,9 @@
       <c r="J91" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" hidden="1">
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
       <c r="A92" t="n">
         <v>1</v>
       </c>
@@ -8238,6 +8409,7 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8261,8 +8433,9 @@
       <c r="J92" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" hidden="1">
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
       <c r="A93" t="n">
         <v>2</v>
       </c>
@@ -8279,6 +8452,7 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8302,8 +8476,9 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" hidden="1">
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
       <c r="A94" t="n">
         <v>1</v>
       </c>
@@ -8320,6 +8495,7 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8343,8 +8519,9 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" hidden="1">
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
       <c r="A95" t="n">
         <v>2</v>
       </c>
@@ -8361,6 +8538,7 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8384,8 +8562,9 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" hidden="1">
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
       <c r="A96" t="n">
         <v>1</v>
       </c>
@@ -8402,6 +8581,7 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8425,8 +8605,9 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" hidden="1">
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
       <c r="A97" t="n">
         <v>2</v>
       </c>
@@ -8443,6 +8624,7 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8466,8 +8648,9 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" hidden="1">
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
       <c r="A98" t="n">
         <v>1</v>
       </c>
@@ -8484,6 +8667,7 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8507,8 +8691,9 @@
       <c r="J98" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" hidden="1">
+      <c r="K98" t="inlineStr"/>
+    </row>
+    <row r="99">
       <c r="A99" t="n">
         <v>2</v>
       </c>
@@ -8525,6 +8710,7 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8548,8 +8734,9 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" hidden="1">
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
       <c r="A100" t="n">
         <v>1</v>
       </c>
@@ -8566,6 +8753,7 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8589,8 +8777,9 @@
       <c r="J100" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" hidden="1">
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
       <c r="A101" t="n">
         <v>2</v>
       </c>
@@ -8607,6 +8796,7 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8630,8 +8820,9 @@
       <c r="J101" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" hidden="1">
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
       <c r="A102" t="n">
         <v>1</v>
       </c>
@@ -8648,6 +8839,7 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8671,8 +8863,9 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" hidden="1">
+      <c r="K102" t="inlineStr"/>
+    </row>
+    <row r="103">
       <c r="A103" t="n">
         <v>2</v>
       </c>
@@ -8689,6 +8882,7 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8712,8 +8906,9 @@
       <c r="J103" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" hidden="1">
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
       <c r="A104" t="n">
         <v>1</v>
       </c>
@@ -8730,6 +8925,7 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8753,8 +8949,9 @@
       <c r="J104" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" hidden="1">
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
       <c r="A105" t="n">
         <v>2</v>
       </c>
@@ -8771,6 +8968,7 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8794,8 +8992,9 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" hidden="1">
+      <c r="K105" t="inlineStr"/>
+    </row>
+    <row r="106">
       <c r="A106" t="n">
         <v>1</v>
       </c>
@@ -8812,6 +9011,7 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -8835,8 +9035,9 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" hidden="1">
+      <c r="K106" t="inlineStr"/>
+    </row>
+    <row r="107">
       <c r="A107" t="n">
         <v>2</v>
       </c>
@@ -8853,6 +9054,7 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -8876,8 +9078,9 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" hidden="1">
+      <c r="K107" t="inlineStr"/>
+    </row>
+    <row r="108">
       <c r="A108" t="n">
         <v>1</v>
       </c>
@@ -8894,6 +9097,7 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -8917,8 +9121,9 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" hidden="1">
+      <c r="K108" t="inlineStr"/>
+    </row>
+    <row r="109">
       <c r="A109" t="n">
         <v>2</v>
       </c>
@@ -8935,6 +9140,7 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -8958,8 +9164,9 @@
       <c r="J109" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" hidden="1">
+      <c r="K109" t="inlineStr"/>
+    </row>
+    <row r="110">
       <c r="A110" t="n">
         <v>1</v>
       </c>
@@ -8976,6 +9183,7 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -8999,8 +9207,9 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" hidden="1">
+      <c r="K110" t="inlineStr"/>
+    </row>
+    <row r="111">
       <c r="A111" t="n">
         <v>2</v>
       </c>
@@ -9017,6 +9226,7 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -9040,8 +9250,9 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" hidden="1">
+      <c r="K111" t="inlineStr"/>
+    </row>
+    <row r="112">
       <c r="A112" t="n">
         <v>1</v>
       </c>
@@ -9058,6 +9269,7 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9081,8 +9293,9 @@
       <c r="J112" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" hidden="1">
+      <c r="K112" t="inlineStr"/>
+    </row>
+    <row r="113">
       <c r="A113" t="n">
         <v>2</v>
       </c>
@@ -9099,6 +9312,7 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9122,8 +9336,9 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" hidden="1">
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
       <c r="A114" t="n">
         <v>1</v>
       </c>
@@ -9140,6 +9355,7 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9163,8 +9379,9 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" hidden="1">
+      <c r="K114" t="inlineStr"/>
+    </row>
+    <row r="115">
       <c r="A115" t="n">
         <v>2</v>
       </c>
@@ -9181,6 +9398,7 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9204,8 +9422,9 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" hidden="1">
+      <c r="K115" t="inlineStr"/>
+    </row>
+    <row r="116">
       <c r="A116" t="n">
         <v>1</v>
       </c>
@@ -9222,6 +9441,7 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9245,8 +9465,9 @@
       <c r="J116" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" hidden="1">
+      <c r="K116" t="inlineStr"/>
+    </row>
+    <row r="117">
       <c r="A117" t="n">
         <v>2</v>
       </c>
@@ -9263,6 +9484,7 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9286,8 +9508,9 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" hidden="1">
+      <c r="K117" t="inlineStr"/>
+    </row>
+    <row r="118">
       <c r="A118" t="n">
         <v>1</v>
       </c>
@@ -9304,6 +9527,7 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9327,8 +9551,9 @@
       <c r="J118" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" hidden="1">
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
       <c r="A119" t="n">
         <v>2</v>
       </c>
@@ -9345,6 +9570,7 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9368,8 +9594,9 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" hidden="1">
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
       <c r="A120" t="n">
         <v>1</v>
       </c>
@@ -9386,6 +9613,7 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9409,8 +9637,9 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" hidden="1">
+      <c r="K120" t="inlineStr"/>
+    </row>
+    <row r="121">
       <c r="A121" t="n">
         <v>2</v>
       </c>
@@ -9427,6 +9656,7 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9450,8 +9680,9 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" hidden="1">
+      <c r="K121" t="inlineStr"/>
+    </row>
+    <row r="122">
       <c r="A122" t="n">
         <v>1</v>
       </c>
@@ -9468,6 +9699,7 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9491,8 +9723,9 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" hidden="1">
+      <c r="K122" t="inlineStr"/>
+    </row>
+    <row r="123">
       <c r="A123" t="n">
         <v>2</v>
       </c>
@@ -9509,6 +9742,7 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9532,8 +9766,9 @@
       <c r="J123" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" hidden="1">
+      <c r="K123" t="inlineStr"/>
+    </row>
+    <row r="124">
       <c r="A124" t="n">
         <v>1</v>
       </c>
@@ -9550,6 +9785,7 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9573,8 +9809,9 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" hidden="1">
+      <c r="K124" t="inlineStr"/>
+    </row>
+    <row r="125">
       <c r="A125" t="n">
         <v>2</v>
       </c>
@@ -9591,6 +9828,7 @@
       <c r="D125" t="n">
         <v>1</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9614,8 +9852,9 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" hidden="1">
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
       <c r="A126" t="n">
         <v>1</v>
       </c>
@@ -9632,6 +9871,7 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9655,8 +9895,9 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" hidden="1">
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
       <c r="A127" t="n">
         <v>2</v>
       </c>
@@ -9673,6 +9914,7 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9696,8 +9938,9 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" hidden="1">
+      <c r="K127" t="inlineStr"/>
+    </row>
+    <row r="128">
       <c r="A128" t="n">
         <v>1</v>
       </c>
@@ -9714,6 +9957,7 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -9737,8 +9981,9 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" hidden="1">
+      <c r="K128" t="inlineStr"/>
+    </row>
+    <row r="129">
       <c r="A129" t="n">
         <v>2</v>
       </c>
@@ -9755,6 +10000,7 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -9778,8 +10024,9 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" hidden="1">
+      <c r="K129" t="inlineStr"/>
+    </row>
+    <row r="130">
       <c r="A130" t="n">
         <v>1</v>
       </c>
@@ -9796,6 +10043,7 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>PWRSPVBGDXX</t>
@@ -9819,8 +10067,9 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" hidden="1">
+      <c r="K130" t="inlineStr"/>
+    </row>
+    <row r="131">
       <c r="A131" t="n">
         <v>1</v>
       </c>
@@ -9837,6 +10086,7 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>PWRSPVBTNXX</t>
@@ -9860,8 +10110,9 @@
       <c r="J131" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" hidden="1">
+      <c r="K131" t="inlineStr"/>
+    </row>
+    <row r="132">
       <c r="A132" t="n">
         <v>1</v>
       </c>
@@ -9878,6 +10129,7 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>PWRSPVINDEA</t>
@@ -9901,8 +10153,9 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" hidden="1">
+      <c r="K132" t="inlineStr"/>
+    </row>
+    <row r="133">
       <c r="A133" t="n">
         <v>1</v>
       </c>
@@ -9919,6 +10172,7 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>PWRSPVINDNE</t>
@@ -9942,8 +10196,9 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" hidden="1">
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
       <c r="A134" t="n">
         <v>1</v>
       </c>
@@ -9960,6 +10215,7 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>PWRSPVINDNO</t>
@@ -9983,8 +10239,9 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" hidden="1">
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
       <c r="A135" t="n">
         <v>1</v>
       </c>
@@ -10001,6 +10258,7 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>PWRSPVINDSO</t>
@@ -10024,8 +10282,9 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" hidden="1">
+      <c r="K135" t="inlineStr"/>
+    </row>
+    <row r="136">
       <c r="A136" t="n">
         <v>1</v>
       </c>
@@ -10042,6 +10301,7 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>PWRSPVINDWE</t>
@@ -10065,8 +10325,9 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" hidden="1">
+      <c r="K136" t="inlineStr"/>
+    </row>
+    <row r="137">
       <c r="A137" t="n">
         <v>1</v>
       </c>
@@ -10083,6 +10344,7 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>PWRSPVLKAXX</t>
@@ -10106,8 +10368,9 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" hidden="1">
+      <c r="K137" t="inlineStr"/>
+    </row>
+    <row r="138">
       <c r="A138" t="n">
         <v>1</v>
       </c>
@@ -10124,6 +10387,7 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>PWRSPVMDVXX</t>
@@ -10147,8 +10411,9 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" hidden="1">
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
       <c r="A139" t="n">
         <v>1</v>
       </c>
@@ -10165,6 +10430,7 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>PWRSPVNPLXX</t>
@@ -10188,8 +10454,9 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" hidden="1">
+      <c r="K139" t="inlineStr"/>
+    </row>
+    <row r="140">
       <c r="A140" t="n">
         <v>1</v>
       </c>
@@ -10206,6 +10473,7 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10229,8 +10497,9 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" hidden="1">
+      <c r="K140" t="inlineStr"/>
+    </row>
+    <row r="141">
       <c r="A141" t="n">
         <v>2</v>
       </c>
@@ -10247,6 +10516,7 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10270,8 +10540,9 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" hidden="1">
+      <c r="K141" t="inlineStr"/>
+    </row>
+    <row r="142">
       <c r="A142" t="n">
         <v>1</v>
       </c>
@@ -10288,6 +10559,7 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10311,8 +10583,9 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" hidden="1">
+      <c r="K142" t="inlineStr"/>
+    </row>
+    <row r="143">
       <c r="A143" t="n">
         <v>2</v>
       </c>
@@ -10329,6 +10602,7 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10352,8 +10626,9 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" hidden="1">
+      <c r="K143" t="inlineStr"/>
+    </row>
+    <row r="144">
       <c r="A144" t="n">
         <v>1</v>
       </c>
@@ -10370,6 +10645,7 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10393,8 +10669,9 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" hidden="1">
+      <c r="K144" t="inlineStr"/>
+    </row>
+    <row r="145">
       <c r="A145" t="n">
         <v>2</v>
       </c>
@@ -10411,6 +10688,7 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10434,8 +10712,9 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" hidden="1">
+      <c r="K145" t="inlineStr"/>
+    </row>
+    <row r="146">
       <c r="A146" t="n">
         <v>1</v>
       </c>
@@ -10452,6 +10731,7 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10475,8 +10755,9 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" hidden="1">
+      <c r="K146" t="inlineStr"/>
+    </row>
+    <row r="147">
       <c r="A147" t="n">
         <v>2</v>
       </c>
@@ -10493,6 +10774,7 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10516,8 +10798,9 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" hidden="1">
+      <c r="K147" t="inlineStr"/>
+    </row>
+    <row r="148">
       <c r="A148" t="n">
         <v>1</v>
       </c>
@@ -10534,6 +10817,7 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10557,8 +10841,9 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" hidden="1">
+      <c r="K148" t="inlineStr"/>
+    </row>
+    <row r="149">
       <c r="A149" t="n">
         <v>2</v>
       </c>
@@ -10575,6 +10860,7 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10598,8 +10884,9 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" hidden="1">
+      <c r="K149" t="inlineStr"/>
+    </row>
+    <row r="150">
       <c r="A150" t="n">
         <v>1</v>
       </c>
@@ -10616,6 +10903,7 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10639,8 +10927,9 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" hidden="1">
+      <c r="K150" t="inlineStr"/>
+    </row>
+    <row r="151">
       <c r="A151" t="n">
         <v>2</v>
       </c>
@@ -10657,6 +10946,7 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10680,8 +10970,9 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" hidden="1">
+      <c r="K151" t="inlineStr"/>
+    </row>
+    <row r="152">
       <c r="A152" t="n">
         <v>1</v>
       </c>
@@ -10698,6 +10989,7 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>PWRWASBGDXX</t>
@@ -10721,8 +11013,9 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" hidden="1">
+      <c r="K152" t="inlineStr"/>
+    </row>
+    <row r="153">
       <c r="A153" t="n">
         <v>1</v>
       </c>
@@ -10739,6 +11032,7 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>PWRWASINDEA</t>
@@ -10762,8 +11056,9 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" hidden="1">
+      <c r="K153" t="inlineStr"/>
+    </row>
+    <row r="154">
       <c r="A154" t="n">
         <v>1</v>
       </c>
@@ -10780,6 +11075,7 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>PWRWASINDNE</t>
@@ -10803,8 +11099,9 @@
       <c r="J154" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" hidden="1">
+      <c r="K154" t="inlineStr"/>
+    </row>
+    <row r="155">
       <c r="A155" t="n">
         <v>1</v>
       </c>
@@ -10821,6 +11118,7 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>PWRWASINDNO</t>
@@ -10844,8 +11142,9 @@
       <c r="J155" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" hidden="1">
+      <c r="K155" t="inlineStr"/>
+    </row>
+    <row r="156">
       <c r="A156" t="n">
         <v>1</v>
       </c>
@@ -10862,6 +11161,7 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>PWRWASINDSO</t>
@@ -10885,8 +11185,9 @@
       <c r="J156" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" hidden="1">
+      <c r="K156" t="inlineStr"/>
+    </row>
+    <row r="157">
       <c r="A157" t="n">
         <v>1</v>
       </c>
@@ -10903,6 +11204,7 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>PWRWASINDWE</t>
@@ -10926,8 +11228,9 @@
       <c r="J157" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" hidden="1">
+      <c r="K157" t="inlineStr"/>
+    </row>
+    <row r="158">
       <c r="A158" t="n">
         <v>1</v>
       </c>
@@ -10944,6 +11247,7 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>PWRWASLKAXX</t>
@@ -10967,8 +11271,9 @@
       <c r="J158" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" hidden="1">
+      <c r="K158" t="inlineStr"/>
+    </row>
+    <row r="159">
       <c r="A159" t="n">
         <v>1</v>
       </c>
@@ -10985,6 +11290,7 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>PWRWASNPLXX</t>
@@ -11008,8 +11314,9 @@
       <c r="J159" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" hidden="1">
+      <c r="K159" t="inlineStr"/>
+    </row>
+    <row r="160">
       <c r="A160" t="n">
         <v>1</v>
       </c>
@@ -11026,6 +11333,7 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>PWRWOFBGDXX</t>
@@ -11049,8 +11357,9 @@
       <c r="J160" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" hidden="1">
+      <c r="K160" t="inlineStr"/>
+    </row>
+    <row r="161">
       <c r="A161" t="n">
         <v>1</v>
       </c>
@@ -11067,6 +11376,7 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>PWRWOFINDEA</t>
@@ -11090,8 +11400,9 @@
       <c r="J161" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" hidden="1">
+      <c r="K161" t="inlineStr"/>
+    </row>
+    <row r="162">
       <c r="A162" t="n">
         <v>1</v>
       </c>
@@ -11108,6 +11419,7 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>PWRWOFINDNE</t>
@@ -11131,8 +11443,9 @@
       <c r="J162" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" hidden="1">
+      <c r="K162" t="inlineStr"/>
+    </row>
+    <row r="163">
       <c r="A163" t="n">
         <v>1</v>
       </c>
@@ -11149,6 +11462,7 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>PWRWOFINDNO</t>
@@ -11172,8 +11486,9 @@
       <c r="J163" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" hidden="1">
+      <c r="K163" t="inlineStr"/>
+    </row>
+    <row r="164">
       <c r="A164" t="n">
         <v>1</v>
       </c>
@@ -11190,6 +11505,7 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>PWRWOFINDSO</t>
@@ -11213,8 +11529,9 @@
       <c r="J164" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" hidden="1">
+      <c r="K164" t="inlineStr"/>
+    </row>
+    <row r="165">
       <c r="A165" t="n">
         <v>1</v>
       </c>
@@ -11231,6 +11548,7 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>PWRWOFINDWE</t>
@@ -11254,8 +11572,9 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" hidden="1">
+      <c r="K165" t="inlineStr"/>
+    </row>
+    <row r="166">
       <c r="A166" t="n">
         <v>1</v>
       </c>
@@ -11272,6 +11591,7 @@
       <c r="D166" t="n">
         <v>1</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>PWRWOFLKAXX</t>
@@ -11295,8 +11615,9 @@
       <c r="J166" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" hidden="1">
+      <c r="K166" t="inlineStr"/>
+    </row>
+    <row r="167">
       <c r="A167" t="n">
         <v>1</v>
       </c>
@@ -11313,6 +11634,7 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>PWRWONBGDXX</t>
@@ -11336,8 +11658,9 @@
       <c r="J167" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" hidden="1">
+      <c r="K167" t="inlineStr"/>
+    </row>
+    <row r="168">
       <c r="A168" t="n">
         <v>1</v>
       </c>
@@ -11354,6 +11677,7 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>PWRWONBTNXX</t>
@@ -11377,8 +11701,9 @@
       <c r="J168" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" hidden="1">
+      <c r="K168" t="inlineStr"/>
+    </row>
+    <row r="169">
       <c r="A169" t="n">
         <v>1</v>
       </c>
@@ -11395,6 +11720,7 @@
       <c r="D169" t="n">
         <v>1</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>PWRWONINDEA</t>
@@ -11418,8 +11744,9 @@
       <c r="J169" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" hidden="1">
+      <c r="K169" t="inlineStr"/>
+    </row>
+    <row r="170">
       <c r="A170" t="n">
         <v>1</v>
       </c>
@@ -11436,6 +11763,7 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>PWRWONINDNE</t>
@@ -11459,8 +11787,9 @@
       <c r="J170" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" hidden="1">
+      <c r="K170" t="inlineStr"/>
+    </row>
+    <row r="171">
       <c r="A171" t="n">
         <v>1</v>
       </c>
@@ -11477,6 +11806,7 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>PWRWONINDNO</t>
@@ -11500,8 +11830,9 @@
       <c r="J171" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" hidden="1">
+      <c r="K171" t="inlineStr"/>
+    </row>
+    <row r="172">
       <c r="A172" t="n">
         <v>1</v>
       </c>
@@ -11518,6 +11849,7 @@
       <c r="D172" t="n">
         <v>1</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>PWRWONINDSO</t>
@@ -11541,8 +11873,9 @@
       <c r="J172" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" hidden="1">
+      <c r="K172" t="inlineStr"/>
+    </row>
+    <row r="173">
       <c r="A173" t="n">
         <v>1</v>
       </c>
@@ -11559,6 +11892,7 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>PWRWONINDWE</t>
@@ -11582,8 +11916,9 @@
       <c r="J173" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" hidden="1">
+      <c r="K173" t="inlineStr"/>
+    </row>
+    <row r="174">
       <c r="A174" t="n">
         <v>1</v>
       </c>
@@ -11600,6 +11935,7 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>PWRWONLKAXX</t>
@@ -11623,8 +11959,9 @@
       <c r="J174" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" hidden="1">
+      <c r="K174" t="inlineStr"/>
+    </row>
+    <row r="175">
       <c r="A175" t="n">
         <v>1</v>
       </c>
@@ -11641,6 +11978,7 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>PWRWONNPLXX</t>
@@ -11664,6 +12002,7 @@
       <c r="J175" t="n">
         <v>1</v>
       </c>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -11680,8 +12019,9 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -11703,8 +12043,9 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -11723,6 +12064,7 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -11746,8 +12088,9 @@
       <c r="J177" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" hidden="1">
+      <c r="K177" t="inlineStr"/>
+    </row>
+    <row r="178">
       <c r="A178" t="n">
         <v>1</v>
       </c>
@@ -11764,6 +12107,7 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -11787,8 +12131,9 @@
       <c r="J178" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" hidden="1">
+      <c r="K178" t="inlineStr"/>
+    </row>
+    <row r="179">
       <c r="A179" t="n">
         <v>2</v>
       </c>
@@ -11805,6 +12150,7 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -11828,8 +12174,9 @@
       <c r="J179" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" hidden="1">
+      <c r="K179" t="inlineStr"/>
+    </row>
+    <row r="180">
       <c r="A180" t="n">
         <v>1</v>
       </c>
@@ -11846,6 +12193,7 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -11869,8 +12217,9 @@
       <c r="J180" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" hidden="1">
+      <c r="K180" t="inlineStr"/>
+    </row>
+    <row r="181">
       <c r="A181" t="n">
         <v>2</v>
       </c>
@@ -11887,6 +12236,7 @@
       <c r="D181" t="n">
         <v>1</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -11910,8 +12260,9 @@
       <c r="J181" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" hidden="1">
+      <c r="K181" t="inlineStr"/>
+    </row>
+    <row r="182">
       <c r="A182" t="n">
         <v>1</v>
       </c>
@@ -11928,6 +12279,7 @@
       <c r="D182" t="n">
         <v>1</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -11951,8 +12303,9 @@
       <c r="J182" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" hidden="1">
+      <c r="K182" t="inlineStr"/>
+    </row>
+    <row r="183">
       <c r="A183" t="n">
         <v>2</v>
       </c>
@@ -11969,6 +12322,7 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -11992,8 +12346,9 @@
       <c r="J183" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" hidden="1">
+      <c r="K183" t="inlineStr"/>
+    </row>
+    <row r="184">
       <c r="A184" t="n">
         <v>1</v>
       </c>
@@ -12010,6 +12365,7 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12033,8 +12389,9 @@
       <c r="J184" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" hidden="1">
+      <c r="K184" t="inlineStr"/>
+    </row>
+    <row r="185">
       <c r="A185" t="n">
         <v>2</v>
       </c>
@@ -12051,6 +12408,7 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12074,8 +12432,9 @@
       <c r="J185" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" hidden="1">
+      <c r="K185" t="inlineStr"/>
+    </row>
+    <row r="186">
       <c r="A186" t="n">
         <v>1</v>
       </c>
@@ -12092,6 +12451,7 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12115,8 +12475,9 @@
       <c r="J186" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" hidden="1">
+      <c r="K186" t="inlineStr"/>
+    </row>
+    <row r="187">
       <c r="A187" t="n">
         <v>2</v>
       </c>
@@ -12133,6 +12494,7 @@
       <c r="D187" t="n">
         <v>1</v>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12156,8 +12518,9 @@
       <c r="J187" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" hidden="1">
+      <c r="K187" t="inlineStr"/>
+    </row>
+    <row r="188">
       <c r="A188" t="n">
         <v>1</v>
       </c>
@@ -12174,6 +12537,7 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12197,8 +12561,9 @@
       <c r="J188" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" hidden="1">
+      <c r="K188" t="inlineStr"/>
+    </row>
+    <row r="189">
       <c r="A189" t="n">
         <v>2</v>
       </c>
@@ -12215,6 +12580,7 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12238,8 +12604,9 @@
       <c r="J189" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" hidden="1">
+      <c r="K189" t="inlineStr"/>
+    </row>
+    <row r="190">
       <c r="A190" t="n">
         <v>1</v>
       </c>
@@ -12256,6 +12623,7 @@
       <c r="D190" t="n">
         <v>1</v>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12279,8 +12647,9 @@
       <c r="J190" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" hidden="1">
+      <c r="K190" t="inlineStr"/>
+    </row>
+    <row r="191">
       <c r="A191" t="n">
         <v>2</v>
       </c>
@@ -12297,6 +12666,7 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12320,8 +12690,9 @@
       <c r="J191" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" hidden="1">
+      <c r="K191" t="inlineStr"/>
+    </row>
+    <row r="192">
       <c r="A192" t="n">
         <v>1</v>
       </c>
@@ -12338,6 +12709,7 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12361,8 +12733,9 @@
       <c r="J192" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" hidden="1">
+      <c r="K192" t="inlineStr"/>
+    </row>
+    <row r="193">
       <c r="A193" t="n">
         <v>2</v>
       </c>
@@ -12379,6 +12752,7 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12402,8 +12776,9 @@
       <c r="J193" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" hidden="1">
+      <c r="K193" t="inlineStr"/>
+    </row>
+    <row r="194">
       <c r="A194" t="n">
         <v>1</v>
       </c>
@@ -12420,6 +12795,7 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12443,8 +12819,9 @@
       <c r="J194" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" hidden="1">
+      <c r="K194" t="inlineStr"/>
+    </row>
+    <row r="195">
       <c r="A195" t="n">
         <v>2</v>
       </c>
@@ -12461,6 +12838,7 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12484,8 +12862,9 @@
       <c r="J195" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" hidden="1">
+      <c r="K195" t="inlineStr"/>
+    </row>
+    <row r="196">
       <c r="A196" t="n">
         <v>1</v>
       </c>
@@ -12502,6 +12881,7 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12525,8 +12905,9 @@
       <c r="J196" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" hidden="1">
+      <c r="K196" t="inlineStr"/>
+    </row>
+    <row r="197">
       <c r="A197" t="n">
         <v>2</v>
       </c>
@@ -12543,6 +12924,7 @@
       <c r="D197" t="n">
         <v>1</v>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12566,8 +12948,9 @@
       <c r="J197" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" hidden="1">
+      <c r="K197" t="inlineStr"/>
+    </row>
+    <row r="198">
       <c r="A198" t="n">
         <v>1</v>
       </c>
@@ -12584,6 +12967,7 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -12607,8 +12991,9 @@
       <c r="J198" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" hidden="1">
+      <c r="K198" t="inlineStr"/>
+    </row>
+    <row r="199">
       <c r="A199" t="n">
         <v>2</v>
       </c>
@@ -12625,6 +13010,7 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -12648,8 +13034,9 @@
       <c r="J199" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" hidden="1">
+      <c r="K199" t="inlineStr"/>
+    </row>
+    <row r="200">
       <c r="A200" t="n">
         <v>1</v>
       </c>
@@ -12666,6 +13053,7 @@
       <c r="D200" t="n">
         <v>1</v>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -12689,8 +13077,9 @@
       <c r="J200" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" hidden="1">
+      <c r="K200" t="inlineStr"/>
+    </row>
+    <row r="201">
       <c r="A201" t="n">
         <v>2</v>
       </c>
@@ -12707,6 +13096,7 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -12730,1415 +13120,1745 @@
       <c r="J201" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" hidden="1">
+      <c r="K201" t="inlineStr"/>
+    </row>
+    <row r="202">
       <c r="A202" t="n">
         <v>1</v>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ELCLKAXX02</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, region XX, transmission line output</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
+          <t>TRNLKAXXMDVXX</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Sri Lanka, region XX to Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>ELCMDVXX01</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ELCMDVXX02</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, transmission line output</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>TRNLKAXXMDVXX</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Sri Lanka, region XX to Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>ELCLKAXX01</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
           <t>PWRBCKBGDXX</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>Backstop (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H204" t="inlineStr">
         <is>
           <t>ELCBGDXX01</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I204" t="inlineStr">
         <is>
           <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J202" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" hidden="1">
-      <c r="A203" t="n">
-        <v>1</v>
-      </c>
-      <c r="F203" t="inlineStr">
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
         <is>
           <t>PWRBCKBTNXX</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>Backstop (Power generator) Bhutan, region XX</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>ELCBTNXX01</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I205" t="inlineStr">
         <is>
           <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J203" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" hidden="1">
-      <c r="A204" t="n">
-        <v>1</v>
-      </c>
-      <c r="F204" t="inlineStr">
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
         <is>
           <t>PWRBCKINDEA</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>Backstop (Power generator) India, region EA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>ELCINDEA01</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I206" t="inlineStr">
         <is>
           <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J204" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" hidden="1">
-      <c r="A205" t="n">
-        <v>1</v>
-      </c>
-      <c r="F205" t="inlineStr">
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
         <is>
           <t>PWRBCKINDNE</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>Backstop (Power generator) India, region NE</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H207" t="inlineStr">
         <is>
           <t>ELCINDNE01</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I207" t="inlineStr">
         <is>
           <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J205" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" hidden="1">
-      <c r="A206" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" t="inlineStr">
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
         <is>
           <t>PWRBCKINDNO</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>Backstop (Power generator) India, region NO</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>ELCINDNO01</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I208" t="inlineStr">
         <is>
           <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J206" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" hidden="1">
-      <c r="A207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" t="inlineStr">
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1</v>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
         <is>
           <t>PWRBCKINDSO</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>Backstop (Power generator) India, region SO</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>ELCINDSO01</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I209" t="inlineStr">
         <is>
           <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J207" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" hidden="1">
-      <c r="A208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="inlineStr">
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
         <is>
           <t>PWRBCKINDWE</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>Backstop (Power generator) India, region WE</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>ELCINDWE01</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J208" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" hidden="1">
-      <c r="A209" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" t="inlineStr">
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
         <is>
           <t>PWRBCKLKAXX</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>Backstop (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>ELCLKAXX01</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I211" t="inlineStr">
         <is>
           <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J209" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" hidden="1">
-      <c r="A210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="inlineStr">
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1</v>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
         <is>
           <t>PWRBCKMDVXX</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>Backstop (Power generator) Maldives, region XX</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H212" t="inlineStr">
         <is>
           <t>ELCMDVXX01</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I212" t="inlineStr">
         <is>
           <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J210" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" hidden="1">
-      <c r="A211" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" t="inlineStr">
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
         <is>
           <t>PWRBCKNPLXX</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>Backstop (Power generator) Nepal, region XX</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H213" t="inlineStr">
         <is>
           <t>ELCNPLXX01</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I213" t="inlineStr">
         <is>
           <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
-      <c r="J211" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" hidden="1">
-      <c r="A212" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>PWRLDSBGDXX</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>ELCBGDXX00</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J212" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" hidden="1">
-      <c r="A213" t="n">
-        <v>2</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>PWRLDSBTNXX</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Long duration storage (Power generator) Bhutan, region XX</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>ELCBTNXX00</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
-        </is>
-      </c>
       <c r="J213" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" hidden="1">
+      <c r="K213" t="inlineStr"/>
+    </row>
+    <row r="214">
       <c r="A214" t="n">
         <v>2</v>
       </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PWRLDSINDEA</t>
+          <t>PWRLDSBGDXX</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region EA</t>
+          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J214" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" hidden="1">
+      <c r="K214" t="inlineStr"/>
+    </row>
+    <row r="215">
       <c r="A215" t="n">
         <v>2</v>
       </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PWRLDSINDNE</t>
+          <t>PWRLDSBTNXX</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NE</t>
+          <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J215" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" hidden="1">
+      <c r="K215" t="inlineStr"/>
+    </row>
+    <row r="216">
       <c r="A216" t="n">
         <v>2</v>
       </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>PWRLDSINDNO</t>
+          <t>PWRLDSINDEA</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NO</t>
+          <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J216" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" hidden="1">
+      <c r="K216" t="inlineStr"/>
+    </row>
+    <row r="217">
       <c r="A217" t="n">
         <v>2</v>
       </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>PWRLDSINDSO</t>
+          <t>PWRLDSINDNE</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region SO</t>
+          <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J217" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" hidden="1">
+      <c r="K217" t="inlineStr"/>
+    </row>
+    <row r="218">
       <c r="A218" t="n">
         <v>2</v>
       </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PWRLDSINDWE</t>
+          <t>PWRLDSINDNO</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region WE</t>
+          <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J218" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" hidden="1">
+      <c r="K218" t="inlineStr"/>
+    </row>
+    <row r="219">
       <c r="A219" t="n">
         <v>2</v>
       </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PWRLDSLKAXX</t>
+          <t>PWRLDSINDSO</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J219" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" hidden="1">
+      <c r="K219" t="inlineStr"/>
+    </row>
+    <row r="220">
       <c r="A220" t="n">
         <v>2</v>
       </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>PWRLDSMDVXX</t>
+          <t>PWRLDSINDWE</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Maldives, region XX</t>
+          <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>ELCMDVXX00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J220" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" hidden="1">
+      <c r="K220" t="inlineStr"/>
+    </row>
+    <row r="221">
       <c r="A221" t="n">
         <v>2</v>
       </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSLKAXX</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J221" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" hidden="1">
+      <c r="K221" t="inlineStr"/>
+    </row>
+    <row r="222">
       <c r="A222" t="n">
         <v>2</v>
       </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCMDVXX00</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J222" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" hidden="1">
+      <c r="K222" t="inlineStr"/>
+    </row>
+    <row r="223">
       <c r="A223" t="n">
         <v>2</v>
       </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCNPLXX00</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J223" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" hidden="1">
+      <c r="K223" t="inlineStr"/>
+    </row>
+    <row r="224">
       <c r="A224" t="n">
         <v>2</v>
       </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J224" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" hidden="1">
+      <c r="K224" t="inlineStr"/>
+    </row>
+    <row r="225">
       <c r="A225" t="n">
         <v>2</v>
       </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J225" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" hidden="1">
+      <c r="K225" t="inlineStr"/>
+    </row>
+    <row r="226">
       <c r="A226" t="n">
         <v>2</v>
       </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J226" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" hidden="1">
+      <c r="K226" t="inlineStr"/>
+    </row>
+    <row r="227">
       <c r="A227" t="n">
         <v>2</v>
       </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J227" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" hidden="1">
+      <c r="K227" t="inlineStr"/>
+    </row>
+    <row r="228">
       <c r="A228" t="n">
         <v>2</v>
       </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J228" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" hidden="1">
+      <c r="K228" t="inlineStr"/>
+    </row>
+    <row r="229">
       <c r="A229" t="n">
         <v>2</v>
       </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J229" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" hidden="1">
+      <c r="K229" t="inlineStr"/>
+    </row>
+    <row r="230">
       <c r="A230" t="n">
         <v>2</v>
       </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PWRSDSMDVXX</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Maldives, region XX</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>ELCMDVXX00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J230" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" hidden="1">
+      <c r="K230" t="inlineStr"/>
+    </row>
+    <row r="231">
       <c r="A231" t="n">
         <v>2</v>
       </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
+          <t>PWRSDSLKAXX</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>ELCLKAXX00</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2</v>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
           <t>PWRSDSNPLXX</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H233" t="inlineStr">
         <is>
           <t>ELCNPLXX00</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I233" t="inlineStr">
         <is>
           <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="J231" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" hidden="1">
-      <c r="A232" t="n">
-        <v>1</v>
-      </c>
-      <c r="B232" t="inlineStr">
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1</v>
+      </c>
+      <c r="B234" t="inlineStr">
         <is>
           <t>ELCBGDXX00</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D232" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" t="inlineStr">
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
         <is>
           <t>PWRLDSBGDXX</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="233" hidden="1">
-      <c r="A233" t="n">
-        <v>1</v>
-      </c>
-      <c r="B233" t="inlineStr">
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>1</v>
+      </c>
+      <c r="B235" t="inlineStr">
         <is>
           <t>ELCBTNXX00</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D233" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" t="inlineStr">
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
         <is>
           <t>PWRLDSBTNXX</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="234" hidden="1">
-      <c r="A234" t="n">
-        <v>1</v>
-      </c>
-      <c r="B234" t="inlineStr">
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1</v>
+      </c>
+      <c r="B236" t="inlineStr">
         <is>
           <t>ELCINDEA00</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
-      <c r="D234" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" t="inlineStr">
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
         <is>
           <t>PWRLDSINDEA</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
-    </row>
-    <row r="235" hidden="1">
-      <c r="A235" t="n">
-        <v>1</v>
-      </c>
-      <c r="B235" t="inlineStr">
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>1</v>
+      </c>
+      <c r="B237" t="inlineStr">
         <is>
           <t>ELCINDNE00</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
-      <c r="D235" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" t="inlineStr">
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
         <is>
           <t>PWRLDSINDNE</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
-    </row>
-    <row r="236" hidden="1">
-      <c r="A236" t="n">
-        <v>1</v>
-      </c>
-      <c r="B236" t="inlineStr">
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>1</v>
+      </c>
+      <c r="B238" t="inlineStr">
         <is>
           <t>ELCINDNO00</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
-      <c r="D236" t="n">
-        <v>1</v>
-      </c>
-      <c r="F236" t="inlineStr">
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
         <is>
           <t>PWRLDSINDNO</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
-    </row>
-    <row r="237" hidden="1">
-      <c r="A237" t="n">
-        <v>1</v>
-      </c>
-      <c r="B237" t="inlineStr">
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>1</v>
+      </c>
+      <c r="B239" t="inlineStr">
         <is>
           <t>ELCINDSO00</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
-      <c r="D237" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" t="inlineStr">
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
         <is>
           <t>PWRLDSINDSO</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
-    </row>
-    <row r="238" hidden="1">
-      <c r="A238" t="n">
-        <v>1</v>
-      </c>
-      <c r="B238" t="inlineStr">
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>1</v>
+      </c>
+      <c r="B240" t="inlineStr">
         <is>
           <t>ELCINDWE00</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
-      <c r="D238" t="n">
-        <v>1</v>
-      </c>
-      <c r="F238" t="inlineStr">
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
         <is>
           <t>PWRLDSINDWE</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
-    </row>
-    <row r="239" hidden="1">
-      <c r="A239" t="n">
-        <v>1</v>
-      </c>
-      <c r="B239" t="inlineStr">
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>1</v>
+      </c>
+      <c r="B241" t="inlineStr">
         <is>
           <t>ELCLKAXX00</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D239" t="n">
-        <v>1</v>
-      </c>
-      <c r="F239" t="inlineStr">
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
         <is>
           <t>PWRLDSLKAXX</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G241" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="240" hidden="1">
-      <c r="A240" t="n">
-        <v>1</v>
-      </c>
-      <c r="B240" t="inlineStr">
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" t="inlineStr">
         <is>
           <t>ELCMDVXX00</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Electricity, Maldives, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" t="inlineStr">
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
         <is>
           <t>PWRLDSMDVXX</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="241" hidden="1">
-      <c r="A241" t="n">
-        <v>1</v>
-      </c>
-      <c r="B241" t="inlineStr">
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1</v>
+      </c>
+      <c r="B243" t="inlineStr">
         <is>
           <t>ELCNPLXX00</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D241" t="n">
-        <v>1</v>
-      </c>
-      <c r="F241" t="inlineStr">
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
         <is>
           <t>PWRLDSNPLXX</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="242" hidden="1">
-      <c r="A242" t="n">
-        <v>1</v>
-      </c>
-      <c r="B242" t="inlineStr">
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1</v>
+      </c>
+      <c r="B244" t="inlineStr">
         <is>
           <t>ELCBGDXX00</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D242" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" t="inlineStr">
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
         <is>
           <t>PWRSDSBGDXX</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G244" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="243" hidden="1">
-      <c r="A243" t="n">
-        <v>1</v>
-      </c>
-      <c r="B243" t="inlineStr">
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1</v>
+      </c>
+      <c r="B245" t="inlineStr">
         <is>
           <t>ELCBTNXX00</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D243" t="n">
-        <v>1</v>
-      </c>
-      <c r="F243" t="inlineStr">
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
         <is>
           <t>PWRSDSBTNXX</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G245" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="244" hidden="1">
-      <c r="A244" t="n">
-        <v>1</v>
-      </c>
-      <c r="B244" t="inlineStr">
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" t="inlineStr">
         <is>
           <t>ELCINDEA00</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
-      <c r="D244" t="n">
-        <v>1</v>
-      </c>
-      <c r="F244" t="inlineStr">
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
         <is>
           <t>PWRSDSINDEA</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G246" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
-    </row>
-    <row r="245" hidden="1">
-      <c r="A245" t="n">
-        <v>1</v>
-      </c>
-      <c r="B245" t="inlineStr">
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1</v>
+      </c>
+      <c r="B247" t="inlineStr">
         <is>
           <t>ELCINDNE00</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
-      <c r="D245" t="n">
-        <v>1</v>
-      </c>
-      <c r="F245" t="inlineStr">
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
         <is>
           <t>PWRSDSINDNE</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G247" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
-    </row>
-    <row r="246" hidden="1">
-      <c r="A246" t="n">
-        <v>1</v>
-      </c>
-      <c r="B246" t="inlineStr">
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1</v>
+      </c>
+      <c r="B248" t="inlineStr">
         <is>
           <t>ELCINDNO00</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
-      <c r="D246" t="n">
-        <v>1</v>
-      </c>
-      <c r="F246" t="inlineStr">
+      <c r="D248" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
         <is>
           <t>PWRSDSINDNO</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
-    </row>
-    <row r="247" hidden="1">
-      <c r="A247" t="n">
-        <v>1</v>
-      </c>
-      <c r="B247" t="inlineStr">
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1</v>
+      </c>
+      <c r="B249" t="inlineStr">
         <is>
           <t>ELCINDSO00</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
-      <c r="D247" t="n">
-        <v>1</v>
-      </c>
-      <c r="F247" t="inlineStr">
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
         <is>
           <t>PWRSDSINDSO</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G249" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
-    </row>
-    <row r="248" hidden="1">
-      <c r="A248" t="n">
-        <v>1</v>
-      </c>
-      <c r="B248" t="inlineStr">
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1</v>
+      </c>
+      <c r="B250" t="inlineStr">
         <is>
           <t>ELCINDWE00</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
-      <c r="D248" t="n">
-        <v>1</v>
-      </c>
-      <c r="F248" t="inlineStr">
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
         <is>
           <t>PWRSDSINDWE</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G250" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
-    </row>
-    <row r="249" hidden="1">
-      <c r="A249" t="n">
-        <v>1</v>
-      </c>
-      <c r="B249" t="inlineStr">
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1</v>
+      </c>
+      <c r="B251" t="inlineStr">
         <is>
           <t>ELCLKAXX00</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D249" t="n">
-        <v>1</v>
-      </c>
-      <c r="F249" t="inlineStr">
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
         <is>
           <t>PWRSDSLKAXX</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G251" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="250" hidden="1">
-      <c r="A250" t="n">
-        <v>1</v>
-      </c>
-      <c r="B250" t="inlineStr">
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>1</v>
+      </c>
+      <c r="B252" t="inlineStr">
         <is>
           <t>ELCMDVXX00</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>Electricity, Maldives, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D250" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" t="inlineStr">
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
         <is>
           <t>PWRSDSMDVXX</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="251" hidden="1">
-      <c r="A251" t="n">
-        <v>1</v>
-      </c>
-      <c r="B251" t="inlineStr">
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>1</v>
+      </c>
+      <c r="B253" t="inlineStr">
         <is>
           <t>ELCNPLXX00</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
-      <c r="D251" t="n">
-        <v>1</v>
-      </c>
-      <c r="F251" t="inlineStr">
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
         <is>
           <t>PWRSDSNPLXX</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K251">
-    <filterColumn colId="5" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="TRNBGDXXINDEA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14150,71 +14870,71 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="60.140625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="57.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="60.109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="57.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Mode.Operation</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Fuel.I</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Fuel.I.Name</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Value.Fuel.I</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Unit.Fuel.I</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Tech.Name</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Fuel.O</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Fuel.O.Name</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Value.Fuel.O</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Unit.Fuel.O</t>
         </is>
@@ -14237,6 +14957,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>RNWTRNBGDXX</t>
@@ -14260,6 +14981,7 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -14278,6 +15000,7 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>RNWRPOBGDXX</t>
@@ -14301,6 +15024,7 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14319,6 +15043,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>RNWNLIBGDXX</t>
@@ -14342,6 +15067,7 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -14360,6 +15086,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRTRNBGDXX</t>
@@ -14383,6 +15110,7 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -14401,6 +15129,7 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TRNRPOBGDXX</t>
@@ -14424,6 +15153,7 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -14442,6 +15172,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TRNNLIBGDXX</t>
@@ -14465,6 +15196,7 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14483,6 +15215,7 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>RNWTRNBTNXX</t>
@@ -14506,6 +15239,7 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14524,6 +15258,7 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>RNWRPOBTNXX</t>
@@ -14547,6 +15282,7 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14565,6 +15301,7 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>RNWNLIBTNXX</t>
@@ -14588,6 +15325,7 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14606,6 +15344,7 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PWRTRNBTNXX</t>
@@ -14629,6 +15368,7 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14647,6 +15387,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>TRNRPOBTNXX</t>
@@ -14670,6 +15411,7 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14688,6 +15430,7 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>TRNNLIBTNXX</t>
@@ -14711,6 +15454,7 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14729,6 +15473,7 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>RNWTRNINDEA</t>
@@ -14752,6 +15497,7 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14770,6 +15516,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>RNWRPOINDEA</t>
@@ -14793,6 +15540,7 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14811,6 +15559,7 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>RNWNLIINDEA</t>
@@ -14834,6 +15583,7 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14852,6 +15602,7 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PWRTRNINDEA</t>
@@ -14875,6 +15626,7 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14893,6 +15645,7 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>TRNRPOINDEA</t>
@@ -14916,6 +15669,7 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14934,6 +15688,7 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>TRNNLIINDEA</t>
@@ -14957,6 +15712,7 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14975,6 +15731,7 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>RNWTRNINDNE</t>
@@ -14998,6 +15755,7 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15016,6 +15774,7 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>RNWRPOINDNE</t>
@@ -15039,6 +15798,7 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15057,6 +15817,7 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>RNWNLIINDNE</t>
@@ -15080,6 +15841,7 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15098,6 +15860,7 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PWRTRNINDNE</t>
@@ -15121,6 +15884,7 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15139,6 +15903,7 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>TRNRPOINDNE</t>
@@ -15162,6 +15927,7 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -15180,6 +15946,7 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>TRNNLIINDNE</t>
@@ -15203,6 +15970,7 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -15221,6 +15989,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>RNWTRNINDNO</t>
@@ -15244,6 +16013,7 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -15262,6 +16032,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>RNWRPOINDNO</t>
@@ -15285,6 +16056,7 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15303,6 +16075,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>RNWNLIINDNO</t>
@@ -15326,6 +16099,7 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15344,6 +16118,7 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRTRNINDNO</t>
@@ -15367,6 +16142,7 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15385,6 +16161,7 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TRNRPOINDNO</t>
@@ -15408,6 +16185,7 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15426,6 +16204,7 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TRNNLIINDNO</t>
@@ -15449,6 +16228,7 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -15467,6 +16247,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>RNWTRNINDSO</t>
@@ -15490,6 +16271,7 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -15508,6 +16290,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>RNWRPOINDSO</t>
@@ -15531,6 +16314,7 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -15549,6 +16333,7 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>RNWNLIINDSO</t>
@@ -15572,6 +16357,7 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -15590,6 +16376,7 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>PWRTRNINDSO</t>
@@ -15613,6 +16400,7 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -15631,6 +16419,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>TRNRPOINDSO</t>
@@ -15654,6 +16443,7 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -15672,6 +16462,7 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>TRNNLIINDSO</t>
@@ -15695,6 +16486,7 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -15713,6 +16505,7 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>RNWTRNINDWE</t>
@@ -15736,6 +16529,7 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -15754,6 +16548,7 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>RNWRPOINDWE</t>
@@ -15777,6 +16572,7 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -15795,6 +16591,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>RNWNLIINDWE</t>
@@ -15818,6 +16615,7 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -15836,6 +16634,7 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>PWRTRNINDWE</t>
@@ -15859,6 +16658,7 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -15877,6 +16677,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>TRNRPOINDWE</t>
@@ -15900,6 +16701,7 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -15918,6 +16720,7 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>TRNNLIINDWE</t>
@@ -15941,6 +16744,7 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -15959,6 +16763,7 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>RNWTRNNPLXX</t>
@@ -15982,6 +16787,7 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -16000,6 +16806,7 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>RNWRPONPLXX</t>
@@ -16023,6 +16830,7 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -16041,6 +16849,7 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>RNWNLINPLXX</t>
@@ -16064,6 +16873,7 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -16082,6 +16892,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>PWRTRNNPLXX</t>
@@ -16105,6 +16916,7 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -16123,6 +16935,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>TRNRPONPLXX</t>
@@ -16146,6 +16959,7 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -16164,6 +16978,7 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>TRNNLINPLXX</t>
@@ -16187,6 +17002,7 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -16205,6 +17021,7 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>RNWTRNLKAXX</t>
@@ -16228,6 +17045,7 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -16246,6 +17064,7 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>RNWRPOLKAXX</t>
@@ -16269,6 +17088,7 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -16287,6 +17107,7 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>RNWNLILKAXX</t>
@@ -16310,6 +17131,7 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -16328,6 +17150,7 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRTRNLKAXX</t>
@@ -16351,6 +17174,7 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -16369,6 +17193,7 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>TRNRPOLKAXX</t>
@@ -16392,6 +17217,7 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -16410,6 +17236,7 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>TRNNLILKAXX</t>
@@ -16433,6 +17260,7 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -16451,6 +17279,7 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>RNWTRNMDVXX</t>
@@ -16474,6 +17303,7 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -16492,6 +17322,7 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>RNWRPOMDVXX</t>
@@ -16515,6 +17346,7 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -16533,6 +17365,7 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>RNWNLIMDVXX</t>
@@ -16556,6 +17389,7 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -16574,6 +17408,7 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>PWRTRNMDVXX</t>
@@ -16597,6 +17432,7 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -16615,6 +17451,7 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>TRNRPOMDVXX</t>
@@ -16638,6 +17475,7 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -16656,6 +17494,7 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>TRNNLIMDVXX</t>
@@ -16679,6 +17518,7 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
+      <c r="K61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16692,22 +17532,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="7.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="38.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="10.85546875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="39.5703125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="7.44140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="38.44140625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="39.5546875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="11" bestFit="1" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Mode.Operation</t>
         </is>
@@ -16775,25 +17615,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="13" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="13" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="17.7109375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="17.6640625" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="26" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="13" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="12" max="13"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="12" max="13"/>
     <col width="11" bestFit="1" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Mode.Operation</t>
         </is>
@@ -16881,22 +17721,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.109375" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="11" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="12.42578125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="15.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="35.28515625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="12.44140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="35.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="11" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Mode.Operation</t>
         </is>
@@ -16953,134 +17793,134 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -692,22 +692,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MINCOANPL</t>
+          <t>MINCOAMDV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coal (Mining tradable commodity) Nepal</t>
+          <t>Coal (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COANPL</t>
+          <t>COAMDV</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coal, Nepal</t>
+          <t>Coal, Maldives</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -720,22 +720,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MINCOGBGD</t>
+          <t>MINCOANPL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) Bangladesh</t>
+          <t>Coal (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COGBGD</t>
+          <t>COANPL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cogeneration, Bangladesh</t>
+          <t>Coal, Nepal</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -748,22 +748,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MINCOGBTN</t>
+          <t>MINCOGBGD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) Bhutan</t>
+          <t>Cogeneration (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COGBTN</t>
+          <t>COGBGD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cogeneration, Bhutan</t>
+          <t>Cogeneration, Bangladesh</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -776,22 +776,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MINCOGIND</t>
+          <t>MINCOGBTN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) India</t>
+          <t>Cogeneration (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>COGIND</t>
+          <t>COGBTN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cogeneration, India</t>
+          <t>Cogeneration, Bhutan</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MINCOGINT</t>
+          <t>MINCOGIND</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) International Markets</t>
+          <t>Cogeneration (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COGINT</t>
+          <t>COGIND</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cogeneration, International Markets</t>
+          <t>Cogeneration, India</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -832,22 +832,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MINCOGLKA</t>
+          <t>MINCOGINT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) Sri Lanka</t>
+          <t>Cogeneration (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COGLKA</t>
+          <t>COGINT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cogeneration, Sri Lanka</t>
+          <t>Cogeneration, International Markets</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -860,22 +860,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MINCOGNPL</t>
+          <t>MINCOGLKA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cogeneration (Mining tradable commodity) Nepal</t>
+          <t>Cogeneration (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COGNPL</t>
+          <t>COGLKA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cogeneration, Nepal</t>
+          <t>Cogeneration, Sri Lanka</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -888,22 +888,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MINGASBGD</t>
+          <t>MINCOGMDV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) Bangladesh</t>
+          <t>Cogeneration (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GASBGD</t>
+          <t>COGMDV</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Natural Gas, Bangladesh</t>
+          <t>Cogeneration, Maldives</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -916,22 +916,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MINGASBTN</t>
+          <t>MINCOGNPL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) Bhutan</t>
+          <t>Cogeneration (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GASBTN</t>
+          <t>COGNPL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Natural Gas, Bhutan</t>
+          <t>Cogeneration, Nepal</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -944,22 +944,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MINGASIND</t>
+          <t>MINGASBGD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) India</t>
+          <t>Natural Gas (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GASIND</t>
+          <t>GASBGD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Natural Gas, India</t>
+          <t>Natural Gas, Bangladesh</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -972,22 +972,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MINGASINT</t>
+          <t>MINGASBTN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) International Markets</t>
+          <t>Natural Gas (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GASINT</t>
+          <t>GASBTN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Natural Gas, International Markets</t>
+          <t>Natural Gas, Bhutan</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1000,22 +1000,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MINGASLKA</t>
+          <t>MINGASIND</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) Sri Lanka</t>
+          <t>Natural Gas (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GASLKA</t>
+          <t>GASIND</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Natural Gas, Sri Lanka</t>
+          <t>Natural Gas, India</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MINGASNPL</t>
+          <t>MINGASINT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Natural Gas (Mining tradable commodity) Nepal</t>
+          <t>Natural Gas (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GASNPL</t>
+          <t>GASINT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Natural Gas, Nepal</t>
+          <t>Natural Gas, International Markets</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MINOILBGD</t>
+          <t>MINGASLKA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) Bangladesh</t>
+          <t>Natural Gas (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OILBGD</t>
+          <t>GASLKA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oil, Bangladesh</t>
+          <t>Natural Gas, Sri Lanka</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MINOILBTN</t>
+          <t>MINGASMDV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) Bhutan</t>
+          <t>Natural Gas (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OILBTN</t>
+          <t>GASMDV</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oil, Bhutan</t>
+          <t>Natural Gas, Maldives</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1112,22 +1112,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MINOILIND</t>
+          <t>MINGASNPL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) India</t>
+          <t>Natural Gas (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OILIND</t>
+          <t>GASNPL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oil, India</t>
+          <t>Natural Gas, Nepal</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MINOILINT</t>
+          <t>MINOILBGD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) International Markets</t>
+          <t>Oil (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OILINT</t>
+          <t>OILBGD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil, International Markets</t>
+          <t>Oil, Bangladesh</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MINOILLKA</t>
+          <t>MINOILBTN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) Sri Lanka</t>
+          <t>Oil (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OILLKA</t>
+          <t>OILBTN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil, Sri Lanka</t>
+          <t>Oil, Bhutan</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1196,22 +1196,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MINOILNPL</t>
+          <t>MINOILIND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oil (Mining tradable commodity) Nepal</t>
+          <t>Oil (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OILNPL</t>
+          <t>OILIND</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oil, Nepal</t>
+          <t>Oil, India</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MINOTHBGD</t>
+          <t>MINOILINT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) Bangladesh</t>
+          <t>Oil (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OTHBGD</t>
+          <t>OILINT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Other, Bangladesh</t>
+          <t>Oil, International Markets</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MINOTHBTN</t>
+          <t>MINOILLKA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) Bhutan</t>
+          <t>Oil (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OTHBTN</t>
+          <t>OILLKA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Other, Bhutan</t>
+          <t>Oil, Sri Lanka</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MINOTHIND</t>
+          <t>MINOILMDV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) India</t>
+          <t>Oil (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OTHIND</t>
+          <t>OILMDV</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Other, India</t>
+          <t>Oil, Maldives</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MINOTHINT</t>
+          <t>MINOILNPL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) International Markets</t>
+          <t>Oil (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OTHINT</t>
+          <t>OILNPL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Other, International Markets</t>
+          <t>Oil, Nepal</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MINOTHLKA</t>
+          <t>MINOTHBGD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) Sri Lanka</t>
+          <t>Other (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OTHLKA</t>
+          <t>OTHBGD</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Other, Sri Lanka</t>
+          <t>Other, Bangladesh</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MINOTHNPL</t>
+          <t>MINOTHBTN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other (Mining tradable commodity) Nepal</t>
+          <t>Other (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OTHNPL</t>
+          <t>OTHBTN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Other, Nepal</t>
+          <t>Other, Bhutan</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MINPETBGD</t>
+          <t>MINOTHIND</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) Bangladesh</t>
+          <t>Other (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PETBGD</t>
+          <t>OTHIND</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petroleum, Bangladesh</t>
+          <t>Other, India</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1420,22 +1420,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MINPETBTN</t>
+          <t>MINOTHINT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) Bhutan</t>
+          <t>Other (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PETBTN</t>
+          <t>OTHINT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petroleum, Bhutan</t>
+          <t>Other, International Markets</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1448,22 +1448,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MINPETIND</t>
+          <t>MINOTHLKA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) India</t>
+          <t>Other (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PETIND</t>
+          <t>OTHLKA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petroleum, India</t>
+          <t>Other, Sri Lanka</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MINPETINT</t>
+          <t>MINOTHMDV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) International Markets</t>
+          <t>Other (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PETINT</t>
+          <t>OTHMDV</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Petroleum, International Markets</t>
+          <t>Other, Maldives</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1504,22 +1504,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MINPETLKA</t>
+          <t>MINOTHNPL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) Sri Lanka</t>
+          <t>Other (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PETLKA</t>
+          <t>OTHNPL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Petroleum, Sri Lanka</t>
+          <t>Other, Nepal</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1532,22 +1532,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MINPETNPL</t>
+          <t>MINPETBGD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Petroleum (Mining tradable commodity) Nepal</t>
+          <t>Petroleum (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PETNPL</t>
+          <t>PETBGD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Petroleum, Nepal</t>
+          <t>Petroleum, Bangladesh</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MINURNBGD</t>
+          <t>MINPETBTN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) Bangladesh</t>
+          <t>Petroleum (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>URNBGD</t>
+          <t>PETBTN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nuclear, Bangladesh</t>
+          <t>Petroleum, Bhutan</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1588,22 +1588,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MINURNBTN</t>
+          <t>MINPETIND</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) Bhutan</t>
+          <t>Petroleum (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>URNBTN</t>
+          <t>PETIND</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nuclear, Bhutan</t>
+          <t>Petroleum, India</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1616,22 +1616,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MINURNIND</t>
+          <t>MINPETINT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) India</t>
+          <t>Petroleum (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>PETINT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Petroleum, International Markets</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MINURNINT</t>
+          <t>MINPETLKA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) International Markets</t>
+          <t>Petroleum (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>PETLKA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Petroleum, Sri Lanka</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MINURNLKA</t>
+          <t>MINPETMDV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) Sri Lanka</t>
+          <t>Petroleum (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>URNLKA</t>
+          <t>PETMDV</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nuclear, Sri Lanka</t>
+          <t>Petroleum, Maldives</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MINURNNPL</t>
+          <t>MINPETNPL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nuclear (Mining tradable commodity) Nepal</t>
+          <t>Petroleum (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>URNNPL</t>
+          <t>PETNPL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nuclear, Nepal</t>
+          <t>Petroleum, Nepal</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1728,22 +1728,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RNWBIOBGDXX</t>
+          <t>MINURNBGD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Nuclear (Mining tradable commodity) Bangladesh</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BIOBGDXX</t>
+          <t>URNBGD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Biomass, Bangladesh, region XX</t>
+          <t>Nuclear, Bangladesh</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1756,22 +1756,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RNWBIOBTNXX</t>
+          <t>MINURNBTN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Nuclear (Mining tradable commodity) Bhutan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BIOBTNXX</t>
+          <t>URNBTN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Biomass, Bhutan, region XX</t>
+          <t>Nuclear, Bhutan</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RNWBIOINDEA</t>
+          <t>MINURNIND</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Nuclear (Mining tradable commodity) India</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BIOINDEA</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Biomass, India, region EA</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1812,22 +1812,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RNWBIOINDNE</t>
+          <t>MINURNINT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Nuclear (Mining tradable commodity) International Markets</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BIOINDNE</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Biomass, India, region NE</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RNWBIOINDNO</t>
+          <t>MINURNLKA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Nuclear (Mining tradable commodity) Sri Lanka</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BIOINDNO</t>
+          <t>URNLKA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Biomass, India, region NO</t>
+          <t>Nuclear, Sri Lanka</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1868,22 +1868,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RNWBIOINDSO</t>
+          <t>MINURNMDV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Nuclear (Mining tradable commodity) Maldives</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BIOINDSO</t>
+          <t>URNMDV</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Biomass, India, region SO</t>
+          <t>Nuclear, Maldives</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RNWBIOINDWE</t>
+          <t>MINURNNPL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Nuclear (Mining tradable commodity) Nepal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BIOINDWE</t>
+          <t>URNNPL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Biomass, India, region WE</t>
+          <t>Nuclear, Nepal</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1924,22 +1924,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RNWBIOLKAXX</t>
+          <t>RNWBIOBGDXX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BIOLKAXX</t>
+          <t>BIOBGDXX</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Biomass, Sri Lanka, region XX</t>
+          <t>Biomass, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1952,22 +1952,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RNWBIONPLXX</t>
+          <t>RNWBIOBTNXX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Biomass (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BIONPLXX</t>
+          <t>BIOBTNXX</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Biomass, Nepal, region XX</t>
+          <t>Biomass, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RNWCSPBGDXX</t>
+          <t>RNWBIOINDEA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CSPBGDXX</t>
+          <t>BIOINDEA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, Bangladesh, region XX</t>
+          <t>Biomass, India, region EA</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2008,22 +2008,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RNWCSPBTNXX</t>
+          <t>RNWBIOINDNE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CSPBTNXX</t>
+          <t>BIOINDNE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, Bhutan, region XX</t>
+          <t>Biomass, India, region NE</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2036,22 +2036,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RNWCSPINDEA</t>
+          <t>RNWBIOINDNO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CSPINDEA</t>
+          <t>BIOINDNO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, India, region EA</t>
+          <t>Biomass, India, region NO</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2064,22 +2064,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RNWCSPINDNE</t>
+          <t>RNWBIOINDSO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CSPINDNE</t>
+          <t>BIOINDSO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, India, region NE</t>
+          <t>Biomass, India, region SO</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RNWCSPINDNO</t>
+          <t>RNWBIOINDWE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CSPINDNO</t>
+          <t>BIOINDWE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, India, region NO</t>
+          <t>Biomass, India, region WE</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RNWCSPINDSO</t>
+          <t>RNWBIOLKAXX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CSPINDSO</t>
+          <t>BIOLKAXX</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, India, region SO</t>
+          <t>Biomass, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RNWCSPINDWE</t>
+          <t>RNWBIOMDVXX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CSPINDWE</t>
+          <t>BIOMDVXX</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, India, region WE</t>
+          <t>Biomass, Maldives, region XX</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RNWCSPLKAXX</t>
+          <t>RNWBIONPLXX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Biomass (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CSPLKAXX</t>
+          <t>BIONPLXX</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, Sri Lanka, region XX</t>
+          <t>Biomass, Nepal, region XX</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RNWCSPNPLXX</t>
+          <t>RNWCSPBGDXX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CSPNPLXX</t>
+          <t>CSPBGDXX</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concentrated Solar Power, Nepal, region XX</t>
+          <t>Concentrated Solar Power, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2232,22 +2232,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RNWGEOBGDXX</t>
+          <t>RNWCSPBTNXX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GEOBGDXX</t>
+          <t>CSPBTNXX</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Geothermal, Bangladesh, region XX</t>
+          <t>Concentrated Solar Power, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2260,22 +2260,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RNWGEOBTNXX</t>
+          <t>RNWCSPINDEA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GEOBTNXX</t>
+          <t>CSPINDEA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Geothermal, Bhutan, region XX</t>
+          <t>Concentrated Solar Power, India, region EA</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2288,22 +2288,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RNWGEOINDEA</t>
+          <t>RNWCSPINDNE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GEOINDEA</t>
+          <t>CSPINDNE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Geothermal, India, region EA</t>
+          <t>Concentrated Solar Power, India, region NE</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RNWGEOINDNE</t>
+          <t>RNWCSPINDNO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GEOINDNE</t>
+          <t>CSPINDNO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Geothermal, India, region NE</t>
+          <t>Concentrated Solar Power, India, region NO</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2344,22 +2344,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RNWGEOINDNO</t>
+          <t>RNWCSPINDSO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GEOINDNO</t>
+          <t>CSPINDSO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Geothermal, India, region NO</t>
+          <t>Concentrated Solar Power, India, region SO</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RNWGEOINDSO</t>
+          <t>RNWCSPINDWE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GEOINDSO</t>
+          <t>CSPINDWE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Geothermal, India, region SO</t>
+          <t>Concentrated Solar Power, India, region WE</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2400,22 +2400,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RNWGEOINDWE</t>
+          <t>RNWCSPLKAXX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GEOINDWE</t>
+          <t>CSPLKAXX</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Geothermal, India, region WE</t>
+          <t>Concentrated Solar Power, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RNWGEOLKAXX</t>
+          <t>RNWCSPMDVXX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>GEOLKAXX</t>
+          <t>CSPMDVXX</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Geothermal, Sri Lanka, region XX</t>
+          <t>Concentrated Solar Power, Maldives, region XX</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2456,22 +2456,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RNWGEONPLXX</t>
+          <t>RNWCSPNPLXX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Geothermal (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Concentrated Solar Power (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>GEONPLXX</t>
+          <t>CSPNPLXX</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Geothermal, Nepal, region XX</t>
+          <t>Concentrated Solar Power, Nepal, region XX</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2484,22 +2484,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RNWHYDBGDXX</t>
+          <t>RNWGEOBGDXX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>HYDBGDXX</t>
+          <t>GEOBGDXX</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hydroelectric, Bangladesh, region XX</t>
+          <t>Geothermal, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RNWHYDBTNXX</t>
+          <t>RNWGEOBTNXX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HYDBTNXX</t>
+          <t>GEOBTNXX</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hydroelectric, Bhutan, region XX</t>
+          <t>Geothermal, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2540,22 +2540,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RNWHYDINDEA</t>
+          <t>RNWGEOINDEA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HYDINDEA</t>
+          <t>GEOINDEA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hydroelectric, India, region EA</t>
+          <t>Geothermal, India, region EA</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RNWHYDINDNE</t>
+          <t>RNWGEOINDNE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HYDINDNE</t>
+          <t>GEOINDNE</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hydroelectric, India, region NE</t>
+          <t>Geothermal, India, region NE</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RNWHYDINDNO</t>
+          <t>RNWGEOINDNO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HYDINDNO</t>
+          <t>GEOINDNO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hydroelectric, India, region NO</t>
+          <t>Geothermal, India, region NO</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2624,22 +2624,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RNWHYDINDSO</t>
+          <t>RNWGEOINDSO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HYDINDSO</t>
+          <t>GEOINDSO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hydroelectric, India, region SO</t>
+          <t>Geothermal, India, region SO</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2652,22 +2652,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RNWHYDINDWE</t>
+          <t>RNWGEOINDWE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HYDINDWE</t>
+          <t>GEOINDWE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hydroelectric, India, region WE</t>
+          <t>Geothermal, India, region WE</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2680,22 +2680,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RNWHYDLKAXX</t>
+          <t>RNWGEOLKAXX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HYDLKAXX</t>
+          <t>GEOLKAXX</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hydroelectric, Sri Lanka, region XX</t>
+          <t>Geothermal, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2708,22 +2708,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RNWHYDNPLXX</t>
+          <t>RNWGEOMDVXX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>HYDNPLXX</t>
+          <t>GEOMDVXX</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hydroelectric, Nepal, region XX</t>
+          <t>Geothermal, Maldives, region XX</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2736,22 +2736,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RNWSPVBGDXX</t>
+          <t>RNWGEONPLXX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Geothermal (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SPVBGDXX</t>
+          <t>GEONPLXX</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Bangladesh, region XX</t>
+          <t>Geothermal, Nepal, region XX</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RNWSPVBTNXX</t>
+          <t>RNWHYDBGDXX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SPVBTNXX</t>
+          <t>HYDBGDXX</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Bhutan, region XX</t>
+          <t>Hydroelectric, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2792,22 +2792,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RNWSPVINDEA</t>
+          <t>RNWHYDBTNXX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SPVINDEA</t>
+          <t>HYDBTNXX</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region EA</t>
+          <t>Hydroelectric, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2820,22 +2820,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RNWSPVINDNE</t>
+          <t>RNWHYDINDEA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SPVINDNE</t>
+          <t>HYDINDEA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region NE</t>
+          <t>Hydroelectric, India, region EA</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2848,22 +2848,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RNWSPVINDNO</t>
+          <t>RNWHYDINDNE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SPVINDNO</t>
+          <t>HYDINDNE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region NO</t>
+          <t>Hydroelectric, India, region NE</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2876,22 +2876,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RNWSPVINDSO</t>
+          <t>RNWHYDINDNO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SPVINDSO</t>
+          <t>HYDINDNO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region SO</t>
+          <t>Hydroelectric, India, region NO</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RNWSPVINDWE</t>
+          <t>RNWHYDINDSO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SPVINDWE</t>
+          <t>HYDINDSO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region WE</t>
+          <t>Hydroelectric, India, region SO</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2932,22 +2932,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RNWSPVLKAXX</t>
+          <t>RNWHYDINDWE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SPVLKAXX</t>
+          <t>HYDINDWE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Sri Lanka, region XX</t>
+          <t>Hydroelectric, India, region WE</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -2960,22 +2960,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RNWSPVNPLXX</t>
+          <t>RNWHYDLKAXX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SPVNPLXX</t>
+          <t>HYDLKAXX</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Nepal, region XX</t>
+          <t>Hydroelectric, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -2988,22 +2988,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RNWWASBGDXX</t>
+          <t>RNWHYDMDVXX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>WASBGDXX</t>
+          <t>HYDMDVXX</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Waste, Bangladesh, region XX</t>
+          <t>Hydroelectric, Maldives, region XX</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RNWWASBTNXX</t>
+          <t>RNWHYDNPLXX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Hydroelectric (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>WASBTNXX</t>
+          <t>HYDNPLXX</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waste, Bhutan, region XX</t>
+          <t>Hydroelectric, Nepal, region XX</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3044,22 +3044,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RNWWASINDEA</t>
+          <t>RNWSPVBGDXX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>WASINDEA</t>
+          <t>SPVBGDXX</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waste, India, region EA</t>
+          <t>Solar Photovoltaic, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RNWWASINDNE</t>
+          <t>RNWSPVBTNXX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>WASINDNE</t>
+          <t>SPVBTNXX</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Waste, India, region NE</t>
+          <t>Solar Photovoltaic, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RNWWASINDNO</t>
+          <t>RNWSPVINDEA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>WASINDNO</t>
+          <t>SPVINDEA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Waste, India, region NO</t>
+          <t>Solar Photovoltaic, India, region EA</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3128,22 +3128,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RNWWASINDSO</t>
+          <t>RNWSPVINDNE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>WASINDSO</t>
+          <t>SPVINDNE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waste, India, region SO</t>
+          <t>Solar Photovoltaic, India, region NE</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RNWWASINDWE</t>
+          <t>RNWSPVINDNO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>WASINDWE</t>
+          <t>SPVINDNO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waste, India, region WE</t>
+          <t>Solar Photovoltaic, India, region NO</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3184,22 +3184,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RNWWASLKAXX</t>
+          <t>RNWSPVINDSO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>WASLKAXX</t>
+          <t>SPVINDSO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waste, Sri Lanka, region XX</t>
+          <t>Solar Photovoltaic, India, region SO</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3212,22 +3212,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RNWWASNPLXX</t>
+          <t>RNWSPVINDWE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Waste (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>WASNPLXX</t>
+          <t>SPVINDWE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waste, Nepal, region XX</t>
+          <t>Solar Photovoltaic, India, region WE</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RNWWAVBGDXX</t>
+          <t>RNWSPVLKAXX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>WAVBGDXX</t>
+          <t>SPVLKAXX</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wave, Bangladesh, region XX</t>
+          <t>Solar Photovoltaic, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3268,22 +3268,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RNWWAVBTNXX</t>
+          <t>RNWSPVMDVXX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WAVBTNXX</t>
+          <t>SPVMDVXX</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wave, Bhutan, region XX</t>
+          <t>Solar Photovoltaic, Maldives, region XX</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RNWWAVINDEA</t>
+          <t>RNWSPVNPLXX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Solar Photovoltaic (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>WAVINDEA</t>
+          <t>SPVNPLXX</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wave, India, region EA</t>
+          <t>Solar Photovoltaic, Nepal, region XX</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3324,22 +3324,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RNWWAVINDNE</t>
+          <t>RNWWASBGDXX</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>WAVINDNE</t>
+          <t>WASBGDXX</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wave, India, region NE</t>
+          <t>Waste, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RNWWAVINDNO</t>
+          <t>RNWWASBTNXX</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>WAVINDNO</t>
+          <t>WASBTNXX</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wave, India, region NO</t>
+          <t>Waste, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3380,22 +3380,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RNWWAVINDSO</t>
+          <t>RNWWASINDEA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WAVINDSO</t>
+          <t>WASINDEA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wave, India, region SO</t>
+          <t>Waste, India, region EA</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RNWWAVINDWE</t>
+          <t>RNWWASINDNE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WAVINDWE</t>
+          <t>WASINDNE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wave, India, region WE</t>
+          <t>Waste, India, region NE</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3436,22 +3436,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RNWWAVLKAXX</t>
+          <t>RNWWASINDNO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>WAVLKAXX</t>
+          <t>WASINDNO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wave, Sri Lanka, region XX</t>
+          <t>Waste, India, region NO</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3464,22 +3464,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RNWWAVNPLXX</t>
+          <t>RNWWASINDSO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wave (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WAVNPLXX</t>
+          <t>WASINDSO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wave, Nepal, region XX</t>
+          <t>Waste, India, region SO</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3492,22 +3492,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RNWWOFBGDXX</t>
+          <t>RNWWASINDWE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WOFBGDXX</t>
+          <t>WASINDWE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Offshore Wind, Bangladesh, region XX</t>
+          <t>Waste, India, region WE</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3520,22 +3520,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RNWWOFBTNXX</t>
+          <t>RNWWASLKAXX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>WOFBTNXX</t>
+          <t>WASLKAXX</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Offshore Wind, Bhutan, region XX</t>
+          <t>Waste, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RNWWOFINDEA</t>
+          <t>RNWWASMDVXX</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>WOFINDEA</t>
+          <t>WASMDVXX</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region EA</t>
+          <t>Waste, Maldives, region XX</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RNWWOFINDNE</t>
+          <t>RNWWASNPLXX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Waste (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>WOFINDNE</t>
+          <t>WASNPLXX</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region NE</t>
+          <t>Waste, Nepal, region XX</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3604,22 +3604,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RNWWOFINDNO</t>
+          <t>RNWWAVBGDXX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>WOFINDNO</t>
+          <t>WAVBGDXX</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region NO</t>
+          <t>Wave, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3632,22 +3632,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RNWWOFINDSO</t>
+          <t>RNWWAVBTNXX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>WOFINDSO</t>
+          <t>WAVBTNXX</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region SO</t>
+          <t>Wave, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3660,22 +3660,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RNWWOFINDWE</t>
+          <t>RNWWAVINDEA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>WOFINDWE</t>
+          <t>WAVINDEA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region WE</t>
+          <t>Wave, India, region EA</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3688,22 +3688,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RNWWOFLKAXX</t>
+          <t>RNWWAVINDNE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) India, region NE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>WOFLKAXX</t>
+          <t>WAVINDNE</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Offshore Wind, Sri Lanka, region XX</t>
+          <t>Wave, India, region NE</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3716,22 +3716,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RNWWOFNPLXX</t>
+          <t>RNWWAVINDNO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) India, region NO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>WOFNPLXX</t>
+          <t>WAVINDNO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Offshore Wind, Nepal, region XX</t>
+          <t>Wave, India, region NO</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3744,22 +3744,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RNWWONBGDXX</t>
+          <t>RNWWAVINDSO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) India, region SO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>WONBGDXX</t>
+          <t>WAVINDSO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Onshore Wind, Bangladesh, region XX</t>
+          <t>Wave, India, region SO</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3772,22 +3772,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RNWWONBTNXX</t>
+          <t>RNWWAVINDWE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) India, region WE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>WONBTNXX</t>
+          <t>WAVINDWE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Onshore Wind, Bhutan, region XX</t>
+          <t>Wave, India, region WE</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3800,22 +3800,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RNWWONINDEA</t>
+          <t>RNWWAVLKAXX</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region EA</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>WONINDEA</t>
+          <t>WAVLKAXX</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region EA</t>
+          <t>Wave, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3828,22 +3828,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RNWWONINDNE</t>
+          <t>RNWWAVMDVXX</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region NE</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WONINDNE</t>
+          <t>WAVMDVXX</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region NE</t>
+          <t>Wave, Maldives, region XX</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3856,22 +3856,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RNWWONINDNO</t>
+          <t>RNWWAVNPLXX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region NO</t>
+          <t>Wave (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>WONINDNO</t>
+          <t>WAVNPLXX</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region NO</t>
+          <t>Wave, Nepal, region XX</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RNWWONINDSO</t>
+          <t>RNWWOFBGDXX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region SO</t>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>WONINDSO</t>
+          <t>WOFBGDXX</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region SO</t>
+          <t>Offshore Wind, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -3912,22 +3912,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RNWWONINDWE</t>
+          <t>RNWWOFBTNXX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region WE</t>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>WONINDWE</t>
+          <t>WOFBTNXX</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region WE</t>
+          <t>Offshore Wind, Bhutan, region XX</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -3940,22 +3940,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RNWWONLKAXX</t>
+          <t>RNWWOFINDEA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region EA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>WONLKAXX</t>
+          <t>WOFINDEA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Onshore Wind, Sri Lanka, region XX</t>
+          <t>Offshore Wind, India, region EA</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -3968,25 +3968,473 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>RNWWOFINDNE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region NE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>WOFINDNE</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Offshore Wind, India, region NE</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RNWWOFINDNO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region NO</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>WOFINDNO</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Offshore Wind, India, region NO</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RNWWOFINDSO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region SO</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>WOFINDSO</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Offshore Wind, India, region SO</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RNWWOFINDWE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) India, region WE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>WOFINDWE</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Offshore Wind, India, region WE</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RNWWOFLKAXX</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>WOFLKAXX</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Offshore Wind, Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RNWWOFMDVXX</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>WOFMDVXX</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Offshore Wind, Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RNWWOFNPLXX</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>WOFNPLXX</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Offshore Wind, Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RNWWONBGDXX</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>WONBGDXX</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Onshore Wind, Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RNWWONBTNXX</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Bhutan, region XX</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>WONBTNXX</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Onshore Wind, Bhutan, region XX</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RNWWONINDEA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region EA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>WONINDEA</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Onshore Wind, India, region EA</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RNWWONINDNE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region NE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>WONINDNE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Onshore Wind, India, region NE</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RNWWONINDNO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region NO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>WONINDNO</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Onshore Wind, India, region NO</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RNWWONINDSO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region SO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>WONINDSO</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Onshore Wind, India, region SO</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RNWWONINDWE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) India, region WE</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>WONINDWE</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Onshore Wind, India, region WE</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RNWWONLKAXX</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>WONLKAXX</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Onshore Wind, Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RNWWONMDVXX</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Mining non-tradable (renewable) commodity) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>WONMDVXX</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Onshore Wind, Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>RNWWONNPLXX</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Onshore Wind (Mining non-tradable (renewable) commodity) Nepal, region XX</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>WONNPLXX</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>Onshore Wind, Nepal, region XX</t>
         </is>
       </c>
-      <c r="F124" t="n">
+      <c r="F140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4002,7 +4450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K241"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -8552,12 +9000,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OTHNPL</t>
+          <t>OTHMDV</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Other, Nepal</t>
+          <t>Other, Maldives</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -8566,22 +9014,22 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PWROTHNPLXX</t>
+          <t>PWROTHMDVXX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Other (Power generator) Nepal, region XX</t>
+          <t>Other (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ELCNPLXX01</t>
+          <t>ELCMDVXX01</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -8609,22 +9057,22 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PWROTHNPLXX</t>
+          <t>PWROTHMDVXX</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Other (Power generator) Nepal, region XX</t>
+          <t>Other (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ELCNPLXX01</t>
+          <t>ELCMDVXX01</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -8638,12 +9086,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PETBGD</t>
+          <t>OTHNPL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Petroleum, Bangladesh</t>
+          <t>Other, Nepal</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -8652,22 +9100,22 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PWRPETBGDXX</t>
+          <t>PWROTHNPLXX</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Bangladesh, region XX</t>
+          <t>Other (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ELCBGDXX01</t>
+          <t>ELCNPLXX01</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -8681,12 +9129,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PETINT</t>
+          <t>OTHINT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Petroleum, International Markets</t>
+          <t>Other, International Markets</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -8695,22 +9143,22 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>PWRPETBGDXX</t>
+          <t>PWROTHNPLXX</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Bangladesh, region XX</t>
+          <t>Other (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ELCBGDXX01</t>
+          <t>ELCNPLXX01</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -8724,12 +9172,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PETBTN</t>
+          <t>PETBGD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Petroleum, Bhutan</t>
+          <t>Petroleum, Bangladesh</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -8738,22 +9186,22 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>PWRPETBTNXX</t>
+          <t>PWRPETBGDXX</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Bhutan, region XX</t>
+          <t>Petroleum (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ELCBTNXX01</t>
+          <t>ELCBGDXX01</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -8781,22 +9229,22 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PWRPETBTNXX</t>
+          <t>PWRPETBGDXX</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Bhutan, region XX</t>
+          <t>Petroleum (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ELCBTNXX01</t>
+          <t>ELCBGDXX01</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -8810,12 +9258,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PETIND</t>
+          <t>PETBTN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Petroleum, India</t>
+          <t>Petroleum, Bhutan</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -8824,22 +9272,22 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PWRPETINDEA</t>
+          <t>PWRPETBTNXX</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region EA</t>
+          <t>Petroleum (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ELCINDEA01</t>
+          <t>ELCBTNXX01</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, NO renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -8867,22 +9315,22 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PWRPETINDEA</t>
+          <t>PWRPETBTNXX</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region EA</t>
+          <t>Petroleum (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ELCINDEA01</t>
+          <t>ELCBTNXX01</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, NO renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -8910,22 +9358,22 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PWRPETINDNE</t>
+          <t>PWRPETINDEA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region NE</t>
+          <t>Petroleum (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ELCINDNE01</t>
+          <t>ELCINDEA01</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, NO renewable power plant output</t>
+          <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -8953,22 +9401,22 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PWRPETINDNE</t>
+          <t>PWRPETINDEA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region NE</t>
+          <t>Petroleum (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ELCINDNE01</t>
+          <t>ELCINDEA01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, NO renewable power plant output</t>
+          <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -8996,22 +9444,22 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PWRPETINDNO</t>
+          <t>PWRPETINDNE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region NO</t>
+          <t>Petroleum (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ELCINDNO01</t>
+          <t>ELCINDNE01</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, NO renewable power plant output</t>
+          <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -9039,22 +9487,22 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PWRPETINDNO</t>
+          <t>PWRPETINDNE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region NO</t>
+          <t>Petroleum (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ELCINDNO01</t>
+          <t>ELCINDNE01</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, NO renewable power plant output</t>
+          <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -9082,22 +9530,22 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PWRPETINDSO</t>
+          <t>PWRPETINDNO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region SO</t>
+          <t>Petroleum (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ELCINDSO01</t>
+          <t>ELCINDNO01</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, NO renewable power plant output</t>
+          <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -9125,22 +9573,22 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PWRPETINDSO</t>
+          <t>PWRPETINDNO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region SO</t>
+          <t>Petroleum (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ELCINDSO01</t>
+          <t>ELCINDNO01</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, NO renewable power plant output</t>
+          <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -9168,22 +9616,22 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PWRPETINDWE</t>
+          <t>PWRPETINDSO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region WE</t>
+          <t>Petroleum (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ELCINDWE01</t>
+          <t>ELCINDSO01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, NO renewable power plant output</t>
+          <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -9211,22 +9659,22 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PWRPETINDWE</t>
+          <t>PWRPETINDSO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) India, region WE</t>
+          <t>Petroleum (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ELCINDWE01</t>
+          <t>ELCINDSO01</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, NO renewable power plant output</t>
+          <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -9240,12 +9688,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PETLKA</t>
+          <t>PETIND</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Petroleum, Sri Lanka</t>
+          <t>Petroleum, India</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -9254,22 +9702,22 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PWRPETLKAXX</t>
+          <t>PWRPETINDWE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Sri Lanka, region XX</t>
+          <t>Petroleum (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ELCLKAXX01</t>
+          <t>ELCINDWE01</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -9297,22 +9745,22 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PWRPETLKAXX</t>
+          <t>PWRPETINDWE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Sri Lanka, region XX</t>
+          <t>Petroleum (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ELCLKAXX01</t>
+          <t>ELCINDWE01</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -9326,12 +9774,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PETNPL</t>
+          <t>PETLKA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Petroleum, Nepal</t>
+          <t>Petroleum, Sri Lanka</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -9340,22 +9788,22 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PWRPETNPLXX</t>
+          <t>PWRPETLKAXX</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Nepal, region XX</t>
+          <t>Petroleum (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ELCNPLXX01</t>
+          <t>ELCLKAXX01</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -9383,22 +9831,22 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PWRPETNPLXX</t>
+          <t>PWRPETLKAXX</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Petroleum (Power generator) Nepal, region XX</t>
+          <t>Petroleum (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ELCNPLXX01</t>
+          <t>ELCLKAXX01</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -9412,12 +9860,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SPVBGDXX</t>
+          <t>PETMDV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Bangladesh, region XX</t>
+          <t>Petroleum, Maldives</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -9426,22 +9874,22 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PWRSPVBGDXX</t>
+          <t>PWRPETMDVXX</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) Bangladesh, region XX</t>
+          <t>Petroleum (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCMDVXX01</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -9451,16 +9899,16 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SPVBTNXX</t>
+          <t>PETINT</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Bhutan, region XX</t>
+          <t>Petroleum, International Markets</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -9469,22 +9917,22 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PWRSPVBTNXX</t>
+          <t>PWRPETMDVXX</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) Bhutan, region XX</t>
+          <t>Petroleum (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCMDVXX01</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -9498,12 +9946,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SPVINDEA</t>
+          <t>PETNPL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region EA</t>
+          <t>Petroleum, Nepal</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -9512,22 +9960,22 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PWRSPVINDEA</t>
+          <t>PWRPETNPLXX</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) India, region EA</t>
+          <t>Petroleum (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCNPLXX01</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -9537,16 +9985,16 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SPVINDNE</t>
+          <t>PETINT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region NE</t>
+          <t>Petroleum, International Markets</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -9555,22 +10003,22 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PWRSPVINDNE</t>
+          <t>PWRPETNPLXX</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) India, region NE</t>
+          <t>Petroleum (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCNPLXX01</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -9584,12 +10032,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SPVINDNO</t>
+          <t>SPVBGDXX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region NO</t>
+          <t>Solar Photovoltaic, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -9598,22 +10046,22 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PWRSPVINDNO</t>
+          <t>PWRSPVBGDXX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) India, region NO</t>
+          <t>Solar Photovoltaic (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -9627,12 +10075,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPVINDSO</t>
+          <t>SPVBTNXX</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region SO</t>
+          <t>Solar Photovoltaic, Bhutan, region XX</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -9641,22 +10089,22 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PWRSPVINDSO</t>
+          <t>PWRSPVBTNXX</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) India, region SO</t>
+          <t>Solar Photovoltaic (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -9670,12 +10118,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SPVINDWE</t>
+          <t>SPVINDEA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, India, region WE</t>
+          <t>Solar Photovoltaic, India, region EA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -9684,22 +10132,22 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PWRSPVINDWE</t>
+          <t>PWRSPVINDEA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) India, region WE</t>
+          <t>Solar Photovoltaic (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -9713,12 +10161,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SPVLKAXX</t>
+          <t>SPVINDNE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Sri Lanka, region XX</t>
+          <t>Solar Photovoltaic, India, region NE</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -9727,22 +10175,22 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PWRSPVLKAXX</t>
+          <t>PWRSPVINDNE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) Sri Lanka, region XX</t>
+          <t>Solar Photovoltaic (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -9756,12 +10204,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SPVNPLXX</t>
+          <t>SPVINDNO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic, Nepal, region XX</t>
+          <t>Solar Photovoltaic, India, region NO</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -9770,22 +10218,22 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PWRSPVNPLXX</t>
+          <t>PWRSPVINDNO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Solar Photovoltaic (Power generator) Nepal, region XX</t>
+          <t>Solar Photovoltaic (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -9799,12 +10247,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>URNBGD</t>
+          <t>SPVINDSO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nuclear, Bangladesh</t>
+          <t>Solar Photovoltaic, India, region SO</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -9813,22 +10261,22 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PWRURNBGDXX</t>
+          <t>PWRSPVINDSO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) Bangladesh, region XX</t>
+          <t>Solar Photovoltaic (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ELCBGDXX01</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -9838,16 +10286,16 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>SPVINDWE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Solar Photovoltaic, India, region WE</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -9856,22 +10304,22 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PWRURNBGDXX</t>
+          <t>PWRSPVINDWE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) Bangladesh, region XX</t>
+          <t>Solar Photovoltaic (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ELCBGDXX01</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -9885,12 +10333,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>SPVLKAXX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Solar Photovoltaic, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -9899,22 +10347,22 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PWRURNINDEA</t>
+          <t>PWRSPVLKAXX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region EA</t>
+          <t>Solar Photovoltaic (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>ELCINDEA01</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, NO renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -9924,16 +10372,16 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>SPVMDVXX</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Solar Photovoltaic, Maldives, region XX</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -9942,22 +10390,22 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PWRURNINDEA</t>
+          <t>PWRSPVMDVXX</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region EA</t>
+          <t>Solar Photovoltaic (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ELCINDEA01</t>
+          <t>ELCMDVXX00</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, NO renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -9971,12 +10419,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>SPVNPLXX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Solar Photovoltaic, Nepal, region XX</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -9985,22 +10433,22 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PWRURNINDNE</t>
+          <t>PWRSPVNPLXX</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region NE</t>
+          <t>Solar Photovoltaic (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ELCINDNE01</t>
+          <t>ELCNPLXX00</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, NO renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -10010,16 +10458,16 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>URNBGD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Nuclear, Bangladesh</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -10028,22 +10476,22 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PWRURNINDNE</t>
+          <t>PWRURNBGDXX</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region NE</t>
+          <t>Nuclear (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ELCINDNE01</t>
+          <t>ELCBGDXX01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, NO renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -10053,16 +10501,16 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -10071,22 +10519,22 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>PWRURNINDNO</t>
+          <t>PWRURNBGDXX</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region NO</t>
+          <t>Nuclear (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ELCINDNO01</t>
+          <t>ELCBGDXX01</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, NO renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -10096,16 +10544,16 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -10114,22 +10562,22 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PWRURNINDNO</t>
+          <t>PWRURNINDEA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region NO</t>
+          <t>Nuclear (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ELCINDNO01</t>
+          <t>ELCINDEA01</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, NO renewable power plant output</t>
+          <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -10139,16 +10587,16 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -10157,22 +10605,22 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PWRURNINDSO</t>
+          <t>PWRURNINDEA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region SO</t>
+          <t>Nuclear (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ELCINDSO01</t>
+          <t>ELCINDEA01</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, NO renewable power plant output</t>
+          <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -10182,16 +10630,16 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -10200,22 +10648,22 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PWRURNINDSO</t>
+          <t>PWRURNINDNE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region SO</t>
+          <t>Nuclear (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ELCINDSO01</t>
+          <t>ELCINDNE01</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, NO renewable power plant output</t>
+          <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -10225,16 +10673,16 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>URNIND</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Nuclear, India</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -10243,22 +10691,22 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>PWRURNINDWE</t>
+          <t>PWRURNINDNE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region WE</t>
+          <t>Nuclear (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ELCINDWE01</t>
+          <t>ELCINDNE01</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, NO renewable power plant output</t>
+          <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -10268,16 +10716,16 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>URNINT</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nuclear, International Markets</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -10286,22 +10734,22 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PWRURNINDWE</t>
+          <t>PWRURNINDNO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nuclear (Power generator) India, region WE</t>
+          <t>Nuclear (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ELCINDWE01</t>
+          <t>ELCINDNO01</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, NO renewable power plant output</t>
+          <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -10311,16 +10759,16 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>WASBGDXX</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Waste, Bangladesh, region XX</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -10329,22 +10777,22 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>PWRWASBGDXX</t>
+          <t>PWRURNINDNO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Waste (Power generator) Bangladesh, region XX</t>
+          <t>Nuclear (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCINDNO01</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -10358,12 +10806,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>WASINDEA</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Waste, India, region EA</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -10372,22 +10820,22 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PWRWASINDEA</t>
+          <t>PWRURNINDSO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Waste (Power generator) India, region EA</t>
+          <t>Nuclear (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCINDSO01</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -10397,16 +10845,16 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WASINDNE</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Waste, India, region NE</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -10415,22 +10863,22 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>PWRWASINDNE</t>
+          <t>PWRURNINDSO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Waste (Power generator) India, region NE</t>
+          <t>Nuclear (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDSO01</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -10444,12 +10892,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WASINDNO</t>
+          <t>URNIND</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Waste, India, region NO</t>
+          <t>Nuclear, India</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -10458,22 +10906,22 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>PWRWASINDNO</t>
+          <t>PWRURNINDWE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Waste (Power generator) India, region NO</t>
+          <t>Nuclear (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDWE01</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -10483,16 +10931,16 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>WASINDSO</t>
+          <t>URNINT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Waste, India, region SO</t>
+          <t>Nuclear, International Markets</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -10501,22 +10949,22 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>PWRWASINDSO</t>
+          <t>PWRURNINDWE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Waste (Power generator) India, region SO</t>
+          <t>Nuclear (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCINDWE01</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -10530,12 +10978,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>WASINDWE</t>
+          <t>WASBGDXX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Waste, India, region WE</t>
+          <t>Waste, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -10544,22 +10992,22 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PWRWASINDWE</t>
+          <t>PWRWASBGDXX</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Waste (Power generator) India, region WE</t>
+          <t>Waste (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -10573,12 +11021,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>WASLKAXX</t>
+          <t>WASINDEA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Waste, Sri Lanka, region XX</t>
+          <t>Waste, India, region EA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -10587,22 +11035,22 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>PWRWASLKAXX</t>
+          <t>PWRWASINDEA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Waste (Power generator) Sri Lanka, region XX</t>
+          <t>Waste (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -10616,12 +11064,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>WASNPLXX</t>
+          <t>WASINDNE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Waste, Nepal, region XX</t>
+          <t>Waste, India, region NE</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -10630,22 +11078,22 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>PWRWASNPLXX</t>
+          <t>PWRWASINDNE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Waste (Power generator) Nepal, region XX</t>
+          <t>Waste (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -10659,12 +11107,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>WOFBGDXX</t>
+          <t>WASINDNO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Offshore Wind, Bangladesh, region XX</t>
+          <t>Waste, India, region NO</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -10673,22 +11121,22 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>PWRWOFBGDXX</t>
+          <t>PWRWASINDNO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) Bangladesh, region XX</t>
+          <t>Waste (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -10702,12 +11150,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>WOFINDEA</t>
+          <t>WASINDSO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region EA</t>
+          <t>Waste, India, region SO</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -10716,22 +11164,22 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>PWRWOFINDEA</t>
+          <t>PWRWASINDSO</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) India, region EA</t>
+          <t>Waste (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -10745,12 +11193,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>WOFINDNE</t>
+          <t>WASINDWE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region NE</t>
+          <t>Waste, India, region WE</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -10759,22 +11207,22 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>PWRWOFINDNE</t>
+          <t>PWRWASINDWE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) India, region NE</t>
+          <t>Waste (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -10788,12 +11236,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>WOFINDNO</t>
+          <t>WASLKAXX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region NO</t>
+          <t>Waste, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -10802,22 +11250,22 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>PWRWOFINDNO</t>
+          <t>PWRWASLKAXX</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) India, region NO</t>
+          <t>Waste (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -10831,12 +11279,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>WOFINDSO</t>
+          <t>WASNPLXX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region SO</t>
+          <t>Waste, Nepal, region XX</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -10845,22 +11293,22 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PWRWOFINDSO</t>
+          <t>PWRWASNPLXX</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) India, region SO</t>
+          <t>Waste (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCNPLXX00</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -10874,12 +11322,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>WOFINDWE</t>
+          <t>WOFBGDXX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Offshore Wind, India, region WE</t>
+          <t>Offshore Wind, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -10888,22 +11336,22 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>PWRWOFINDWE</t>
+          <t>PWRWOFBGDXX</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) India, region WE</t>
+          <t>Offshore Wind (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -10917,12 +11365,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>WOFLKAXX</t>
+          <t>WOFINDEA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Offshore Wind, Sri Lanka, region XX</t>
+          <t>Offshore Wind, India, region EA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -10931,22 +11379,22 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>PWRWOFLKAXX</t>
+          <t>PWRWOFINDEA</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Offshore Wind (Power generator) Sri Lanka, region XX</t>
+          <t>Offshore Wind (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -10960,12 +11408,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>WONBGDXX</t>
+          <t>WOFINDNE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Onshore Wind, Bangladesh, region XX</t>
+          <t>Offshore Wind, India, region NE</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -10974,22 +11422,22 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>PWRWONBGDXX</t>
+          <t>PWRWOFINDNE</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) Bangladesh, region XX</t>
+          <t>Offshore Wind (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -11003,12 +11451,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>WONBTNXX</t>
+          <t>WOFINDNO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Onshore Wind, Bhutan, region XX</t>
+          <t>Offshore Wind, India, region NO</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -11017,22 +11465,22 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PWRWONBTNXX</t>
+          <t>PWRWOFINDNO</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) Bhutan, region XX</t>
+          <t>Offshore Wind (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -11046,12 +11494,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>WONINDEA</t>
+          <t>WOFINDSO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region EA</t>
+          <t>Offshore Wind, India, region SO</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -11060,22 +11508,22 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>PWRWONINDEA</t>
+          <t>PWRWOFINDSO</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) India, region EA</t>
+          <t>Offshore Wind (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -11089,12 +11537,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WONINDNE</t>
+          <t>WOFINDWE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region NE</t>
+          <t>Offshore Wind, India, region WE</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -11103,22 +11551,22 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PWRWONINDNE</t>
+          <t>PWRWOFINDWE</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) India, region NE</t>
+          <t>Offshore Wind (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -11132,12 +11580,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WONINDNO</t>
+          <t>WOFLKAXX</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region NO</t>
+          <t>Offshore Wind, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -11146,22 +11594,22 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PWRWONINDNO</t>
+          <t>PWRWOFLKAXX</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) India, region NO</t>
+          <t>Offshore Wind (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -11175,12 +11623,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WONINDSO</t>
+          <t>WONBGDXX</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region SO</t>
+          <t>Onshore Wind, Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -11189,22 +11637,22 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PWRWONINDSO</t>
+          <t>PWRWONBGDXX</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) India, region SO</t>
+          <t>Onshore Wind (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -11218,12 +11666,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>WONINDWE</t>
+          <t>WONBTNXX</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Onshore Wind, India, region WE</t>
+          <t>Onshore Wind, Bhutan, region XX</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -11232,22 +11680,22 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PWRWONINDWE</t>
+          <t>PWRWONBTNXX</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) India, region WE</t>
+          <t>Onshore Wind (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -11261,12 +11709,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WONLKAXX</t>
+          <t>WONINDEA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Onshore Wind, Sri Lanka, region XX</t>
+          <t>Onshore Wind, India, region EA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -11275,22 +11723,22 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>PWRWONLKAXX</t>
+          <t>PWRWONINDEA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) Sri Lanka, region XX</t>
+          <t>Onshore Wind (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -11304,12 +11752,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WONNPLXX</t>
+          <t>WONINDNE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Onshore Wind, Nepal, region XX</t>
+          <t>Onshore Wind, India, region NE</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -11318,22 +11766,22 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>PWRWONNPLXX</t>
+          <t>PWRWONINDNE</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Onshore Wind (Power generator) Nepal, region XX</t>
+          <t>Onshore Wind (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -11347,12 +11795,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ELCBGDXX03</t>
+          <t>WONINDNO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
+          <t>Onshore Wind, India, region NO</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -11361,22 +11809,22 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>TRNBGDXXINDEA</t>
+          <t>PWRWONINDNO</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bangladesh, region XX to India, region EA</t>
+          <t>Onshore Wind (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -11386,16 +11834,16 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ELCINDEA03</t>
+          <t>WONINDSO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
+          <t>Onshore Wind, India, region SO</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -11404,22 +11852,22 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>TRNBGDXXINDEA</t>
+          <t>PWRWONINDSO</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bangladesh, region XX to India, region EA</t>
+          <t>Onshore Wind (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ELCBGDXX04</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, region XX, power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -11433,12 +11881,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ELCBGDXX03</t>
+          <t>WONINDWE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
+          <t>Onshore Wind, India, region WE</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -11447,22 +11895,22 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>TRNBGDXXINDNE</t>
+          <t>PWRWONINDWE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bangladesh, region XX to India, region NE</t>
+          <t>Onshore Wind (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>ELCINDNE04</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -11472,16 +11920,16 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ELCINDNE03</t>
+          <t>WONLKAXX</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
+          <t>Onshore Wind, Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -11490,22 +11938,22 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>TRNBGDXXINDNE</t>
+          <t>PWRWONLKAXX</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bangladesh, region XX to India, region NE</t>
+          <t>Onshore Wind (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ELCBGDXX04</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, region XX, power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -11519,12 +11967,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ELCBTNXX03</t>
+          <t>WONNPLXX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
+          <t>Onshore Wind, Nepal, region XX</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -11533,22 +11981,22 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TRNBTNXXINDEA</t>
+          <t>PWRWONNPLXX</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bhutan, region XX to India, region EA</t>
+          <t>Onshore Wind (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCNPLXX00</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -11558,16 +12006,16 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ELCINDEA03</t>
+          <t>ELCBGDXX03</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
+          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -11576,22 +12024,22 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TRNBTNXXINDEA</t>
+          <t>TRNBGDXXINDEA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Transmission interconnection from Bhutan, region XX to India, region EA</t>
+          <t>Transmission interconnection from Bangladesh, region XX to India, region EA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>ELCBTNXX04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, region XX, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -11601,7 +12049,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -11619,22 +12067,22 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TRNINDEAINDNE</t>
+          <t>TRNBGDXXINDEA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region NE</t>
+          <t>Transmission interconnection from Bangladesh, region XX to India, region EA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ELCINDNE04</t>
+          <t>ELCBGDXX04</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, power plant output</t>
+          <t>Electricity, Bangladesh, region XX, power plant output</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -11644,16 +12092,16 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ELCINDNE03</t>
+          <t>ELCBGDXX03</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
+          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -11662,22 +12110,22 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TRNINDEAINDNE</t>
+          <t>TRNBGDXXINDNE</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region NE</t>
+          <t>Transmission interconnection from Bangladesh, region XX to India, region NE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCINDNE04</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, India, region NE, power plant output</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -11687,16 +12135,16 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ELCINDEA03</t>
+          <t>ELCINDNE03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -11705,22 +12153,22 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TRNINDEAINDNO</t>
+          <t>TRNBGDXXINDNE</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region NO</t>
+          <t>Transmission interconnection from Bangladesh, region XX to India, region NE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ELCINDNO04</t>
+          <t>ELCBGDXX04</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, power plant output</t>
+          <t>Electricity, Bangladesh, region XX, power plant output</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -11730,16 +12178,16 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ELCINDNO03</t>
+          <t>ELCBTNXX03</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
+          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -11748,12 +12196,12 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TRNINDEAINDNO</t>
+          <t>TRNBTNXXINDEA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region NO</t>
+          <t>Transmission interconnection from Bhutan, region XX to India, region EA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11773,7 +12221,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -11791,22 +12239,22 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>TRNINDEAINDSO</t>
+          <t>TRNBTNXXINDEA</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region SO</t>
+          <t>Transmission interconnection from Bhutan, region XX to India, region EA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>ELCINDSO04</t>
+          <t>ELCBTNXX04</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, power plant output</t>
+          <t>Electricity, Bhutan, region XX, power plant output</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -11816,16 +12264,16 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ELCINDSO03</t>
+          <t>ELCINDEA03</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -11834,22 +12282,22 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>TRNINDEAINDSO</t>
+          <t>TRNINDEAINDNE</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region SO</t>
+          <t>Transmission interconnection from India, region EA to India, region NE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCINDNE04</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, India, region NE, power plant output</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -11859,16 +12307,16 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ELCINDEA03</t>
+          <t>ELCINDNE03</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -11877,22 +12325,22 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TRNINDEAINDWE</t>
+          <t>TRNINDEAINDNE</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region WE</t>
+          <t>Transmission interconnection from India, region EA to India, region NE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ELCINDWE04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -11902,16 +12350,16 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ELCINDWE03</t>
+          <t>ELCINDEA03</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -11920,22 +12368,22 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>TRNINDEAINDWE</t>
+          <t>TRNINDEAINDNO</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to India, region WE</t>
+          <t>Transmission interconnection from India, region EA to India, region NO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCINDNO04</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, India, region NO, power plant output</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -11945,16 +12393,16 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ELCINDEA03</t>
+          <t>ELCINDNO03</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -11963,22 +12411,22 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>TRNINDEANPLXX</t>
+          <t>TRNINDEAINDNO</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to Nepal, region XX</t>
+          <t>Transmission interconnection from India, region EA to India, region NO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>ELCNPLXX04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, region XX, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -11988,16 +12436,16 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ELCNPLXX03</t>
+          <t>ELCINDEA03</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -12006,22 +12454,22 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>TRNINDEANPLXX</t>
+          <t>TRNINDEAINDSO</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region EA to Nepal, region XX</t>
+          <t>Transmission interconnection from India, region EA to India, region SO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ELCINDEA04</t>
+          <t>ELCINDSO04</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Electricity, India, region EA, power plant output</t>
+          <t>Electricity, India, region SO, power plant output</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -12031,16 +12479,16 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ELCINDNE03</t>
+          <t>ELCINDSO03</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -12049,22 +12497,22 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>TRNINDNEINDNO</t>
+          <t>TRNINDEAINDSO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NE to India, region NO</t>
+          <t>Transmission interconnection from India, region EA to India, region SO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>ELCINDNO04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -12074,16 +12522,16 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ELCINDNO03</t>
+          <t>ELCINDEA03</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -12092,22 +12540,22 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>TRNINDNEINDNO</t>
+          <t>TRNINDEAINDWE</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NE to India, region NO</t>
+          <t>Transmission interconnection from India, region EA to India, region WE</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ELCINDNE04</t>
+          <t>ELCINDWE04</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Electricity, India, region NE, power plant output</t>
+          <t>Electricity, India, region WE, power plant output</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -12117,16 +12565,16 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ELCINDNO03</t>
+          <t>ELCINDWE03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -12135,22 +12583,22 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TRNINDNOINDWE</t>
+          <t>TRNINDEAINDWE</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NO to India, region WE</t>
+          <t>Transmission interconnection from India, region EA to India, region WE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>ELCINDWE04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -12160,16 +12608,16 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ELCINDWE03</t>
+          <t>ELCINDEA03</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region EA, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -12178,22 +12626,22 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TRNINDNOINDWE</t>
+          <t>TRNINDEANPLXX</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NO to India, region WE</t>
+          <t>Transmission interconnection from India, region EA to Nepal, region XX</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ELCINDNO04</t>
+          <t>ELCNPLXX04</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, power plant output</t>
+          <t>Electricity, Nepal, region XX, power plant output</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -12203,16 +12651,16 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ELCINDNO03</t>
+          <t>ELCNPLXX03</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
+          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -12221,22 +12669,22 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>TRNINDNONPLXX</t>
+          <t>TRNINDEANPLXX</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NO to Nepal, region XX</t>
+          <t>Transmission interconnection from India, region EA to Nepal, region XX</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>ELCNPLXX04</t>
+          <t>ELCINDEA04</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, region XX, power plant output</t>
+          <t>Electricity, India, region EA, power plant output</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -12246,16 +12694,16 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ELCNPLXX03</t>
+          <t>ELCINDNE03</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -12264,12 +12712,12 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>TRNINDNONPLXX</t>
+          <t>TRNINDNEINDNO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region NO to Nepal, region XX</t>
+          <t>Transmission interconnection from India, region NE to India, region NO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12289,16 +12737,16 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ELCINDSO03</t>
+          <t>ELCINDNO03</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -12307,22 +12755,22 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>TRNINDSOINDWE</t>
+          <t>TRNINDNEINDNO</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region SO to India, region WE</t>
+          <t>Transmission interconnection from India, region NE to India, region NO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>ELCINDWE04</t>
+          <t>ELCINDNE04</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, power plant output</t>
+          <t>Electricity, India, region NE, power plant output</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -12332,16 +12780,16 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ELCINDWE03</t>
+          <t>ELCINDNO03</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -12350,22 +12798,22 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>TRNINDSOINDWE</t>
+          <t>TRNINDNOINDWE</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region SO to India, region WE</t>
+          <t>Transmission interconnection from India, region NO to India, region WE</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>ELCINDSO04</t>
+          <t>ELCINDWE04</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, power plant output</t>
+          <t>Electricity, India, region WE, power plant output</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -12375,16 +12823,16 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ELCINDSO03</t>
+          <t>ELCINDWE03</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -12393,22 +12841,22 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>TRNINDSOLKAXX</t>
+          <t>TRNINDNOINDWE</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region SO to Sri Lanka, region XX</t>
+          <t>Transmission interconnection from India, region NO to India, region WE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ELCLKAXX04</t>
+          <t>ELCINDNO04</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, region XX, power plant output</t>
+          <t>Electricity, India, region NO, power plant output</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -12418,16 +12866,16 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ELCLKAXX03</t>
+          <t>ELCINDNO03</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, region XX, dispatch-ready for interconnection</t>
+          <t>Electricity, India, region NO, dispatch-ready for interconnection</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -12436,22 +12884,22 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>TRNINDSOLKAXX</t>
+          <t>TRNINDNONPLXX</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Transmission interconnection from India, region SO to Sri Lanka, region XX</t>
+          <t>Transmission interconnection from India, region NO to Nepal, region XX</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>ELCINDSO04</t>
+          <t>ELCNPLXX04</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Electricity, India, region SO, power plant output</t>
+          <t>Electricity, Nepal, region XX, power plant output</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -12461,30 +12909,40 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1</v>
-      </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ELCNPLXX03</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>PWRBCKBGDXX</t>
+          <t>TRNINDNONPLXX</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) Bangladesh, region XX</t>
+          <t>Transmission interconnection from India, region NO to Nepal, region XX</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>ELCBGDXX01</t>
+          <t>ELCINDNO04</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, region NO, power plant output</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -12496,28 +12954,38 @@
       <c r="A198" t="n">
         <v>1</v>
       </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ELCINDSO03</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>PWRBCKBTNXX</t>
+          <t>TRNINDSOINDWE</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) Bhutan, region XX</t>
+          <t>Transmission interconnection from India, region SO to India, region WE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>ELCBTNXX01</t>
+          <t>ELCINDWE04</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
+          <t>Electricity, India, region WE, power plant output</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -12527,30 +12995,40 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1</v>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ELCINDWE03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Electricity, India, region WE, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>PWRBCKINDEA</t>
+          <t>TRNINDSOINDWE</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) India, region EA</t>
+          <t>Transmission interconnection from India, region SO to India, region WE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>ELCINDEA01</t>
+          <t>ELCINDSO04</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, NO renewable power plant output</t>
+          <t>Electricity, India, region SO, power plant output</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -12562,28 +13040,38 @@
       <c r="A200" t="n">
         <v>1</v>
       </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ELCINDSO03</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>PWRBCKINDNE</t>
+          <t>TRNINDSOLKAXX</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) India, region NE</t>
+          <t>Transmission interconnection from India, region SO to Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>ELCINDNE01</t>
+          <t>ELCLKAXX04</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, NO renewable power plant output</t>
+          <t>Electricity, Sri Lanka, region XX, power plant output</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -12593,30 +13081,40 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1</v>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ELCLKAXX03</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>PWRBCKINDNO</t>
+          <t>TRNINDSOLKAXX</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) India, region NO</t>
+          <t>Transmission interconnection from India, region SO to Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>ELCINDNO01</t>
+          <t>ELCINDSO04</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, NO renewable power plant output</t>
+          <t>Electricity, India, region SO, power plant output</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -12628,28 +13126,38 @@
       <c r="A202" t="n">
         <v>1</v>
       </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ELCLKAXX03</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>PWRBCKINDSO</t>
+          <t>TRNLKAXXMDVXX</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) India, region SO</t>
+          <t>Transmission interconnection from Sri Lanka, region XX to Maldives, region XX</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>ELCINDSO01</t>
+          <t>ELCMDVXX04</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, NO renewable power plant output</t>
+          <t>Electricity, Maldives, region XX, power plant output</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -12659,30 +13167,40 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1</v>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ELCMDVXX03</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>PWRBCKINDWE</t>
+          <t>TRNLKAXXMDVXX</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) India, region WE</t>
+          <t>Transmission interconnection from Sri Lanka, region XX to Maldives, region XX</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>ELCINDWE01</t>
+          <t>ELCLKAXX04</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, NO renewable power plant output</t>
+          <t>Electricity, Sri Lanka, region XX, power plant output</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -12700,22 +13218,22 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>PWRBCKLKAXX</t>
+          <t>PWRBCKBGDXX</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) Sri Lanka, region XX</t>
+          <t>Backstop (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>ELCLKAXX01</t>
+          <t>ELCBGDXX01</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -12733,22 +13251,22 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>PWRBCKNPLXX</t>
+          <t>PWRBCKBTNXX</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Backstop (Power generator) Nepal, region XX</t>
+          <t>Backstop (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>ELCNPLXX01</t>
+          <t>ELCBTNXX01</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -12758,7 +13276,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr"/>
@@ -12766,22 +13284,22 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>PWRLDSBGDXX</t>
+          <t>PWRBCKINDEA</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Backstop (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCINDEA01</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region EA, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -12791,7 +13309,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr"/>
@@ -12799,22 +13317,22 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>PWRLDSBTNXX</t>
+          <t>PWRBCKINDNE</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Bhutan, region XX</t>
+          <t>Backstop (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCINDNE01</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region NE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -12824,7 +13342,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr"/>
@@ -12832,22 +13350,22 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>PWRLDSINDEA</t>
+          <t>PWRBCKINDNO</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region EA</t>
+          <t>Backstop (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCINDNO01</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, India, Region NO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -12857,7 +13375,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
@@ -12865,22 +13383,22 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PWRLDSINDNE</t>
+          <t>PWRBCKINDSO</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NE</t>
+          <t>Backstop (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDSO01</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region SO, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -12890,7 +13408,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
@@ -12898,22 +13416,22 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>PWRLDSINDNO</t>
+          <t>PWRBCKINDWE</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NO</t>
+          <t>Backstop (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDWE01</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region WE, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -12923,7 +13441,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr"/>
@@ -12931,22 +13449,22 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PWRLDSINDSO</t>
+          <t>PWRBCKLKAXX</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region SO</t>
+          <t>Backstop (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCLKAXX01</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -12956,7 +13474,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
@@ -12964,22 +13482,22 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>PWRLDSINDWE</t>
+          <t>PWRBCKMDVXX</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region WE</t>
+          <t>Backstop (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCMDVXX01</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -12989,7 +13507,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr"/>
@@ -12997,22 +13515,22 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>PWRLDSLKAXX</t>
+          <t>PWRBCKNPLXX</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Backstop (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCNPLXX01</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, Nepal, Region XX, NO renewable power plant output</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -13030,22 +13548,22 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSBGDXX</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -13063,22 +13581,22 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSBTNXX</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ELCBGDXX00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -13096,22 +13614,22 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRLDSINDEA</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -13129,22 +13647,22 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRLDSINDNE</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="J217" t="n">
@@ -13162,22 +13680,22 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRLDSINDNO</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -13195,22 +13713,22 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRLDSINDSO</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -13228,22 +13746,22 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRLDSINDWE</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="J220" t="n">
@@ -13261,22 +13779,22 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRLDSLKAXX</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -13294,22 +13812,22 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCMDVXX00</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -13327,12 +13845,12 @@
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PWRSDSNPLXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -13352,332 +13870,332 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>ELCBGDXX00</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>PWRLDSBGDXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>ELCBGDXX00</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>ELCBTNXX00</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>PWRLDSBTNXX</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Bhutan, region XX</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>ELCBTNXX00</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>ELCINDEA00</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>PWRLDSINDEA</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region EA</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
+          <t>Short duration storage (Power generator) India, region EA</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>ELCINDEA00</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>ELCINDNE00</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>PWRLDSINDNE</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NE</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
+          <t>Short duration storage (Power generator) India, region NE</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>ELCINDNE00</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>ELCINDNO00</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>PWRLDSINDNO</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region NO</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
+          <t>Short duration storage (Power generator) India, region NO</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>ELCINDNO00</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>ELCINDSO00</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>PWRLDSINDSO</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region SO</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+          <t>Short duration storage (Power generator) India, region SO</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>ELCINDSO00</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>ELCINDWE00</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PWRLDSINDWE</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) India, region WE</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
+          <t>Short duration storage (Power generator) India, region WE</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>ELCINDWE00</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>ELCLKAXX00</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>PWRLDSLKAXX</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>ELCLKAXX00</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>ELCNPLXX00</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRSDSMDVXX</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>ELCBGDXX00</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRSDSNPLXX</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>ELCNPLXX00</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -13686,12 +14204,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ELCBTNXX00</t>
+          <t>ELCBGDXX00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -13700,12 +14218,12 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRLDSBGDXX</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
@@ -13719,12 +14237,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ELCINDEA00</t>
+          <t>ELCBTNXX00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -13733,12 +14251,12 @@
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRLDSBTNXX</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -13752,12 +14270,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ELCINDNE00</t>
+          <t>ELCINDEA00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -13766,12 +14284,12 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRLDSINDEA</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -13785,12 +14303,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ELCINDNO00</t>
+          <t>ELCINDNE00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -13799,12 +14317,12 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRLDSINDNE</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
@@ -13818,12 +14336,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ELCINDSO00</t>
+          <t>ELCINDNO00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -13832,12 +14350,12 @@
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRLDSINDNO</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -13851,12 +14369,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ELCINDWE00</t>
+          <t>ELCINDSO00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -13865,12 +14383,12 @@
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRLDSINDSO</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -13884,12 +14402,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ELCLKAXX00</t>
+          <t>ELCINDWE00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -13898,12 +14416,12 @@
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRLDSINDWE</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -13917,12 +14435,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ELCNPLXX00</t>
+          <t>ELCLKAXX00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -13931,18 +14449,414 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>PWRSDSNPLXX</t>
+          <t>PWRLDSLKAXX</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>PWRLDSMDVXX</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ELCNPLXX00</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>PWRLDSNPLXX</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ELCBGDXX00</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>PWRSDSBGDXX</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ELCBTNXX00</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>PWRSDSBTNXX</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ELCINDEA00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>PWRSDSINDEA</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) India, region EA</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ELCINDNE00</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>PWRSDSINDNE</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) India, region NE</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ELCINDNO00</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>PWRSDSINDNO</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) India, region NO</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ELCINDSO00</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>PWRSDSINDSO</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) India, region SO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ELCINDWE00</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>PWRSDSINDWE</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) India, region WE</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ELCLKAXX00</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Electricity, Sri Lanka, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>PWRSDSLKAXX</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>1</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>1</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ELCNPLXX00</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, Region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>PWRSDSNPLXX</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -49,7 +49,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,18 +66,6 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCD5B4"/>
-        <bgColor rgb="FFFCD5B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9B59B6"/>
-        <bgColor rgb="FF9B59B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -143,8 +131,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4464,7 +4450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K277"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -4553,6 +4539,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PWRBIOBGDXX</t>
@@ -4576,6 +4563,7 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4594,6 +4582,7 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>PWRBIOINDEA</t>
@@ -4617,6 +4606,7 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4635,6 +4625,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>PWRBIOINDNE</t>
@@ -4658,6 +4649,7 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4676,6 +4668,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRBIOINDNO</t>
@@ -4699,6 +4692,7 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4717,6 +4711,7 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>PWRBIOINDSO</t>
@@ -4740,6 +4735,7 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4758,6 +4754,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>PWRBIOINDWE</t>
@@ -4781,6 +4778,7 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4799,6 +4797,7 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>PWRBIOLKAXX</t>
@@ -4822,6 +4821,7 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4840,6 +4840,7 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PWRBIONPLXX</t>
@@ -4863,6 +4864,7 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4881,6 +4883,7 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4904,6 +4907,7 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4922,6 +4926,7 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4945,6 +4950,7 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4963,6 +4969,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -4986,6 +4993,7 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5004,6 +5012,7 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -5027,6 +5036,7 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5045,6 +5055,7 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5068,6 +5079,7 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5086,6 +5098,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5109,6 +5122,7 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5127,6 +5141,7 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5150,6 +5165,7 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5168,6 +5184,7 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5191,6 +5208,7 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5209,6 +5227,7 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5232,6 +5251,7 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5250,6 +5270,7 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5273,6 +5294,7 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5291,6 +5313,7 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5314,6 +5337,7 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5332,6 +5356,7 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5355,6 +5380,7 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5373,6 +5399,7 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5396,6 +5423,7 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5414,6 +5442,7 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5437,6 +5466,7 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5455,6 +5485,7 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5478,6 +5509,7 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5496,6 +5528,7 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5519,6 +5552,7 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5537,6 +5571,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5560,6 +5595,7 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5578,6 +5614,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5601,6 +5638,7 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5619,6 +5657,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5642,6 +5681,7 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5660,6 +5700,7 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5683,6 +5724,7 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5701,6 +5743,7 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5724,6 +5767,7 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5742,6 +5786,7 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5765,6 +5810,7 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5783,6 +5829,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5806,6 +5853,7 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5824,6 +5872,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5847,6 +5896,7 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5865,6 +5915,7 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5888,6 +5939,7 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5906,6 +5958,7 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5929,6 +5982,7 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5947,6 +6001,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -5970,6 +6025,7 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5988,6 +6044,7 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -6011,6 +6068,7 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6029,6 +6087,7 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6052,6 +6111,7 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6070,6 +6130,7 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6093,6 +6154,7 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6111,6 +6173,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6134,6 +6197,7 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6152,6 +6216,7 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6175,6 +6240,7 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6193,6 +6259,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6216,6 +6283,7 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6234,6 +6302,7 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6257,6 +6326,7 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6275,6 +6345,7 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6298,6 +6369,7 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6316,6 +6388,7 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6339,6 +6412,7 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6357,6 +6431,7 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6380,6 +6455,7 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6398,6 +6474,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6421,6 +6498,7 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6439,6 +6517,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6462,6 +6541,7 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6480,6 +6560,7 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6503,6 +6584,7 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6521,6 +6603,7 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>PWRCSPINDEA</t>
@@ -6544,6 +6627,7 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6562,6 +6646,7 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>PWRCSPINDNE</t>
@@ -6585,6 +6670,7 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6603,6 +6689,7 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>PWRCSPINDNO</t>
@@ -6626,6 +6713,7 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6644,6 +6732,7 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRCSPINDSO</t>
@@ -6667,6 +6756,7 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6685,6 +6775,7 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>PWRCSPINDWE</t>
@@ -6708,6 +6799,7 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6726,6 +6818,7 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>PWRHYDBGDXX</t>
@@ -6749,6 +6842,7 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6767,6 +6861,7 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>PWRHYDBTNXX</t>
@@ -6790,6 +6885,7 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6808,6 +6904,7 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>PWRHYDINDEA</t>
@@ -6831,6 +6928,7 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6849,6 +6947,7 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>PWRHYDINDNE</t>
@@ -6872,6 +6971,7 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6890,6 +6990,7 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>PWRHYDINDNO</t>
@@ -6913,6 +7014,7 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6931,6 +7033,7 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>PWRHYDINDSO</t>
@@ -6954,6 +7057,7 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6972,6 +7076,7 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRHYDINDWE</t>
@@ -6995,6 +7100,7 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7013,6 +7119,7 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>PWRHYDLKAXX</t>
@@ -7036,6 +7143,7 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7054,6 +7162,7 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>PWRHYDNPLXX</t>
@@ -7077,6 +7186,7 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7095,6 +7205,7 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7118,6 +7229,7 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7136,6 +7248,7 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7159,6 +7272,7 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7177,6 +7291,7 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7200,6 +7315,7 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7218,6 +7334,7 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7241,6 +7358,7 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7259,6 +7377,7 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7282,6 +7401,7 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7300,6 +7420,7 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7323,6 +7444,7 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7341,6 +7463,7 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7364,6 +7487,7 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7382,6 +7506,7 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7405,6 +7530,7 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7423,6 +7549,7 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7446,6 +7573,7 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7464,6 +7592,7 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7487,6 +7616,7 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7505,6 +7635,7 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7528,6 +7659,7 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7546,6 +7678,7 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7569,6 +7702,7 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7587,6 +7721,7 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7610,6 +7745,7 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7628,6 +7764,7 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7651,6 +7788,7 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7669,6 +7807,7 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7692,6 +7831,7 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7710,6 +7850,7 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7733,6 +7874,7 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7751,6 +7893,7 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7774,6 +7917,7 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7792,6 +7936,7 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7815,6 +7960,7 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7833,6 +7979,7 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -7856,6 +8003,7 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7874,6 +8022,7 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -7897,6 +8046,7 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7915,6 +8065,7 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -7938,6 +8089,7 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7956,6 +8108,7 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -7979,6 +8132,7 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7997,6 +8151,7 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8020,6 +8175,7 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8038,6 +8194,7 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8061,6 +8218,7 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8079,6 +8237,7 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8102,6 +8261,7 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8120,6 +8280,7 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8143,6 +8304,7 @@
       <c r="J89" t="n">
         <v>1</v>
       </c>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8161,6 +8323,7 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8184,6 +8347,7 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8202,6 +8366,7 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8225,6 +8390,7 @@
       <c r="J91" t="n">
         <v>1</v>
       </c>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8243,6 +8409,7 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8266,6 +8433,7 @@
       <c r="J92" t="n">
         <v>1</v>
       </c>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8284,6 +8452,7 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8307,6 +8476,7 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8325,6 +8495,7 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8348,6 +8519,7 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8366,6 +8538,7 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8389,6 +8562,7 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8407,6 +8581,7 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8430,6 +8605,7 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8448,6 +8624,7 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8471,6 +8648,7 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8489,6 +8667,7 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8512,6 +8691,7 @@
       <c r="J98" t="n">
         <v>1</v>
       </c>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8530,6 +8710,7 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8553,6 +8734,7 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8571,6 +8753,7 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8594,6 +8777,7 @@
       <c r="J100" t="n">
         <v>1</v>
       </c>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8612,6 +8796,7 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8635,6 +8820,7 @@
       <c r="J101" t="n">
         <v>1</v>
       </c>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8653,6 +8839,7 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8676,6 +8863,7 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8694,6 +8882,7 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8717,6 +8906,7 @@
       <c r="J103" t="n">
         <v>1</v>
       </c>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8735,6 +8925,7 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8758,6 +8949,7 @@
       <c r="J104" t="n">
         <v>1</v>
       </c>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8776,6 +8968,7 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8799,6 +8992,7 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8817,6 +9011,7 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -8840,6 +9035,7 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8858,6 +9054,7 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -8881,6 +9078,7 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8899,6 +9097,7 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -8922,6 +9121,7 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8940,6 +9140,7 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -8963,6 +9164,7 @@
       <c r="J109" t="n">
         <v>1</v>
       </c>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8981,6 +9183,7 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -9004,6 +9207,7 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9022,6 +9226,7 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -9045,6 +9250,7 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9063,6 +9269,7 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9086,6 +9293,7 @@
       <c r="J112" t="n">
         <v>1</v>
       </c>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9104,6 +9312,7 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9127,6 +9336,7 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9145,6 +9355,7 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9168,6 +9379,7 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9186,6 +9398,7 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9209,6 +9422,7 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9227,6 +9441,7 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9250,6 +9465,7 @@
       <c r="J116" t="n">
         <v>1</v>
       </c>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9268,6 +9484,7 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9291,6 +9508,7 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9309,6 +9527,7 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9332,6 +9551,7 @@
       <c r="J118" t="n">
         <v>1</v>
       </c>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9350,6 +9570,7 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9373,6 +9594,7 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9391,6 +9613,7 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9414,6 +9637,7 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9432,6 +9656,7 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9455,6 +9680,7 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9473,6 +9699,7 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9496,6 +9723,7 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9514,6 +9742,7 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9537,6 +9766,7 @@
       <c r="J123" t="n">
         <v>1</v>
       </c>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9555,6 +9785,7 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9578,6 +9809,7 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9596,6 +9828,7 @@
       <c r="D125" t="n">
         <v>1</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9619,6 +9852,7 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9637,6 +9871,7 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9660,6 +9895,7 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9678,6 +9914,7 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9701,6 +9938,7 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9719,6 +9957,7 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -9742,6 +9981,7 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9760,6 +10000,7 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -9783,6 +10024,7 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9801,6 +10043,7 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>PWRSPVBGDXX</t>
@@ -9824,6 +10067,7 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9842,6 +10086,7 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>PWRSPVBTNXX</t>
@@ -9865,6 +10110,7 @@
       <c r="J131" t="n">
         <v>1</v>
       </c>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9883,6 +10129,7 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>PWRSPVINDEA</t>
@@ -9906,6 +10153,7 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9924,6 +10172,7 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>PWRSPVINDNE</t>
@@ -9947,6 +10196,7 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9965,6 +10215,7 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>PWRSPVINDNO</t>
@@ -9988,6 +10239,7 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10006,6 +10258,7 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>PWRSPVINDSO</t>
@@ -10029,6 +10282,7 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10047,6 +10301,7 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>PWRSPVINDWE</t>
@@ -10070,6 +10325,7 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10088,6 +10344,7 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>PWRSPVLKAXX</t>
@@ -10111,6 +10368,7 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10129,6 +10387,7 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>PWRSPVMDVXX</t>
@@ -10152,6 +10411,7 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10170,6 +10430,7 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>PWRSPVNPLXX</t>
@@ -10193,6 +10454,7 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10211,6 +10473,7 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10234,6 +10497,7 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10252,6 +10516,7 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10275,6 +10540,7 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10293,6 +10559,7 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10316,6 +10583,7 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10334,6 +10602,7 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10357,6 +10626,7 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10375,6 +10645,7 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10398,6 +10669,7 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10416,6 +10688,7 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10439,6 +10712,7 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10457,6 +10731,7 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10480,6 +10755,7 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10498,6 +10774,7 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10521,6 +10798,7 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10539,6 +10817,7 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10562,6 +10841,7 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10580,6 +10860,7 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10603,6 +10884,7 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10621,6 +10903,7 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10644,6 +10927,7 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
+      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10662,6 +10946,7 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10685,6 +10970,7 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10703,6 +10989,7 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>PWRWASBGDXX</t>
@@ -10726,6 +11013,7 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10744,6 +11032,7 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>PWRWASINDEA</t>
@@ -10767,6 +11056,7 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10785,6 +11075,7 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>PWRWASINDNE</t>
@@ -10808,6 +11099,7 @@
       <c r="J154" t="n">
         <v>1</v>
       </c>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10826,6 +11118,7 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>PWRWASINDNO</t>
@@ -10849,6 +11142,7 @@
       <c r="J155" t="n">
         <v>1</v>
       </c>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10867,6 +11161,7 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>PWRWASINDSO</t>
@@ -10890,6 +11185,7 @@
       <c r="J156" t="n">
         <v>1</v>
       </c>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -10908,6 +11204,7 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>PWRWASINDWE</t>
@@ -10931,6 +11228,7 @@
       <c r="J157" t="n">
         <v>1</v>
       </c>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -10949,6 +11247,7 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>PWRWASLKAXX</t>
@@ -10972,6 +11271,7 @@
       <c r="J158" t="n">
         <v>1</v>
       </c>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -10990,6 +11290,7 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>PWRWASNPLXX</t>
@@ -11013,6 +11314,7 @@
       <c r="J159" t="n">
         <v>1</v>
       </c>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11031,6 +11333,7 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>PWRWOFBGDXX</t>
@@ -11054,6 +11357,7 @@
       <c r="J160" t="n">
         <v>1</v>
       </c>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11072,6 +11376,7 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>PWRWOFINDEA</t>
@@ -11095,6 +11400,7 @@
       <c r="J161" t="n">
         <v>1</v>
       </c>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11113,6 +11419,7 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>PWRWOFINDNE</t>
@@ -11136,6 +11443,7 @@
       <c r="J162" t="n">
         <v>1</v>
       </c>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11154,6 +11462,7 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>PWRWOFINDNO</t>
@@ -11177,6 +11486,7 @@
       <c r="J163" t="n">
         <v>1</v>
       </c>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11195,6 +11505,7 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>PWRWOFINDSO</t>
@@ -11218,6 +11529,7 @@
       <c r="J164" t="n">
         <v>1</v>
       </c>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11236,6 +11548,7 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>PWRWOFINDWE</t>
@@ -11259,6 +11572,7 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11277,6 +11591,7 @@
       <c r="D166" t="n">
         <v>1</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>PWRWOFLKAXX</t>
@@ -11300,6 +11615,7 @@
       <c r="J166" t="n">
         <v>1</v>
       </c>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11318,6 +11634,7 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>PWRWONBGDXX</t>
@@ -11341,6 +11658,7 @@
       <c r="J167" t="n">
         <v>1</v>
       </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11359,6 +11677,7 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>PWRWONBTNXX</t>
@@ -11382,6 +11701,7 @@
       <c r="J168" t="n">
         <v>1</v>
       </c>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11400,6 +11720,7 @@
       <c r="D169" t="n">
         <v>1</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>PWRWONINDEA</t>
@@ -11423,6 +11744,7 @@
       <c r="J169" t="n">
         <v>1</v>
       </c>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11441,6 +11763,7 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>PWRWONINDNE</t>
@@ -11464,6 +11787,7 @@
       <c r="J170" t="n">
         <v>1</v>
       </c>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11482,6 +11806,7 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>PWRWONINDNO</t>
@@ -11505,6 +11830,7 @@
       <c r="J171" t="n">
         <v>1</v>
       </c>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -11523,6 +11849,7 @@
       <c r="D172" t="n">
         <v>1</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>PWRWONINDSO</t>
@@ -11546,6 +11873,7 @@
       <c r="J172" t="n">
         <v>1</v>
       </c>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -11564,6 +11892,7 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>PWRWONINDWE</t>
@@ -11587,6 +11916,7 @@
       <c r="J173" t="n">
         <v>1</v>
       </c>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -11605,6 +11935,7 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>PWRWONLKAXX</t>
@@ -11628,6 +11959,7 @@
       <c r="J174" t="n">
         <v>1</v>
       </c>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -11646,6 +11978,7 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>PWRWONNPLXX</t>
@@ -11669,6 +12002,7 @@
       <c r="J175" t="n">
         <v>1</v>
       </c>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -11687,6 +12021,7 @@
       <c r="D176" t="n">
         <v>1</v>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -11710,6 +12045,7 @@
       <c r="J176" t="n">
         <v>1</v>
       </c>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -11728,6 +12064,7 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -11751,6 +12088,7 @@
       <c r="J177" t="n">
         <v>1</v>
       </c>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -11769,6 +12107,7 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -11792,6 +12131,7 @@
       <c r="J178" t="n">
         <v>1</v>
       </c>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -11810,6 +12150,7 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -11833,6 +12174,7 @@
       <c r="J179" t="n">
         <v>1</v>
       </c>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -11851,6 +12193,7 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -11874,6 +12217,7 @@
       <c r="J180" t="n">
         <v>1</v>
       </c>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -11892,6 +12236,7 @@
       <c r="D181" t="n">
         <v>1</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -11915,6 +12260,7 @@
       <c r="J181" t="n">
         <v>1</v>
       </c>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -11933,6 +12279,7 @@
       <c r="D182" t="n">
         <v>1</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -11956,6 +12303,7 @@
       <c r="J182" t="n">
         <v>1</v>
       </c>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -11974,6 +12322,7 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -11997,6 +12346,7 @@
       <c r="J183" t="n">
         <v>1</v>
       </c>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12015,6 +12365,7 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12038,6 +12389,7 @@
       <c r="J184" t="n">
         <v>1</v>
       </c>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12056,6 +12408,7 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12079,6 +12432,7 @@
       <c r="J185" t="n">
         <v>1</v>
       </c>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12097,6 +12451,7 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12120,6 +12475,7 @@
       <c r="J186" t="n">
         <v>1</v>
       </c>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12138,6 +12494,7 @@
       <c r="D187" t="n">
         <v>1</v>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12161,6 +12518,7 @@
       <c r="J187" t="n">
         <v>1</v>
       </c>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12179,6 +12537,7 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12202,6 +12561,7 @@
       <c r="J188" t="n">
         <v>1</v>
       </c>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -12220,6 +12580,7 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12243,6 +12604,7 @@
       <c r="J189" t="n">
         <v>1</v>
       </c>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -12261,6 +12623,7 @@
       <c r="D190" t="n">
         <v>1</v>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12284,6 +12647,7 @@
       <c r="J190" t="n">
         <v>1</v>
       </c>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -12302,6 +12666,7 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12325,6 +12690,7 @@
       <c r="J191" t="n">
         <v>1</v>
       </c>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -12343,6 +12709,7 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12366,6 +12733,7 @@
       <c r="J192" t="n">
         <v>1</v>
       </c>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -12384,6 +12752,7 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12407,6 +12776,7 @@
       <c r="J193" t="n">
         <v>1</v>
       </c>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -12425,6 +12795,7 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12448,6 +12819,7 @@
       <c r="J194" t="n">
         <v>1</v>
       </c>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -12466,6 +12838,7 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12489,6 +12862,7 @@
       <c r="J195" t="n">
         <v>1</v>
       </c>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -12507,6 +12881,7 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12530,6 +12905,7 @@
       <c r="J196" t="n">
         <v>1</v>
       </c>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -12548,6 +12924,7 @@
       <c r="D197" t="n">
         <v>1</v>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12571,6 +12948,7 @@
       <c r="J197" t="n">
         <v>1</v>
       </c>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -12589,6 +12967,7 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -12612,6 +12991,7 @@
       <c r="J198" t="n">
         <v>1</v>
       </c>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -12630,6 +13010,7 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -12653,6 +13034,7 @@
       <c r="J199" t="n">
         <v>1</v>
       </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12671,6 +13053,7 @@
       <c r="D200" t="n">
         <v>1</v>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -12694,6 +13077,7 @@
       <c r="J200" t="n">
         <v>1</v>
       </c>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12712,6 +13096,7 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -12735,6 +13120,7 @@
       <c r="J201" t="n">
         <v>1</v>
       </c>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12753,6 +13139,7 @@
       <c r="D202" t="n">
         <v>1</v>
       </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>TRNLKAXXMDVXX</t>
@@ -12776,6 +13163,7 @@
       <c r="J202" t="n">
         <v>1</v>
       </c>
+      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12794,6 +13182,7 @@
       <c r="D203" t="n">
         <v>1</v>
       </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>TRNLKAXXMDVXX</t>
@@ -12817,11 +13206,16 @@
       <c r="J203" t="n">
         <v>1</v>
       </c>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>1</v>
       </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>PWRBCKBGDXX</t>
@@ -12845,11 +13239,16 @@
       <c r="J204" t="n">
         <v>1</v>
       </c>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>1</v>
       </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>PWRBCKBTNXX</t>
@@ -12873,11 +13272,16 @@
       <c r="J205" t="n">
         <v>1</v>
       </c>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>1</v>
       </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>PWRBCKINDEA</t>
@@ -12901,11 +13305,16 @@
       <c r="J206" t="n">
         <v>1</v>
       </c>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>1</v>
       </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>PWRBCKINDNE</t>
@@ -12929,11 +13338,16 @@
       <c r="J207" t="n">
         <v>1</v>
       </c>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>1</v>
       </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>PWRBCKINDNO</t>
@@ -12957,11 +13371,16 @@
       <c r="J208" t="n">
         <v>1</v>
       </c>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>1</v>
       </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>PWRBCKINDSO</t>
@@ -12985,11 +13404,16 @@
       <c r="J209" t="n">
         <v>1</v>
       </c>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>1</v>
       </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>PWRBCKINDWE</t>
@@ -13013,11 +13437,16 @@
       <c r="J210" t="n">
         <v>1</v>
       </c>
+      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>1</v>
       </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>PWRBCKLKAXX</t>
@@ -13041,11 +13470,16 @@
       <c r="J211" t="n">
         <v>1</v>
       </c>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>1</v>
       </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>PWRBCKMDVXX</t>
@@ -13069,11 +13503,16 @@
       <c r="J212" t="n">
         <v>1</v>
       </c>
+      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>1</v>
       </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>PWRBCKNPLXX</t>
@@ -13097,11 +13536,16 @@
       <c r="J213" t="n">
         <v>1</v>
       </c>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>2</v>
       </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>PWRLDSBGDXX</t>
@@ -13125,11 +13569,16 @@
       <c r="J214" t="n">
         <v>1</v>
       </c>
+      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>2</v>
       </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>PWRLDSBTNXX</t>
@@ -13153,11 +13602,16 @@
       <c r="J215" t="n">
         <v>1</v>
       </c>
+      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>2</v>
       </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>PWRLDSINDEA</t>
@@ -13181,11 +13635,16 @@
       <c r="J216" t="n">
         <v>1</v>
       </c>
+      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
         <v>2</v>
       </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>PWRLDSINDNE</t>
@@ -13209,11 +13668,16 @@
       <c r="J217" t="n">
         <v>1</v>
       </c>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
         <v>2</v>
       </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>PWRLDSINDNO</t>
@@ -13237,11 +13701,16 @@
       <c r="J218" t="n">
         <v>1</v>
       </c>
+      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
         <v>2</v>
       </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>PWRLDSINDSO</t>
@@ -13265,11 +13734,16 @@
       <c r="J219" t="n">
         <v>1</v>
       </c>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
         <v>2</v>
       </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>PWRLDSINDWE</t>
@@ -13293,11 +13767,16 @@
       <c r="J220" t="n">
         <v>1</v>
       </c>
+      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
         <v>2</v>
       </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>PWRLDSLKAXX</t>
@@ -13321,11 +13800,16 @@
       <c r="J221" t="n">
         <v>1</v>
       </c>
+      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
         <v>2</v>
       </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>PWRLDSMDVXX</t>
@@ -13349,11 +13833,16 @@
       <c r="J222" t="n">
         <v>1</v>
       </c>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
         <v>2</v>
       </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>PWRLDSNPLXX</t>
@@ -13377,11 +13866,16 @@
       <c r="J223" t="n">
         <v>1</v>
       </c>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
         <v>2</v>
       </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>PWRSDSBGDXX</t>
@@ -13405,11 +13899,16 @@
       <c r="J224" t="n">
         <v>1</v>
       </c>
+      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
         <v>2</v>
       </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>PWRSDSBTNXX</t>
@@ -13433,11 +13932,16 @@
       <c r="J225" t="n">
         <v>1</v>
       </c>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
         <v>2</v>
       </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>PWRSDSINDEA</t>
@@ -13461,11 +13965,16 @@
       <c r="J226" t="n">
         <v>1</v>
       </c>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
         <v>2</v>
       </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>PWRSDSINDNE</t>
@@ -13489,11 +13998,16 @@
       <c r="J227" t="n">
         <v>1</v>
       </c>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
         <v>2</v>
       </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>PWRSDSINDNO</t>
@@ -13517,11 +14031,16 @@
       <c r="J228" t="n">
         <v>1</v>
       </c>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
         <v>2</v>
       </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>PWRSDSINDSO</t>
@@ -13545,11 +14064,16 @@
       <c r="J229" t="n">
         <v>1</v>
       </c>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
         <v>2</v>
       </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>PWRSDSINDWE</t>
@@ -13573,11 +14097,16 @@
       <c r="J230" t="n">
         <v>1</v>
       </c>
+      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
         <v>2</v>
       </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>PWRSDSLKAXX</t>
@@ -13601,11 +14130,16 @@
       <c r="J231" t="n">
         <v>1</v>
       </c>
+      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
         <v>2</v>
       </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>PWRSDSMDVXX</t>
@@ -13629,11 +14163,16 @@
       <c r="J232" t="n">
         <v>1</v>
       </c>
+      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
         <v>2</v>
       </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>PWRSDSNPLXX</t>
@@ -13657,6 +14196,7 @@
       <c r="J233" t="n">
         <v>1</v>
       </c>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -13675,6 +14215,7 @@
       <c r="D234" t="n">
         <v>1</v>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>PWRLDSBGDXX</t>
@@ -13685,6 +14226,10 @@
           <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -13703,6 +14248,7 @@
       <c r="D235" t="n">
         <v>1</v>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>PWRLDSBTNXX</t>
@@ -13713,6 +14259,10 @@
           <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -13731,6 +14281,7 @@
       <c r="D236" t="n">
         <v>1</v>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>PWRLDSINDEA</t>
@@ -13741,6 +14292,10 @@
           <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -13759,6 +14314,7 @@
       <c r="D237" t="n">
         <v>1</v>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>PWRLDSINDNE</t>
@@ -13769,6 +14325,10 @@
           <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -13787,6 +14347,7 @@
       <c r="D238" t="n">
         <v>1</v>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>PWRLDSINDNO</t>
@@ -13797,6 +14358,10 @@
           <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -13815,6 +14380,7 @@
       <c r="D239" t="n">
         <v>1</v>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>PWRLDSINDSO</t>
@@ -13825,6 +14391,10 @@
           <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -13843,6 +14413,7 @@
       <c r="D240" t="n">
         <v>1</v>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>PWRLDSINDWE</t>
@@ -13853,6 +14424,10 @@
           <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -13871,6 +14446,7 @@
       <c r="D241" t="n">
         <v>1</v>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>PWRLDSLKAXX</t>
@@ -13881,6 +14457,10 @@
           <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -13899,6 +14479,7 @@
       <c r="D242" t="n">
         <v>1</v>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>PWRLDSMDVXX</t>
@@ -13909,6 +14490,10 @@
           <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -13927,6 +14512,7 @@
       <c r="D243" t="n">
         <v>1</v>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>PWRLDSNPLXX</t>
@@ -13937,6 +14523,10 @@
           <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -13955,6 +14545,7 @@
       <c r="D244" t="n">
         <v>1</v>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>PWRSDSBGDXX</t>
@@ -13965,6 +14556,10 @@
           <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -13983,6 +14578,7 @@
       <c r="D245" t="n">
         <v>1</v>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>PWRSDSBTNXX</t>
@@ -13993,6 +14589,10 @@
           <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14011,6 +14611,7 @@
       <c r="D246" t="n">
         <v>1</v>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>PWRSDSINDEA</t>
@@ -14021,6 +14622,10 @@
           <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14039,6 +14644,7 @@
       <c r="D247" t="n">
         <v>1</v>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>PWRSDSINDNE</t>
@@ -14049,6 +14655,10 @@
           <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -14067,6 +14677,7 @@
       <c r="D248" t="n">
         <v>1</v>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>PWRSDSINDNO</t>
@@ -14077,6 +14688,10 @@
           <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -14095,6 +14710,7 @@
       <c r="D249" t="n">
         <v>1</v>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>PWRSDSINDSO</t>
@@ -14105,6 +14721,10 @@
           <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -14123,6 +14743,7 @@
       <c r="D250" t="n">
         <v>1</v>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>PWRSDSINDWE</t>
@@ -14133,6 +14754,10 @@
           <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -14151,6 +14776,7 @@
       <c r="D251" t="n">
         <v>1</v>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>PWRSDSLKAXX</t>
@@ -14161,6 +14787,10 @@
           <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -14179,6 +14809,7 @@
       <c r="D252" t="n">
         <v>1</v>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>PWRSDSMDVXX</t>
@@ -14189,6 +14820,10 @@
           <t>Short duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -14207,6 +14842,7 @@
       <c r="D253" t="n">
         <v>1</v>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>PWRSDSNPLXX</t>
@@ -14217,1038 +14853,10 @@
           <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B254" s="10" t="inlineStr">
-        <is>
-          <t>GEOINDNO</t>
-        </is>
-      </c>
-      <c r="C254" s="10" t="inlineStr">
-        <is>
-          <t>Geothermal, India, region NO</t>
-        </is>
-      </c>
-      <c r="D254" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" s="9" t="n"/>
-      <c r="F254" s="9" t="inlineStr">
-        <is>
-          <t>PWRGEOINDNO</t>
-        </is>
-      </c>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>Geothermal (Power generator) India, region NO</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDNO00</t>
-        </is>
-      </c>
-      <c r="I254" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J254" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K254" s="9" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B255" s="10" t="inlineStr">
-        <is>
-          <t>GASBGD</t>
-        </is>
-      </c>
-      <c r="C255" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas, Bangladesh</t>
-        </is>
-      </c>
-      <c r="D255" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E255" s="9" t="n"/>
-      <c r="F255" s="9" t="inlineStr">
-        <is>
-          <t>PWRNGSBGDXX</t>
-        </is>
-      </c>
-      <c r="G255" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas (Power generator) Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H255" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX01</t>
-        </is>
-      </c>
-      <c r="I255" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J255" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K255" s="9" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B256" s="9" t="inlineStr">
-        <is>
-          <t>GASINT</t>
-        </is>
-      </c>
-      <c r="C256" s="9" t="inlineStr">
-        <is>
-          <t>Natural Gas, International Markets</t>
-        </is>
-      </c>
-      <c r="D256" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E256" s="9" t="n"/>
-      <c r="F256" s="9" t="inlineStr">
-        <is>
-          <t>PWRNGSBGDXX</t>
-        </is>
-      </c>
-      <c r="G256" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas (Power generator) Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H256" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX01</t>
-        </is>
-      </c>
-      <c r="I256" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J256" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K256" s="9" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B257" s="10" t="inlineStr">
-        <is>
-          <t>GASMDV</t>
-        </is>
-      </c>
-      <c r="C257" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas, Maldives</t>
-        </is>
-      </c>
-      <c r="D257" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="9" t="n"/>
-      <c r="F257" s="9" t="inlineStr">
-        <is>
-          <t>PWRNGSMDVXX</t>
-        </is>
-      </c>
-      <c r="G257" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H257" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX01</t>
-        </is>
-      </c>
-      <c r="I257" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J257" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K257" s="9" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
-        <is>
-          <t>GASINT</t>
-        </is>
-      </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>Natural Gas, International Markets</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" s="9" t="n"/>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>PWRNGSMDVXX</t>
-        </is>
-      </c>
-      <c r="G258" s="10" t="inlineStr">
-        <is>
-          <t>Natural Gas (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX01</t>
-        </is>
-      </c>
-      <c r="I258" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J258" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K258" s="9" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B259" s="10" t="inlineStr">
-        <is>
-          <t>OILMDV</t>
-        </is>
-      </c>
-      <c r="C259" s="10" t="inlineStr">
-        <is>
-          <t>Oil, Maldives</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="9" t="n"/>
-      <c r="F259" s="9" t="inlineStr">
-        <is>
-          <t>PWROILMDVXX</t>
-        </is>
-      </c>
-      <c r="G259" s="10" t="inlineStr">
-        <is>
-          <t>Oil (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H259" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX01</t>
-        </is>
-      </c>
-      <c r="I259" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J259" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K259" s="9" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B260" s="9" t="inlineStr">
-        <is>
-          <t>OILINT</t>
-        </is>
-      </c>
-      <c r="C260" s="9" t="inlineStr">
-        <is>
-          <t>Oil, International Markets</t>
-        </is>
-      </c>
-      <c r="D260" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" s="9" t="n"/>
-      <c r="F260" s="9" t="inlineStr">
-        <is>
-          <t>PWROILMDVXX</t>
-        </is>
-      </c>
-      <c r="G260" s="10" t="inlineStr">
-        <is>
-          <t>Oil (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H260" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX01</t>
-        </is>
-      </c>
-      <c r="I260" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J260" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K260" s="9" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B261" s="10" t="inlineStr">
-        <is>
-          <t>OILNPL</t>
-        </is>
-      </c>
-      <c r="C261" s="10" t="inlineStr">
-        <is>
-          <t>Oil, Nepal</t>
-        </is>
-      </c>
-      <c r="D261" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" s="9" t="n"/>
-      <c r="F261" s="9" t="inlineStr">
-        <is>
-          <t>PWROILNPLXX</t>
-        </is>
-      </c>
-      <c r="G261" s="10" t="inlineStr">
-        <is>
-          <t>Oil (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="H261" s="9" t="inlineStr">
-        <is>
-          <t>ELCNPLXX01</t>
-        </is>
-      </c>
-      <c r="I261" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Nepal, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J261" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K261" s="9" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B262" s="9" t="inlineStr">
-        <is>
-          <t>OILINT</t>
-        </is>
-      </c>
-      <c r="C262" s="9" t="inlineStr">
-        <is>
-          <t>Oil, International Markets</t>
-        </is>
-      </c>
-      <c r="D262" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" s="9" t="n"/>
-      <c r="F262" s="9" t="inlineStr">
-        <is>
-          <t>PWROILNPLXX</t>
-        </is>
-      </c>
-      <c r="G262" s="10" t="inlineStr">
-        <is>
-          <t>Oil (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="H262" s="9" t="inlineStr">
-        <is>
-          <t>ELCNPLXX01</t>
-        </is>
-      </c>
-      <c r="I262" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Nepal, region XX, NO renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J262" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K262" s="9" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>HYDINDEA</t>
-        </is>
-      </c>
-      <c r="C263" s="9" t="inlineStr">
-        <is>
-          <t>Hydroelectric, India, region EA</t>
-        </is>
-      </c>
-      <c r="D263" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" s="9" t="n"/>
-      <c r="F263" s="9" t="inlineStr">
-        <is>
-          <t>PWRSHPINDEA</t>
-        </is>
-      </c>
-      <c r="G263" s="10" t="inlineStr">
-        <is>
-          <t>Small Hydropower (Power generator) India, region EA</t>
-        </is>
-      </c>
-      <c r="H263" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDEA00</t>
-        </is>
-      </c>
-      <c r="I263" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region EA, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J263" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K263" s="9" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B264" s="9" t="inlineStr">
-        <is>
-          <t>HYDINDNE</t>
-        </is>
-      </c>
-      <c r="C264" s="9" t="inlineStr">
-        <is>
-          <t>Hydroelectric, India, region NE</t>
-        </is>
-      </c>
-      <c r="D264" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E264" s="9" t="n"/>
-      <c r="F264" s="9" t="inlineStr">
-        <is>
-          <t>PWRSHPINDNE</t>
-        </is>
-      </c>
-      <c r="G264" s="10" t="inlineStr">
-        <is>
-          <t>Small Hydropower (Power generator) India, region NE</t>
-        </is>
-      </c>
-      <c r="H264" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDNE00</t>
-        </is>
-      </c>
-      <c r="I264" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region NE, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J264" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K264" s="9" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
-        <is>
-          <t>HYDINDNO</t>
-        </is>
-      </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>Hydroelectric, India, region NO</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" s="9" t="n"/>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>PWRSHPINDNO</t>
-        </is>
-      </c>
-      <c r="G265" s="10" t="inlineStr">
-        <is>
-          <t>Small Hydropower (Power generator) India, region NO</t>
-        </is>
-      </c>
-      <c r="H265" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDNO00</t>
-        </is>
-      </c>
-      <c r="I265" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region NO, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J265" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K265" s="9" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B266" s="9" t="inlineStr">
-        <is>
-          <t>HYDINDSO</t>
-        </is>
-      </c>
-      <c r="C266" s="9" t="inlineStr">
-        <is>
-          <t>Hydroelectric, India, region SO</t>
-        </is>
-      </c>
-      <c r="D266" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E266" s="9" t="n"/>
-      <c r="F266" s="9" t="inlineStr">
-        <is>
-          <t>PWRSHPINDSO</t>
-        </is>
-      </c>
-      <c r="G266" s="10" t="inlineStr">
-        <is>
-          <t>Small Hydropower (Power generator) India, region SO</t>
-        </is>
-      </c>
-      <c r="H266" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDSO00</t>
-        </is>
-      </c>
-      <c r="I266" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region SO, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J266" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K266" s="9" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
-        <is>
-          <t>HYDINDWE</t>
-        </is>
-      </c>
-      <c r="C267" s="9" t="inlineStr">
-        <is>
-          <t>Hydroelectric, India, region WE</t>
-        </is>
-      </c>
-      <c r="D267" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E267" s="9" t="n"/>
-      <c r="F267" s="9" t="inlineStr">
-        <is>
-          <t>PWRSHPINDWE</t>
-        </is>
-      </c>
-      <c r="G267" s="10" t="inlineStr">
-        <is>
-          <t>Small Hydropower (Power generator) India, region WE</t>
-        </is>
-      </c>
-      <c r="H267" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDWE00</t>
-        </is>
-      </c>
-      <c r="I267" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, Region WE, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J267" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K267" s="9" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B268" s="9" t="inlineStr">
-        <is>
-          <t>WOFMDVXX</t>
-        </is>
-      </c>
-      <c r="C268" s="9" t="inlineStr">
-        <is>
-          <t>Offshore Wind, Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D268" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" s="9" t="n"/>
-      <c r="F268" s="9" t="inlineStr">
-        <is>
-          <t>PWRWOFMDVXX</t>
-        </is>
-      </c>
-      <c r="G268" s="10" t="inlineStr">
-        <is>
-          <t>Offshore Wind (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H268" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX00</t>
-        </is>
-      </c>
-      <c r="I268" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J268" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K268" s="9" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
-        <is>
-          <t>WONMDVXX</t>
-        </is>
-      </c>
-      <c r="C269" s="9" t="inlineStr">
-        <is>
-          <t>Onshore Wind, Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D269" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" s="9" t="n"/>
-      <c r="F269" s="9" t="inlineStr">
-        <is>
-          <t>PWRWONMDVXX</t>
-        </is>
-      </c>
-      <c r="G269" s="10" t="inlineStr">
-        <is>
-          <t>Onshore Wind (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="H269" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX00</t>
-        </is>
-      </c>
-      <c r="I269" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, renewable power plant output</t>
-        </is>
-      </c>
-      <c r="J269" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K269" s="9" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B270" s="9" t="inlineStr">
-        <is>
-          <t>ELCBTNXX03</t>
-        </is>
-      </c>
-      <c r="C270" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" s="9" t="n"/>
-      <c r="F270" s="9" t="inlineStr">
-        <is>
-          <t>TRNBTNXXBGDXX</t>
-        </is>
-      </c>
-      <c r="G270" s="10" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Bhutan, region XX to Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H270" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX04</t>
-        </is>
-      </c>
-      <c r="I270" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J270" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K270" s="9" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B271" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX03</t>
-        </is>
-      </c>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D271" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" s="9" t="n"/>
-      <c r="F271" s="9" t="inlineStr">
-        <is>
-          <t>TRNBTNXXBGDXX</t>
-        </is>
-      </c>
-      <c r="G271" s="10" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Bhutan, region XX to Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H271" s="9" t="inlineStr">
-        <is>
-          <t>ELCBTNXX04</t>
-        </is>
-      </c>
-      <c r="I271" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J271" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K271" s="9" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B272" s="9" t="inlineStr">
-        <is>
-          <t>ELCBTNXX03</t>
-        </is>
-      </c>
-      <c r="C272" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D272" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="9" t="n"/>
-      <c r="F272" s="9" t="inlineStr">
-        <is>
-          <t>TRNBTNXXINDNE</t>
-        </is>
-      </c>
-      <c r="G272" s="10" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Bhutan, region XX to India, region NE</t>
-        </is>
-      </c>
-      <c r="H272" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDNE04</t>
-        </is>
-      </c>
-      <c r="I272" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, region NE, power plant output</t>
-        </is>
-      </c>
-      <c r="J272" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K272" s="9" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B273" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDNE03</t>
-        </is>
-      </c>
-      <c r="C273" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D273" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="9" t="n"/>
-      <c r="F273" s="9" t="inlineStr">
-        <is>
-          <t>TRNBTNXXINDNE</t>
-        </is>
-      </c>
-      <c r="G273" s="10" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Bhutan, region XX to India, region NE</t>
-        </is>
-      </c>
-      <c r="H273" s="9" t="inlineStr">
-        <is>
-          <t>ELCBTNXX04</t>
-        </is>
-      </c>
-      <c r="I273" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bhutan, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J273" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K273" s="9" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B274" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX03</t>
-        </is>
-      </c>
-      <c r="C274" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D274" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="9" t="n"/>
-      <c r="F274" s="9" t="inlineStr">
-        <is>
-          <t>TRNMDVXXINDSO</t>
-        </is>
-      </c>
-      <c r="G274" s="9" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Maldives, region XX to India, region SO</t>
-        </is>
-      </c>
-      <c r="H274" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDSO04</t>
-        </is>
-      </c>
-      <c r="I274" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, region SO, power plant output</t>
-        </is>
-      </c>
-      <c r="J274" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K274" s="9" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B275" s="9" t="inlineStr">
-        <is>
-          <t>ELCINDSO03</t>
-        </is>
-      </c>
-      <c r="C275" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D275" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E275" s="9" t="n"/>
-      <c r="F275" s="9" t="inlineStr">
-        <is>
-          <t>TRNMDVXXINDSO</t>
-        </is>
-      </c>
-      <c r="G275" s="9" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Maldives, region XX to India, region SO</t>
-        </is>
-      </c>
-      <c r="H275" s="9" t="inlineStr">
-        <is>
-          <t>ELCMDVXX04</t>
-        </is>
-      </c>
-      <c r="I275" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Maldives, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J275" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K275" s="9" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B276" s="9" t="inlineStr">
-        <is>
-          <t>ELCNPLXX03</t>
-        </is>
-      </c>
-      <c r="C276" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D276" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E276" s="9" t="n"/>
-      <c r="F276" s="9" t="inlineStr">
-        <is>
-          <t>TRNNPLXXBGDXX</t>
-        </is>
-      </c>
-      <c r="G276" s="9" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Nepal, region XX to Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H276" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX04</t>
-        </is>
-      </c>
-      <c r="I276" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J276" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K276" s="9" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>ELCBGDXX03</t>
-        </is>
-      </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E277" s="9" t="n"/>
-      <c r="F277" s="9" t="inlineStr">
-        <is>
-          <t>TRNNPLXXBGDXX</t>
-        </is>
-      </c>
-      <c r="G277" s="9" t="inlineStr">
-        <is>
-          <t>Transmission interconnection from Nepal, region XX to Bangladesh, region XX</t>
-        </is>
-      </c>
-      <c r="H277" s="9" t="inlineStr">
-        <is>
-          <t>ELCNPLXX04</t>
-        </is>
-      </c>
-      <c r="I277" s="9" t="inlineStr">
-        <is>
-          <t>Electricity, Nepal, region XX, power plant output</t>
-        </is>
-      </c>
-      <c r="J277" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K277" s="9" t="n"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15349,6 +14957,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>RNWTRNBGDXX</t>
@@ -15372,6 +14981,7 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15390,6 +15000,7 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>RNWRPOBGDXX</t>
@@ -15413,6 +15024,7 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15431,6 +15043,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>RNWNLIBGDXX</t>
@@ -15454,6 +15067,7 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15472,6 +15086,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRTRNBGDXX</t>
@@ -15495,6 +15110,7 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15513,6 +15129,7 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TRNRPOBGDXX</t>
@@ -15536,6 +15153,7 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15554,6 +15172,7 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TRNNLIBGDXX</t>
@@ -15577,6 +15196,7 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15595,6 +15215,7 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>DSPTRNBGDXX</t>
@@ -15618,6 +15239,7 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -15636,6 +15258,7 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>DSPTRNBGDXX</t>
@@ -15659,6 +15282,7 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -15677,6 +15301,7 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>RNWTRNBTNXX</t>
@@ -15700,6 +15325,7 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15718,6 +15344,7 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>RNWRPOBTNXX</t>
@@ -15741,6 +15368,7 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15759,6 +15387,7 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>RNWNLIBTNXX</t>
@@ -15782,6 +15411,7 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15800,6 +15430,7 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRTRNBTNXX</t>
@@ -15823,6 +15454,7 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +15473,7 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TRNRPOBTNXX</t>
@@ -15864,6 +15497,7 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15882,6 +15516,7 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TRNNLIBTNXX</t>
@@ -15905,6 +15540,7 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15923,6 +15559,7 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>DSPTRNBTNXX</t>
@@ -15946,6 +15583,7 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15964,6 +15602,7 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>DSPTRNBTNXX</t>
@@ -15987,6 +15626,7 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16005,6 +15645,7 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>RNWTRNINDEA</t>
@@ -16028,6 +15669,7 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16046,6 +15688,7 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>RNWRPOINDEA</t>
@@ -16069,6 +15712,7 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16087,6 +15731,7 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>RNWNLIINDEA</t>
@@ -16110,6 +15755,7 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16128,6 +15774,7 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRTRNINDEA</t>
@@ -16151,6 +15798,7 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16169,6 +15817,7 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>TRNRPOINDEA</t>
@@ -16192,6 +15841,7 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16210,6 +15860,7 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>TRNNLIINDEA</t>
@@ -16233,6 +15884,7 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16251,6 +15903,7 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>DSPTRNINDEA</t>
@@ -16274,6 +15927,7 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -16292,6 +15946,7 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>DSPTRNINDEA</t>
@@ -16315,6 +15970,7 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -16333,6 +15989,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>RNWTRNINDNE</t>
@@ -16356,6 +16013,7 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -16374,6 +16032,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>RNWRPOINDNE</t>
@@ -16397,6 +16056,7 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -16415,6 +16075,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>RNWNLIINDNE</t>
@@ -16438,6 +16099,7 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -16456,6 +16118,7 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRTRNINDNE</t>
@@ -16479,6 +16142,7 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16497,6 +16161,7 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TRNRPOINDNE</t>
@@ -16520,6 +16185,7 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16538,6 +16204,7 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TRNNLIINDNE</t>
@@ -16561,6 +16228,7 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16579,6 +16247,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>DSPTRNINDNE</t>
@@ -16602,6 +16271,7 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16620,6 +16290,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>DSPTRNINDNE</t>
@@ -16643,6 +16314,7 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -16661,6 +16333,7 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>RNWTRNINDNO</t>
@@ -16684,6 +16357,7 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -16702,6 +16376,7 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>RNWRPOINDNO</t>
@@ -16725,6 +16400,7 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -16743,6 +16419,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>RNWNLIINDNO</t>
@@ -16766,6 +16443,7 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -16784,6 +16462,7 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRTRNINDNO</t>
@@ -16807,6 +16486,7 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -16825,6 +16505,7 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>TRNRPOINDNO</t>
@@ -16848,6 +16529,7 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -16866,6 +16548,7 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>TRNNLIINDNO</t>
@@ -16889,6 +16572,7 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -16907,6 +16591,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>DSPTRNINDNO</t>
@@ -16930,6 +16615,7 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -16948,6 +16634,7 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>DSPTRNINDNO</t>
@@ -16971,6 +16658,7 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -16989,6 +16677,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>RNWTRNINDSO</t>
@@ -17012,6 +16701,7 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -17030,6 +16720,7 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>RNWRPOINDSO</t>
@@ -17053,6 +16744,7 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -17071,6 +16763,7 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>RNWNLIINDSO</t>
@@ -17094,6 +16787,7 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -17112,6 +16806,7 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRTRNINDSO</t>
@@ -17135,6 +16830,7 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -17153,6 +16849,7 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>TRNRPOINDSO</t>
@@ -17176,6 +16873,7 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -17194,6 +16892,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>TRNNLIINDSO</t>
@@ -17217,6 +16916,7 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -17235,6 +16935,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>DSPTRNINDSO</t>
@@ -17258,6 +16959,7 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -17276,6 +16978,7 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>DSPTRNINDSO</t>
@@ -17299,6 +17002,7 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -17317,6 +17021,7 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>RNWTRNINDWE</t>
@@ -17340,6 +17045,7 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -17358,6 +17064,7 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>RNWRPOINDWE</t>
@@ -17381,6 +17088,7 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -17399,6 +17107,7 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>RNWNLIINDWE</t>
@@ -17422,6 +17131,7 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -17440,6 +17150,7 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRTRNINDWE</t>
@@ -17463,6 +17174,7 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -17481,6 +17193,7 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>TRNRPOINDWE</t>
@@ -17504,6 +17217,7 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -17522,6 +17236,7 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>TRNNLIINDWE</t>
@@ -17545,6 +17260,7 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -17563,6 +17279,7 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>DSPTRNINDWE</t>
@@ -17586,6 +17303,7 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -17604,6 +17322,7 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>DSPTRNINDWE</t>
@@ -17627,6 +17346,7 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -17645,6 +17365,7 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>RNWTRNNPLXX</t>
@@ -17668,6 +17389,7 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -17686,6 +17408,7 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>RNWRPONPLXX</t>
@@ -17709,6 +17432,7 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -17727,6 +17451,7 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>RNWNLINPLXX</t>
@@ -17750,6 +17475,7 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -17768,6 +17494,7 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRTRNNPLXX</t>
@@ -17791,6 +17518,7 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -17809,6 +17537,7 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>TRNRPONPLXX</t>
@@ -17832,6 +17561,7 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -17850,6 +17580,7 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>TRNNLINPLXX</t>
@@ -17873,6 +17604,7 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -17891,6 +17623,7 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>DSPTRNNPLXX</t>
@@ -17914,6 +17647,7 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -17932,6 +17666,7 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>DSPTRNNPLXX</t>
@@ -17955,6 +17690,7 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -17973,6 +17709,7 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>RNWTRNLKAXX</t>
@@ -17996,6 +17733,7 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -18014,6 +17752,7 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>RNWRPOLKAXX</t>
@@ -18037,6 +17776,7 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -18055,6 +17795,7 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>RNWNLILKAXX</t>
@@ -18078,6 +17819,7 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -18096,6 +17838,7 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRTRNLKAXX</t>
@@ -18119,6 +17862,7 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -18137,6 +17881,7 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>TRNRPOLKAXX</t>
@@ -18160,6 +17905,7 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -18178,6 +17924,7 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>TRNNLILKAXX</t>
@@ -18201,6 +17948,7 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -18219,6 +17967,7 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>DSPTRNLKAXX</t>
@@ -18242,6 +17991,7 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -18260,6 +18010,7 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>DSPTRNLKAXX</t>
@@ -18283,6 +18034,7 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -18301,6 +18053,7 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>RNWTRNMDVXX</t>
@@ -18324,6 +18077,7 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -18342,6 +18096,7 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>RNWRPOMDVXX</t>
@@ -18365,6 +18120,7 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -18383,6 +18139,7 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>RNWNLIMDVXX</t>
@@ -18406,6 +18163,7 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -18424,6 +18182,7 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWRTRNMDVXX</t>
@@ -18447,6 +18206,7 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -18465,6 +18225,7 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>TRNRPOMDVXX</t>
@@ -18488,6 +18249,7 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -18506,6 +18268,7 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>TRNNLIMDVXX</t>
@@ -18529,6 +18292,7 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -18547,6 +18311,7 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>DSPTRNMDVXX</t>
@@ -18570,6 +18335,7 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -18588,6 +18354,7 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>DSPTRNMDVXX</t>
@@ -18611,6 +18378,7 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
+      <c r="K81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -49,7 +49,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,18 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor rgb="FFFCD5B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9B59B6"/>
+        <bgColor rgb="FF9B59B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -131,6 +143,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4450,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K253"/>
+  <dimension ref="A1:K277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -4539,7 +4553,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>PWRBIOBGDXX</t>
@@ -4563,7 +4576,6 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4582,7 +4594,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>PWRBIOINDEA</t>
@@ -4606,7 +4617,6 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4625,7 +4635,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>PWRBIOINDNE</t>
@@ -4649,7 +4658,6 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4668,7 +4676,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRBIOINDNO</t>
@@ -4692,7 +4699,6 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4711,7 +4717,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>PWRBIOINDSO</t>
@@ -4735,7 +4740,6 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4754,7 +4758,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>PWRBIOINDWE</t>
@@ -4778,7 +4781,6 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4797,7 +4799,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>PWRBIOLKAXX</t>
@@ -4821,7 +4822,6 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4840,7 +4840,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PWRBIONPLXX</t>
@@ -4864,7 +4863,6 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4883,7 +4881,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4907,7 +4904,6 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4926,7 +4922,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PWRCCSBGDXX</t>
@@ -4950,7 +4945,6 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4969,7 +4963,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -4993,7 +4986,6 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5012,7 +5004,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRCCSINDEA</t>
@@ -5036,7 +5027,6 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5055,7 +5045,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5079,7 +5068,6 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5098,7 +5086,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>PWRCCSINDNE</t>
@@ -5122,7 +5109,6 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5141,7 +5127,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5165,7 +5150,6 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5184,7 +5168,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PWRCCSINDNO</t>
@@ -5208,7 +5191,6 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5227,7 +5209,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5251,7 +5232,6 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5270,7 +5250,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>PWRCCSINDSO</t>
@@ -5294,7 +5273,6 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5313,7 +5291,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5337,7 +5314,6 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5356,7 +5332,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRCCSINDWE</t>
@@ -5380,7 +5355,6 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5399,7 +5373,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5423,7 +5396,6 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5442,7 +5414,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PWRCOABGDXX</t>
@@ -5466,7 +5437,6 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5485,7 +5455,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5509,7 +5478,6 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5528,7 +5496,6 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>PWRCOAINDEA</t>
@@ -5552,7 +5519,6 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5571,7 +5537,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5595,7 +5560,6 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5614,7 +5578,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>PWRCOAINDNE</t>
@@ -5638,7 +5601,6 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5657,7 +5619,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5681,7 +5642,6 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5700,7 +5660,6 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRCOAINDNO</t>
@@ -5724,7 +5683,6 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5743,7 +5701,6 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5767,7 +5724,6 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5786,7 +5742,6 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>PWRCOAINDSO</t>
@@ -5810,7 +5765,6 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5829,7 +5783,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5853,7 +5806,6 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5872,7 +5824,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>PWRCOAINDWE</t>
@@ -5896,7 +5847,6 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5915,7 +5865,6 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5939,7 +5888,6 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5958,7 +5906,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>PWRCOALKAXX</t>
@@ -5982,7 +5929,6 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6001,7 +5947,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -6025,7 +5970,6 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6044,7 +5988,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRCOGBGDXX</t>
@@ -6068,7 +6011,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6087,7 +6029,6 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6111,7 +6052,6 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6130,7 +6070,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>PWRCOGINDEA</t>
@@ -6154,7 +6093,6 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6173,7 +6111,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6197,7 +6134,6 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6216,7 +6152,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>PWRCOGINDNE</t>
@@ -6240,7 +6175,6 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6259,7 +6193,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6283,7 +6216,6 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6302,7 +6234,6 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>PWRCOGINDNO</t>
@@ -6326,7 +6257,6 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6345,7 +6275,6 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6369,7 +6298,6 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6388,7 +6316,6 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRCOGINDSO</t>
@@ -6412,7 +6339,6 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6431,7 +6357,6 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6455,7 +6380,6 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6474,7 +6398,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>PWRCOGINDWE</t>
@@ -6498,7 +6421,6 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6517,7 +6439,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6541,7 +6462,6 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6560,7 +6480,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>PWRCOGLKAXX</t>
@@ -6584,7 +6503,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6603,7 +6521,6 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>PWRCSPINDEA</t>
@@ -6627,7 +6544,6 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6646,7 +6562,6 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>PWRCSPINDNE</t>
@@ -6670,7 +6585,6 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6689,7 +6603,6 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>PWRCSPINDNO</t>
@@ -6713,7 +6626,6 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6732,7 +6644,6 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRCSPINDSO</t>
@@ -6756,7 +6667,6 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6775,7 +6685,6 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>PWRCSPINDWE</t>
@@ -6799,7 +6708,6 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6818,7 +6726,6 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>PWRHYDBGDXX</t>
@@ -6842,7 +6749,6 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6861,7 +6767,6 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>PWRHYDBTNXX</t>
@@ -6885,7 +6790,6 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6904,7 +6808,6 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>PWRHYDINDEA</t>
@@ -6928,7 +6831,6 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6947,7 +6849,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>PWRHYDINDNE</t>
@@ -6971,7 +6872,6 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6990,7 +6890,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>PWRHYDINDNO</t>
@@ -7014,7 +6913,6 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7033,7 +6931,6 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>PWRHYDINDSO</t>
@@ -7057,7 +6954,6 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7076,7 +6972,6 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRHYDINDWE</t>
@@ -7100,7 +6995,6 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7119,7 +7013,6 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>PWRHYDLKAXX</t>
@@ -7143,7 +7036,6 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7162,7 +7054,6 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>PWRHYDNPLXX</t>
@@ -7186,7 +7077,6 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7205,7 +7095,6 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7229,7 +7118,6 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7248,7 +7136,6 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>PWRNGSINDEA</t>
@@ -7272,7 +7159,6 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7291,7 +7177,6 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7315,7 +7200,6 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7334,7 +7218,6 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>PWRNGSINDNE</t>
@@ -7358,7 +7241,6 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7377,7 +7259,6 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7401,7 +7282,6 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7420,7 +7300,6 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRNGSINDNO</t>
@@ -7444,7 +7323,6 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7463,7 +7341,6 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7487,7 +7364,6 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7506,7 +7382,6 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>PWRNGSINDSO</t>
@@ -7530,7 +7405,6 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7549,7 +7423,6 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7573,7 +7446,6 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7592,7 +7464,6 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>PWRNGSINDWE</t>
@@ -7616,7 +7487,6 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7635,7 +7505,6 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7659,7 +7528,6 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7678,7 +7546,6 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>PWRNGSLKAXX</t>
@@ -7702,7 +7569,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7721,7 +7587,6 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7745,7 +7610,6 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7764,7 +7628,6 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWROILBGDXX</t>
@@ -7788,7 +7651,6 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7807,7 +7669,6 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7831,7 +7692,6 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7850,7 +7710,6 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>PWROILINDEA</t>
@@ -7874,7 +7733,6 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7893,7 +7751,6 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7917,7 +7774,6 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7936,7 +7792,6 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>PWROILINDNE</t>
@@ -7960,7 +7815,6 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7979,7 +7833,6 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -8003,7 +7856,6 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8022,7 +7874,6 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>PWROILINDNO</t>
@@ -8046,7 +7897,6 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8065,7 +7915,6 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -8089,7 +7938,6 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8108,7 +7956,6 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>PWROILINDSO</t>
@@ -8132,7 +7979,6 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8151,7 +7997,6 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8175,7 +8020,6 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8194,7 +8038,6 @@
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>PWROILINDWE</t>
@@ -8218,7 +8061,6 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8237,7 +8079,6 @@
       <c r="D88" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8261,7 +8102,6 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8280,7 +8120,6 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>PWROILLKAXX</t>
@@ -8304,7 +8143,6 @@
       <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8323,7 +8161,6 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8347,7 +8184,6 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8366,7 +8202,6 @@
       <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>PWROTHBGDXX</t>
@@ -8390,7 +8225,6 @@
       <c r="J91" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8409,7 +8243,6 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8433,7 +8266,6 @@
       <c r="J92" t="n">
         <v>1</v>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8452,7 +8284,6 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>PWROTHBTNXX</t>
@@ -8476,7 +8307,6 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8495,7 +8325,6 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8519,7 +8348,6 @@
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8538,7 +8366,6 @@
       <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>PWROTHINDEA</t>
@@ -8562,7 +8389,6 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8581,7 +8407,6 @@
       <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8605,7 +8430,6 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8624,7 +8448,6 @@
       <c r="D97" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>PWROTHINDNE</t>
@@ -8648,7 +8471,6 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8667,7 +8489,6 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8691,7 +8512,6 @@
       <c r="J98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8710,7 +8530,6 @@
       <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>PWROTHINDNO</t>
@@ -8734,7 +8553,6 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8753,7 +8571,6 @@
       <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8777,7 +8594,6 @@
       <c r="J100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8796,7 +8612,6 @@
       <c r="D101" t="n">
         <v>1</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>PWROTHINDSO</t>
@@ -8820,7 +8635,6 @@
       <c r="J101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8839,7 +8653,6 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8863,7 +8676,6 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8882,7 +8694,6 @@
       <c r="D103" t="n">
         <v>1</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>PWROTHINDWE</t>
@@ -8906,7 +8717,6 @@
       <c r="J103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8925,7 +8735,6 @@
       <c r="D104" t="n">
         <v>1</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8949,7 +8758,6 @@
       <c r="J104" t="n">
         <v>1</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8968,7 +8776,6 @@
       <c r="D105" t="n">
         <v>1</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>PWROTHLKAXX</t>
@@ -8992,7 +8799,6 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9011,7 +8817,6 @@
       <c r="D106" t="n">
         <v>1</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -9035,7 +8840,6 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9054,7 +8858,6 @@
       <c r="D107" t="n">
         <v>1</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>PWROTHMDVXX</t>
@@ -9078,7 +8881,6 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9097,7 +8899,6 @@
       <c r="D108" t="n">
         <v>1</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -9121,7 +8922,6 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9140,7 +8940,6 @@
       <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>PWROTHNPLXX</t>
@@ -9164,7 +8963,6 @@
       <c r="J109" t="n">
         <v>1</v>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9183,7 +8981,6 @@
       <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -9207,7 +9004,6 @@
       <c r="J110" t="n">
         <v>1</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -9226,7 +9022,6 @@
       <c r="D111" t="n">
         <v>1</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>PWRPETBGDXX</t>
@@ -9250,7 +9045,6 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9269,7 +9063,6 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9293,7 +9086,6 @@
       <c r="J112" t="n">
         <v>1</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9312,7 +9104,6 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>PWRPETBTNXX</t>
@@ -9336,7 +9127,6 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9355,7 +9145,6 @@
       <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9379,7 +9168,6 @@
       <c r="J114" t="n">
         <v>1</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9398,7 +9186,6 @@
       <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>PWRPETINDEA</t>
@@ -9422,7 +9209,6 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9441,7 +9227,6 @@
       <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9465,7 +9250,6 @@
       <c r="J116" t="n">
         <v>1</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9484,7 +9268,6 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>PWRPETINDNE</t>
@@ -9508,7 +9291,6 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9527,7 +9309,6 @@
       <c r="D118" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9551,7 +9332,6 @@
       <c r="J118" t="n">
         <v>1</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9570,7 +9350,6 @@
       <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>PWRPETINDNO</t>
@@ -9594,7 +9373,6 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9613,7 +9391,6 @@
       <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9637,7 +9414,6 @@
       <c r="J120" t="n">
         <v>1</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9656,7 +9432,6 @@
       <c r="D121" t="n">
         <v>1</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>PWRPETINDSO</t>
@@ -9680,7 +9455,6 @@
       <c r="J121" t="n">
         <v>1</v>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9699,7 +9473,6 @@
       <c r="D122" t="n">
         <v>1</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9723,7 +9496,6 @@
       <c r="J122" t="n">
         <v>1</v>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9742,7 +9514,6 @@
       <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>PWRPETINDWE</t>
@@ -9766,7 +9537,6 @@
       <c r="J123" t="n">
         <v>1</v>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9785,7 +9555,6 @@
       <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9809,7 +9578,6 @@
       <c r="J124" t="n">
         <v>1</v>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9828,7 +9596,6 @@
       <c r="D125" t="n">
         <v>1</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>PWRPETLKAXX</t>
@@ -9852,7 +9619,6 @@
       <c r="J125" t="n">
         <v>1</v>
       </c>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9871,7 +9637,6 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9895,7 +9660,6 @@
       <c r="J126" t="n">
         <v>1</v>
       </c>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9914,7 +9678,6 @@
       <c r="D127" t="n">
         <v>1</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PWRPETMDVXX</t>
@@ -9938,7 +9701,6 @@
       <c r="J127" t="n">
         <v>1</v>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9957,7 +9719,6 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -9981,7 +9742,6 @@
       <c r="J128" t="n">
         <v>1</v>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10000,7 +9760,6 @@
       <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>PWRPETNPLXX</t>
@@ -10024,7 +9783,6 @@
       <c r="J129" t="n">
         <v>1</v>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10043,7 +9801,6 @@
       <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>PWRSPVBGDXX</t>
@@ -10067,7 +9824,6 @@
       <c r="J130" t="n">
         <v>1</v>
       </c>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10086,7 +9842,6 @@
       <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>PWRSPVBTNXX</t>
@@ -10110,7 +9865,6 @@
       <c r="J131" t="n">
         <v>1</v>
       </c>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10129,7 +9883,6 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>PWRSPVINDEA</t>
@@ -10153,7 +9906,6 @@
       <c r="J132" t="n">
         <v>1</v>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10172,7 +9924,6 @@
       <c r="D133" t="n">
         <v>1</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>PWRSPVINDNE</t>
@@ -10196,7 +9947,6 @@
       <c r="J133" t="n">
         <v>1</v>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10215,7 +9965,6 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>PWRSPVINDNO</t>
@@ -10239,7 +9988,6 @@
       <c r="J134" t="n">
         <v>1</v>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10258,7 +10006,6 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>PWRSPVINDSO</t>
@@ -10282,7 +10029,6 @@
       <c r="J135" t="n">
         <v>1</v>
       </c>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10301,7 +10047,6 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>PWRSPVINDWE</t>
@@ -10325,7 +10070,6 @@
       <c r="J136" t="n">
         <v>1</v>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10344,7 +10088,6 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>PWRSPVLKAXX</t>
@@ -10368,7 +10111,6 @@
       <c r="J137" t="n">
         <v>1</v>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10387,7 +10129,6 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>PWRSPVMDVXX</t>
@@ -10411,7 +10152,6 @@
       <c r="J138" t="n">
         <v>1</v>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10430,7 +10170,6 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>PWRSPVNPLXX</t>
@@ -10454,7 +10193,6 @@
       <c r="J139" t="n">
         <v>1</v>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10473,7 +10211,6 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10497,7 +10234,6 @@
       <c r="J140" t="n">
         <v>1</v>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10516,7 +10252,6 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>PWRURNBGDXX</t>
@@ -10540,7 +10275,6 @@
       <c r="J141" t="n">
         <v>1</v>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10559,7 +10293,6 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10583,7 +10316,6 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10602,7 +10334,6 @@
       <c r="D143" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>PWRURNINDEA</t>
@@ -10626,7 +10357,6 @@
       <c r="J143" t="n">
         <v>1</v>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10645,7 +10375,6 @@
       <c r="D144" t="n">
         <v>1</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10669,7 +10398,6 @@
       <c r="J144" t="n">
         <v>1</v>
       </c>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10688,7 +10416,6 @@
       <c r="D145" t="n">
         <v>1</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>PWRURNINDNE</t>
@@ -10712,7 +10439,6 @@
       <c r="J145" t="n">
         <v>1</v>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10731,7 +10457,6 @@
       <c r="D146" t="n">
         <v>1</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10755,7 +10480,6 @@
       <c r="J146" t="n">
         <v>1</v>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10774,7 +10498,6 @@
       <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>PWRURNINDNO</t>
@@ -10798,7 +10521,6 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10817,7 +10539,6 @@
       <c r="D148" t="n">
         <v>1</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10841,7 +10562,6 @@
       <c r="J148" t="n">
         <v>1</v>
       </c>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10860,7 +10580,6 @@
       <c r="D149" t="n">
         <v>1</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>PWRURNINDSO</t>
@@ -10884,7 +10603,6 @@
       <c r="J149" t="n">
         <v>1</v>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10903,7 +10621,6 @@
       <c r="D150" t="n">
         <v>1</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10927,7 +10644,6 @@
       <c r="J150" t="n">
         <v>1</v>
       </c>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10946,7 +10662,6 @@
       <c r="D151" t="n">
         <v>1</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>PWRURNINDWE</t>
@@ -10970,7 +10685,6 @@
       <c r="J151" t="n">
         <v>1</v>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10989,7 +10703,6 @@
       <c r="D152" t="n">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>PWRWASBGDXX</t>
@@ -11013,7 +10726,6 @@
       <c r="J152" t="n">
         <v>1</v>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11032,7 +10744,6 @@
       <c r="D153" t="n">
         <v>1</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>PWRWASINDEA</t>
@@ -11056,7 +10767,6 @@
       <c r="J153" t="n">
         <v>1</v>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11075,7 +10785,6 @@
       <c r="D154" t="n">
         <v>1</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>PWRWASINDNE</t>
@@ -11099,7 +10808,6 @@
       <c r="J154" t="n">
         <v>1</v>
       </c>
-      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11118,7 +10826,6 @@
       <c r="D155" t="n">
         <v>1</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>PWRWASINDNO</t>
@@ -11142,7 +10849,6 @@
       <c r="J155" t="n">
         <v>1</v>
       </c>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11161,7 +10867,6 @@
       <c r="D156" t="n">
         <v>1</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>PWRWASINDSO</t>
@@ -11185,7 +10890,6 @@
       <c r="J156" t="n">
         <v>1</v>
       </c>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11204,7 +10908,6 @@
       <c r="D157" t="n">
         <v>1</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>PWRWASINDWE</t>
@@ -11228,7 +10931,6 @@
       <c r="J157" t="n">
         <v>1</v>
       </c>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -11247,7 +10949,6 @@
       <c r="D158" t="n">
         <v>1</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>PWRWASLKAXX</t>
@@ -11271,7 +10972,6 @@
       <c r="J158" t="n">
         <v>1</v>
       </c>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11290,7 +10990,6 @@
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>PWRWASNPLXX</t>
@@ -11314,7 +11013,6 @@
       <c r="J159" t="n">
         <v>1</v>
       </c>
-      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11333,7 +11031,6 @@
       <c r="D160" t="n">
         <v>1</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>PWRWOFBGDXX</t>
@@ -11357,7 +11054,6 @@
       <c r="J160" t="n">
         <v>1</v>
       </c>
-      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11376,7 +11072,6 @@
       <c r="D161" t="n">
         <v>1</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>PWRWOFINDEA</t>
@@ -11400,7 +11095,6 @@
       <c r="J161" t="n">
         <v>1</v>
       </c>
-      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11419,7 +11113,6 @@
       <c r="D162" t="n">
         <v>1</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>PWRWOFINDNE</t>
@@ -11443,7 +11136,6 @@
       <c r="J162" t="n">
         <v>1</v>
       </c>
-      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11462,7 +11154,6 @@
       <c r="D163" t="n">
         <v>1</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>PWRWOFINDNO</t>
@@ -11486,7 +11177,6 @@
       <c r="J163" t="n">
         <v>1</v>
       </c>
-      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11505,7 +11195,6 @@
       <c r="D164" t="n">
         <v>1</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>PWRWOFINDSO</t>
@@ -11529,7 +11218,6 @@
       <c r="J164" t="n">
         <v>1</v>
       </c>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11548,7 +11236,6 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>PWRWOFINDWE</t>
@@ -11572,7 +11259,6 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
-      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11591,7 +11277,6 @@
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>PWRWOFLKAXX</t>
@@ -11615,7 +11300,6 @@
       <c r="J166" t="n">
         <v>1</v>
       </c>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11634,7 +11318,6 @@
       <c r="D167" t="n">
         <v>1</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>PWRWONBGDXX</t>
@@ -11658,7 +11341,6 @@
       <c r="J167" t="n">
         <v>1</v>
       </c>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11677,7 +11359,6 @@
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>PWRWONBTNXX</t>
@@ -11701,7 +11382,6 @@
       <c r="J168" t="n">
         <v>1</v>
       </c>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11720,7 +11400,6 @@
       <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>PWRWONINDEA</t>
@@ -11744,7 +11423,6 @@
       <c r="J169" t="n">
         <v>1</v>
       </c>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11763,7 +11441,6 @@
       <c r="D170" t="n">
         <v>1</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>PWRWONINDNE</t>
@@ -11787,7 +11464,6 @@
       <c r="J170" t="n">
         <v>1</v>
       </c>
-      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11806,7 +11482,6 @@
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>PWRWONINDNO</t>
@@ -11830,7 +11505,6 @@
       <c r="J171" t="n">
         <v>1</v>
       </c>
-      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -11849,7 +11523,6 @@
       <c r="D172" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>PWRWONINDSO</t>
@@ -11873,7 +11546,6 @@
       <c r="J172" t="n">
         <v>1</v>
       </c>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -11892,7 +11564,6 @@
       <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>PWRWONINDWE</t>
@@ -11916,7 +11587,6 @@
       <c r="J173" t="n">
         <v>1</v>
       </c>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -11935,7 +11605,6 @@
       <c r="D174" t="n">
         <v>1</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>PWRWONLKAXX</t>
@@ -11959,7 +11628,6 @@
       <c r="J174" t="n">
         <v>1</v>
       </c>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -11978,7 +11646,6 @@
       <c r="D175" t="n">
         <v>1</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>PWRWONNPLXX</t>
@@ -12002,7 +11669,6 @@
       <c r="J175" t="n">
         <v>1</v>
       </c>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12021,7 +11687,6 @@
       <c r="D176" t="n">
         <v>1</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -12045,7 +11710,6 @@
       <c r="J176" t="n">
         <v>1</v>
       </c>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12064,7 +11728,6 @@
       <c r="D177" t="n">
         <v>1</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>TRNBGDXXINDEA</t>
@@ -12088,7 +11751,6 @@
       <c r="J177" t="n">
         <v>1</v>
       </c>
-      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12107,7 +11769,6 @@
       <c r="D178" t="n">
         <v>1</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -12131,7 +11792,6 @@
       <c r="J178" t="n">
         <v>1</v>
       </c>
-      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12150,7 +11810,6 @@
       <c r="D179" t="n">
         <v>1</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>TRNBGDXXINDNE</t>
@@ -12174,7 +11833,6 @@
       <c r="J179" t="n">
         <v>1</v>
       </c>
-      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12193,7 +11851,6 @@
       <c r="D180" t="n">
         <v>1</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -12217,7 +11874,6 @@
       <c r="J180" t="n">
         <v>1</v>
       </c>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12236,7 +11892,6 @@
       <c r="D181" t="n">
         <v>1</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>TRNBTNXXINDEA</t>
@@ -12260,7 +11915,6 @@
       <c r="J181" t="n">
         <v>1</v>
       </c>
-      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12279,7 +11933,6 @@
       <c r="D182" t="n">
         <v>1</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -12303,7 +11956,6 @@
       <c r="J182" t="n">
         <v>1</v>
       </c>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12322,7 +11974,6 @@
       <c r="D183" t="n">
         <v>1</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>TRNINDEAINDNE</t>
@@ -12346,7 +11997,6 @@
       <c r="J183" t="n">
         <v>1</v>
       </c>
-      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12365,7 +12015,6 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12389,7 +12038,6 @@
       <c r="J184" t="n">
         <v>1</v>
       </c>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12408,7 +12056,6 @@
       <c r="D185" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>TRNINDEAINDNO</t>
@@ -12432,7 +12079,6 @@
       <c r="J185" t="n">
         <v>1</v>
       </c>
-      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12451,7 +12097,6 @@
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12475,7 +12120,6 @@
       <c r="J186" t="n">
         <v>1</v>
       </c>
-      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12494,7 +12138,6 @@
       <c r="D187" t="n">
         <v>1</v>
       </c>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>TRNINDEAINDSO</t>
@@ -12518,7 +12161,6 @@
       <c r="J187" t="n">
         <v>1</v>
       </c>
-      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12537,7 +12179,6 @@
       <c r="D188" t="n">
         <v>1</v>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12561,7 +12202,6 @@
       <c r="J188" t="n">
         <v>1</v>
       </c>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -12580,7 +12220,6 @@
       <c r="D189" t="n">
         <v>1</v>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>TRNINDEAINDWE</t>
@@ -12604,7 +12243,6 @@
       <c r="J189" t="n">
         <v>1</v>
       </c>
-      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -12623,7 +12261,6 @@
       <c r="D190" t="n">
         <v>1</v>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12647,7 +12284,6 @@
       <c r="J190" t="n">
         <v>1</v>
       </c>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -12666,7 +12302,6 @@
       <c r="D191" t="n">
         <v>1</v>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>TRNINDEANPLXX</t>
@@ -12690,7 +12325,6 @@
       <c r="J191" t="n">
         <v>1</v>
       </c>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -12709,7 +12343,6 @@
       <c r="D192" t="n">
         <v>1</v>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12733,7 +12366,6 @@
       <c r="J192" t="n">
         <v>1</v>
       </c>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -12752,7 +12384,6 @@
       <c r="D193" t="n">
         <v>1</v>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>TRNINDNEINDNO</t>
@@ -12776,7 +12407,6 @@
       <c r="J193" t="n">
         <v>1</v>
       </c>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -12795,7 +12425,6 @@
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12819,7 +12448,6 @@
       <c r="J194" t="n">
         <v>1</v>
       </c>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -12838,7 +12466,6 @@
       <c r="D195" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>TRNINDNOINDWE</t>
@@ -12862,7 +12489,6 @@
       <c r="J195" t="n">
         <v>1</v>
       </c>
-      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -12881,7 +12507,6 @@
       <c r="D196" t="n">
         <v>1</v>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12905,7 +12530,6 @@
       <c r="J196" t="n">
         <v>1</v>
       </c>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -12924,7 +12548,6 @@
       <c r="D197" t="n">
         <v>1</v>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>TRNINDNONPLXX</t>
@@ -12948,7 +12571,6 @@
       <c r="J197" t="n">
         <v>1</v>
       </c>
-      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -12967,7 +12589,6 @@
       <c r="D198" t="n">
         <v>1</v>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -12991,7 +12612,6 @@
       <c r="J198" t="n">
         <v>1</v>
       </c>
-      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13010,7 +12630,6 @@
       <c r="D199" t="n">
         <v>1</v>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>TRNINDSOINDWE</t>
@@ -13034,7 +12653,6 @@
       <c r="J199" t="n">
         <v>1</v>
       </c>
-      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13053,7 +12671,6 @@
       <c r="D200" t="n">
         <v>1</v>
       </c>
-      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -13077,7 +12694,6 @@
       <c r="J200" t="n">
         <v>1</v>
       </c>
-      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13096,7 +12712,6 @@
       <c r="D201" t="n">
         <v>1</v>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>TRNINDSOLKAXX</t>
@@ -13120,7 +12735,6 @@
       <c r="J201" t="n">
         <v>1</v>
       </c>
-      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -13139,7 +12753,6 @@
       <c r="D202" t="n">
         <v>1</v>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>TRNLKAXXMDVXX</t>
@@ -13163,7 +12776,6 @@
       <c r="J202" t="n">
         <v>1</v>
       </c>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -13182,7 +12794,6 @@
       <c r="D203" t="n">
         <v>1</v>
       </c>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>TRNLKAXXMDVXX</t>
@@ -13206,16 +12817,11 @@
       <c r="J203" t="n">
         <v>1</v>
       </c>
-      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>1</v>
       </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>PWRBCKBGDXX</t>
@@ -13239,16 +12845,11 @@
       <c r="J204" t="n">
         <v>1</v>
       </c>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>1</v>
       </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>PWRBCKBTNXX</t>
@@ -13272,16 +12873,11 @@
       <c r="J205" t="n">
         <v>1</v>
       </c>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>1</v>
       </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>PWRBCKINDEA</t>
@@ -13305,16 +12901,11 @@
       <c r="J206" t="n">
         <v>1</v>
       </c>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>1</v>
       </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>PWRBCKINDNE</t>
@@ -13338,16 +12929,11 @@
       <c r="J207" t="n">
         <v>1</v>
       </c>
-      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>1</v>
       </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>PWRBCKINDNO</t>
@@ -13371,16 +12957,11 @@
       <c r="J208" t="n">
         <v>1</v>
       </c>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>1</v>
       </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>PWRBCKINDSO</t>
@@ -13404,16 +12985,11 @@
       <c r="J209" t="n">
         <v>1</v>
       </c>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>1</v>
       </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>PWRBCKINDWE</t>
@@ -13437,16 +13013,11 @@
       <c r="J210" t="n">
         <v>1</v>
       </c>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>1</v>
       </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>PWRBCKLKAXX</t>
@@ -13470,16 +13041,11 @@
       <c r="J211" t="n">
         <v>1</v>
       </c>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>1</v>
       </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>PWRBCKMDVXX</t>
@@ -13503,16 +13069,11 @@
       <c r="J212" t="n">
         <v>1</v>
       </c>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>1</v>
       </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>PWRBCKNPLXX</t>
@@ -13536,16 +13097,11 @@
       <c r="J213" t="n">
         <v>1</v>
       </c>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>2</v>
       </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>PWRLDSBGDXX</t>
@@ -13569,16 +13125,11 @@
       <c r="J214" t="n">
         <v>1</v>
       </c>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>2</v>
       </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>PWRLDSBTNXX</t>
@@ -13602,16 +13153,11 @@
       <c r="J215" t="n">
         <v>1</v>
       </c>
-      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>2</v>
       </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>PWRLDSINDEA</t>
@@ -13635,16 +13181,11 @@
       <c r="J216" t="n">
         <v>1</v>
       </c>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
         <v>2</v>
       </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>PWRLDSINDNE</t>
@@ -13668,16 +13209,11 @@
       <c r="J217" t="n">
         <v>1</v>
       </c>
-      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
         <v>2</v>
       </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>PWRLDSINDNO</t>
@@ -13701,16 +13237,11 @@
       <c r="J218" t="n">
         <v>1</v>
       </c>
-      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
         <v>2</v>
       </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>PWRLDSINDSO</t>
@@ -13734,16 +13265,11 @@
       <c r="J219" t="n">
         <v>1</v>
       </c>
-      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
         <v>2</v>
       </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>PWRLDSINDWE</t>
@@ -13767,16 +13293,11 @@
       <c r="J220" t="n">
         <v>1</v>
       </c>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
         <v>2</v>
       </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>PWRLDSLKAXX</t>
@@ -13800,16 +13321,11 @@
       <c r="J221" t="n">
         <v>1</v>
       </c>
-      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
         <v>2</v>
       </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>PWRLDSMDVXX</t>
@@ -13833,16 +13349,11 @@
       <c r="J222" t="n">
         <v>1</v>
       </c>
-      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
         <v>2</v>
       </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>PWRLDSNPLXX</t>
@@ -13866,16 +13377,11 @@
       <c r="J223" t="n">
         <v>1</v>
       </c>
-      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
         <v>2</v>
       </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>PWRSDSBGDXX</t>
@@ -13899,16 +13405,11 @@
       <c r="J224" t="n">
         <v>1</v>
       </c>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
         <v>2</v>
       </c>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>PWRSDSBTNXX</t>
@@ -13932,16 +13433,11 @@
       <c r="J225" t="n">
         <v>1</v>
       </c>
-      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
         <v>2</v>
       </c>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>PWRSDSINDEA</t>
@@ -13965,16 +13461,11 @@
       <c r="J226" t="n">
         <v>1</v>
       </c>
-      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
         <v>2</v>
       </c>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>PWRSDSINDNE</t>
@@ -13998,16 +13489,11 @@
       <c r="J227" t="n">
         <v>1</v>
       </c>
-      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
         <v>2</v>
       </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>PWRSDSINDNO</t>
@@ -14031,16 +13517,11 @@
       <c r="J228" t="n">
         <v>1</v>
       </c>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
         <v>2</v>
       </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>PWRSDSINDSO</t>
@@ -14064,16 +13545,11 @@
       <c r="J229" t="n">
         <v>1</v>
       </c>
-      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
         <v>2</v>
       </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>PWRSDSINDWE</t>
@@ -14097,16 +13573,11 @@
       <c r="J230" t="n">
         <v>1</v>
       </c>
-      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
         <v>2</v>
       </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>PWRSDSLKAXX</t>
@@ -14130,16 +13601,11 @@
       <c r="J231" t="n">
         <v>1</v>
       </c>
-      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
         <v>2</v>
       </c>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>PWRSDSMDVXX</t>
@@ -14163,16 +13629,11 @@
       <c r="J232" t="n">
         <v>1</v>
       </c>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
         <v>2</v>
       </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>PWRSDSNPLXX</t>
@@ -14196,7 +13657,6 @@
       <c r="J233" t="n">
         <v>1</v>
       </c>
-      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -14215,7 +13675,6 @@
       <c r="D234" t="n">
         <v>1</v>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>PWRLDSBGDXX</t>
@@ -14226,10 +13685,6 @@
           <t>Long duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -14248,7 +13703,6 @@
       <c r="D235" t="n">
         <v>1</v>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>PWRLDSBTNXX</t>
@@ -14259,10 +13713,6 @@
           <t>Long duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -14281,7 +13731,6 @@
       <c r="D236" t="n">
         <v>1</v>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>PWRLDSINDEA</t>
@@ -14292,10 +13741,6 @@
           <t>Long duration storage (Power generator) India, region EA</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -14314,7 +13759,6 @@
       <c r="D237" t="n">
         <v>1</v>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>PWRLDSINDNE</t>
@@ -14325,10 +13769,6 @@
           <t>Long duration storage (Power generator) India, region NE</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -14347,7 +13787,6 @@
       <c r="D238" t="n">
         <v>1</v>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>PWRLDSINDNO</t>
@@ -14358,10 +13797,6 @@
           <t>Long duration storage (Power generator) India, region NO</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -14380,7 +13815,6 @@
       <c r="D239" t="n">
         <v>1</v>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>PWRLDSINDSO</t>
@@ -14391,10 +13825,6 @@
           <t>Long duration storage (Power generator) India, region SO</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -14413,7 +13843,6 @@
       <c r="D240" t="n">
         <v>1</v>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>PWRLDSINDWE</t>
@@ -14424,10 +13853,6 @@
           <t>Long duration storage (Power generator) India, region WE</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -14446,7 +13871,6 @@
       <c r="D241" t="n">
         <v>1</v>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>PWRLDSLKAXX</t>
@@ -14457,10 +13881,6 @@
           <t>Long duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -14479,7 +13899,6 @@
       <c r="D242" t="n">
         <v>1</v>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>PWRLDSMDVXX</t>
@@ -14490,10 +13909,6 @@
           <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -14512,7 +13927,6 @@
       <c r="D243" t="n">
         <v>1</v>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>PWRLDSNPLXX</t>
@@ -14523,10 +13937,6 @@
           <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -14545,7 +13955,6 @@
       <c r="D244" t="n">
         <v>1</v>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>PWRSDSBGDXX</t>
@@ -14556,10 +13965,6 @@
           <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -14578,7 +13983,6 @@
       <c r="D245" t="n">
         <v>1</v>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>PWRSDSBTNXX</t>
@@ -14589,10 +13993,6 @@
           <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14611,7 +14011,6 @@
       <c r="D246" t="n">
         <v>1</v>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>PWRSDSINDEA</t>
@@ -14622,10 +14021,6 @@
           <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14644,7 +14039,6 @@
       <c r="D247" t="n">
         <v>1</v>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>PWRSDSINDNE</t>
@@ -14655,10 +14049,6 @@
           <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -14677,7 +14067,6 @@
       <c r="D248" t="n">
         <v>1</v>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>PWRSDSINDNO</t>
@@ -14688,10 +14077,6 @@
           <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -14710,7 +14095,6 @@
       <c r="D249" t="n">
         <v>1</v>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>PWRSDSINDSO</t>
@@ -14721,10 +14105,6 @@
           <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -14743,7 +14123,6 @@
       <c r="D250" t="n">
         <v>1</v>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>PWRSDSINDWE</t>
@@ -14754,10 +14133,6 @@
           <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -14776,7 +14151,6 @@
       <c r="D251" t="n">
         <v>1</v>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>PWRSDSLKAXX</t>
@@ -14787,10 +14161,6 @@
           <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -14809,7 +14179,6 @@
       <c r="D252" t="n">
         <v>1</v>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>PWRSDSMDVXX</t>
@@ -14820,10 +14189,6 @@
           <t>Short duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -14842,7 +14207,6 @@
       <c r="D253" t="n">
         <v>1</v>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>PWRSDSNPLXX</t>
@@ -14853,10 +14217,1038 @@
           <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>GEOINDNO</t>
+        </is>
+      </c>
+      <c r="C254" s="10" t="inlineStr">
+        <is>
+          <t>Geothermal, India, region NO</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="9" t="n"/>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>PWRGEOINDNO</t>
+        </is>
+      </c>
+      <c r="G254" s="9" t="inlineStr">
+        <is>
+          <t>Geothermal (Power generator) India, region NO</t>
+        </is>
+      </c>
+      <c r="H254" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDNO00</t>
+        </is>
+      </c>
+      <c r="I254" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J254" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" s="9" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B255" s="10" t="inlineStr">
+        <is>
+          <t>GASBGD</t>
+        </is>
+      </c>
+      <c r="C255" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas, Bangladesh</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" s="9" t="n"/>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>PWRNGSBGDXX</t>
+        </is>
+      </c>
+      <c r="G255" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas (Power generator) Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H255" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX01</t>
+        </is>
+      </c>
+      <c r="I255" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J255" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="9" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>GASINT</t>
+        </is>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>Natural Gas, International Markets</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="9" t="n"/>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>PWRNGSBGDXX</t>
+        </is>
+      </c>
+      <c r="G256" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas (Power generator) Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX01</t>
+        </is>
+      </c>
+      <c r="I256" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J256" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" s="9" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B257" s="10" t="inlineStr">
+        <is>
+          <t>GASMDV</t>
+        </is>
+      </c>
+      <c r="C257" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas, Maldives</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="9" t="n"/>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>PWRNGSMDVXX</t>
+        </is>
+      </c>
+      <c r="G257" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX01</t>
+        </is>
+      </c>
+      <c r="I257" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J257" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" s="9" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
+        <is>
+          <t>GASINT</t>
+        </is>
+      </c>
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>Natural Gas, International Markets</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" s="9" t="n"/>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>PWRNGSMDVXX</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>Natural Gas (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX01</t>
+        </is>
+      </c>
+      <c r="I258" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J258" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" s="9" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B259" s="10" t="inlineStr">
+        <is>
+          <t>OILMDV</t>
+        </is>
+      </c>
+      <c r="C259" s="10" t="inlineStr">
+        <is>
+          <t>Oil, Maldives</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>PWROILMDVXX</t>
+        </is>
+      </c>
+      <c r="G259" s="10" t="inlineStr">
+        <is>
+          <t>Oil (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H259" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX01</t>
+        </is>
+      </c>
+      <c r="I259" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J259" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" s="9" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>OILINT</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>Oil, International Markets</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="9" t="n"/>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>PWROILMDVXX</t>
+        </is>
+      </c>
+      <c r="G260" s="10" t="inlineStr">
+        <is>
+          <t>Oil (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX01</t>
+        </is>
+      </c>
+      <c r="I260" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J260" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" s="9" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B261" s="10" t="inlineStr">
+        <is>
+          <t>OILNPL</t>
+        </is>
+      </c>
+      <c r="C261" s="10" t="inlineStr">
+        <is>
+          <t>Oil, Nepal</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>PWROILNPLXX</t>
+        </is>
+      </c>
+      <c r="G261" s="10" t="inlineStr">
+        <is>
+          <t>Oil (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="inlineStr">
+        <is>
+          <t>ELCNPLXX01</t>
+        </is>
+      </c>
+      <c r="I261" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J261" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" s="9" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>OILINT</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="inlineStr">
+        <is>
+          <t>Oil, International Markets</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>PWROILNPLXX</t>
+        </is>
+      </c>
+      <c r="G262" s="10" t="inlineStr">
+        <is>
+          <t>Oil (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>ELCNPLXX01</t>
+        </is>
+      </c>
+      <c r="I262" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, region XX, NO renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J262" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" s="9" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>HYDINDEA</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric, India, region EA</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="9" t="n"/>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>PWRSHPINDEA</t>
+        </is>
+      </c>
+      <c r="G263" s="10" t="inlineStr">
+        <is>
+          <t>Small Hydropower (Power generator) India, region EA</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDEA00</t>
+        </is>
+      </c>
+      <c r="I263" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region EA, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J263" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" s="9" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>HYDINDNE</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric, India, region NE</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>PWRSHPINDNE</t>
+        </is>
+      </c>
+      <c r="G264" s="10" t="inlineStr">
+        <is>
+          <t>Small Hydropower (Power generator) India, region NE</t>
+        </is>
+      </c>
+      <c r="H264" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDNE00</t>
+        </is>
+      </c>
+      <c r="I264" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J264" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K264" s="9" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
+        <is>
+          <t>HYDINDNO</t>
+        </is>
+      </c>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric, India, region NO</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" s="9" t="n"/>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>PWRSHPINDNO</t>
+        </is>
+      </c>
+      <c r="G265" s="10" t="inlineStr">
+        <is>
+          <t>Small Hydropower (Power generator) India, region NO</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDNO00</t>
+        </is>
+      </c>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region NO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J265" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" s="9" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B266" s="9" t="inlineStr">
+        <is>
+          <t>HYDINDSO</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric, India, region SO</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" s="9" t="n"/>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>PWRSHPINDSO</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>Small Hydropower (Power generator) India, region SO</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDSO00</t>
+        </is>
+      </c>
+      <c r="I266" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region SO, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J266" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" s="9" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>HYDINDWE</t>
+        </is>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric, India, region WE</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" s="9" t="n"/>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>PWRSHPINDWE</t>
+        </is>
+      </c>
+      <c r="G267" s="10" t="inlineStr">
+        <is>
+          <t>Small Hydropower (Power generator) India, region WE</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDWE00</t>
+        </is>
+      </c>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, Region WE, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J267" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" s="9" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
+        <is>
+          <t>WOFMDVXX</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="inlineStr">
+        <is>
+          <t>Offshore Wind, Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="9" t="n"/>
+      <c r="F268" s="9" t="inlineStr">
+        <is>
+          <t>PWRWOFMDVXX</t>
+        </is>
+      </c>
+      <c r="G268" s="10" t="inlineStr">
+        <is>
+          <t>Offshore Wind (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H268" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="I268" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J268" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" s="9" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>WONMDVXX</t>
+        </is>
+      </c>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>Onshore Wind, Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="9" t="n"/>
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>PWRWONMDVXX</t>
+        </is>
+      </c>
+      <c r="G269" s="10" t="inlineStr">
+        <is>
+          <t>Onshore Wind (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="H269" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX00</t>
+        </is>
+      </c>
+      <c r="I269" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, renewable power plant output</t>
+        </is>
+      </c>
+      <c r="J269" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="9" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" s="9" t="inlineStr">
+        <is>
+          <t>ELCBTNXX03</t>
+        </is>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="9" t="n"/>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>TRNBTNXXBGDXX</t>
+        </is>
+      </c>
+      <c r="G270" s="10" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Bhutan, region XX to Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX04</t>
+        </is>
+      </c>
+      <c r="I270" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J270" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" s="9" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX03</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="9" t="n"/>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>TRNBTNXXBGDXX</t>
+        </is>
+      </c>
+      <c r="G271" s="10" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Bhutan, region XX to Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>ELCBTNXX04</t>
+        </is>
+      </c>
+      <c r="I271" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J271" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" s="9" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>ELCBTNXX03</t>
+        </is>
+      </c>
+      <c r="C272" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="9" t="n"/>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>TRNBTNXXINDNE</t>
+        </is>
+      </c>
+      <c r="G272" s="10" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Bhutan, region XX to India, region NE</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDNE04</t>
+        </is>
+      </c>
+      <c r="I272" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, region NE, power plant output</t>
+        </is>
+      </c>
+      <c r="J272" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" s="9" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B273" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDNE03</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, region NE, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="9" t="n"/>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>TRNBTNXXINDNE</t>
+        </is>
+      </c>
+      <c r="G273" s="10" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Bhutan, region XX to India, region NE</t>
+        </is>
+      </c>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>ELCBTNXX04</t>
+        </is>
+      </c>
+      <c r="I273" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bhutan, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J273" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="9" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B274" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX03</t>
+        </is>
+      </c>
+      <c r="C274" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="9" t="n"/>
+      <c r="F274" s="9" t="inlineStr">
+        <is>
+          <t>TRNMDVXXINDSO</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Maldives, region XX to India, region SO</t>
+        </is>
+      </c>
+      <c r="H274" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDSO04</t>
+        </is>
+      </c>
+      <c r="I274" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, region SO, power plant output</t>
+        </is>
+      </c>
+      <c r="J274" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" s="9" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
+        <is>
+          <t>ELCINDSO03</t>
+        </is>
+      </c>
+      <c r="C275" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, India, region SO, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" s="9" t="n"/>
+      <c r="F275" s="9" t="inlineStr">
+        <is>
+          <t>TRNMDVXXINDSO</t>
+        </is>
+      </c>
+      <c r="G275" s="9" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Maldives, region XX to India, region SO</t>
+        </is>
+      </c>
+      <c r="H275" s="9" t="inlineStr">
+        <is>
+          <t>ELCMDVXX04</t>
+        </is>
+      </c>
+      <c r="I275" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Maldives, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J275" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K275" s="9" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
+        <is>
+          <t>ELCNPLXX03</t>
+        </is>
+      </c>
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" s="9" t="n"/>
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>TRNNPLXXBGDXX</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Nepal, region XX to Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H276" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX04</t>
+        </is>
+      </c>
+      <c r="I276" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J276" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K276" s="9" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
+        <is>
+          <t>ELCBGDXX03</t>
+        </is>
+      </c>
+      <c r="C277" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Bangladesh, region XX, dispatch-ready for interconnection</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" s="9" t="n"/>
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>TRNNPLXXBGDXX</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr">
+        <is>
+          <t>Transmission interconnection from Nepal, region XX to Bangladesh, region XX</t>
+        </is>
+      </c>
+      <c r="H277" s="9" t="inlineStr">
+        <is>
+          <t>ELCNPLXX04</t>
+        </is>
+      </c>
+      <c r="I277" s="9" t="inlineStr">
+        <is>
+          <t>Electricity, Nepal, region XX, power plant output</t>
+        </is>
+      </c>
+      <c r="J277" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14957,7 +15349,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>RNWTRNBGDXX</t>
@@ -14981,7 +15372,6 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15000,7 +15390,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>RNWRPOBGDXX</t>
@@ -15024,7 +15413,6 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15043,7 +15431,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>RNWNLIBGDXX</t>
@@ -15067,7 +15454,6 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15086,7 +15472,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>PWRTRNBGDXX</t>
@@ -15110,7 +15495,6 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15129,7 +15513,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TRNRPOBGDXX</t>
@@ -15153,7 +15536,6 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15172,7 +15554,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TRNNLIBGDXX</t>
@@ -15196,7 +15577,6 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15215,7 +15595,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>DSPTRNBGDXX</t>
@@ -15239,7 +15618,6 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -15258,7 +15636,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>DSPTRNBGDXX</t>
@@ -15282,7 +15659,6 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -15301,7 +15677,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>RNWTRNBTNXX</t>
@@ -15325,7 +15700,6 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15344,7 +15718,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>RNWRPOBTNXX</t>
@@ -15368,7 +15741,6 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15387,7 +15759,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>RNWNLIBTNXX</t>
@@ -15411,7 +15782,6 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15430,7 +15800,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PWRTRNBTNXX</t>
@@ -15454,7 +15823,6 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15473,7 +15841,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TRNRPOBTNXX</t>
@@ -15497,7 +15864,6 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15516,7 +15882,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TRNNLIBTNXX</t>
@@ -15540,7 +15905,6 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15559,7 +15923,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>DSPTRNBTNXX</t>
@@ -15583,7 +15946,6 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15602,7 +15964,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>DSPTRNBTNXX</t>
@@ -15626,7 +15987,6 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15645,7 +16005,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>RNWTRNINDEA</t>
@@ -15669,7 +16028,6 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15688,7 +16046,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>RNWRPOINDEA</t>
@@ -15712,7 +16069,6 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15731,7 +16087,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>RNWNLIINDEA</t>
@@ -15755,7 +16110,6 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15774,7 +16128,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PWRTRNINDEA</t>
@@ -15798,7 +16151,6 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15817,7 +16169,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>TRNRPOINDEA</t>
@@ -15841,7 +16192,6 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15860,7 +16210,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>TRNNLIINDEA</t>
@@ -15884,7 +16233,6 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15903,7 +16251,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>DSPTRNINDEA</t>
@@ -15927,7 +16274,6 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -15946,7 +16292,6 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>DSPTRNINDEA</t>
@@ -15970,7 +16315,6 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -15989,7 +16333,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>RNWTRNINDNE</t>
@@ -16013,7 +16356,6 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -16032,7 +16374,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>RNWRPOINDNE</t>
@@ -16056,7 +16397,6 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -16075,7 +16415,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>RNWNLIINDNE</t>
@@ -16099,7 +16438,6 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -16118,7 +16456,6 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>PWRTRNINDNE</t>
@@ -16142,7 +16479,6 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16161,7 +16497,6 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TRNRPOINDNE</t>
@@ -16185,7 +16520,6 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16204,7 +16538,6 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TRNNLIINDNE</t>
@@ -16228,7 +16561,6 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16247,7 +16579,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>DSPTRNINDNE</t>
@@ -16271,7 +16602,6 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16290,7 +16620,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>DSPTRNINDNE</t>
@@ -16314,7 +16643,6 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -16333,7 +16661,6 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>RNWTRNINDNO</t>
@@ -16357,7 +16684,6 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -16376,7 +16702,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>RNWRPOINDNO</t>
@@ -16400,7 +16725,6 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -16419,7 +16743,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>RNWNLIINDNO</t>
@@ -16443,7 +16766,6 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -16462,7 +16784,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>PWRTRNINDNO</t>
@@ -16486,7 +16807,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -16505,7 +16825,6 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>TRNRPOINDNO</t>
@@ -16529,7 +16848,6 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -16548,7 +16866,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>TRNNLIINDNO</t>
@@ -16572,7 +16889,6 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -16591,7 +16907,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>DSPTRNINDNO</t>
@@ -16615,7 +16930,6 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -16634,7 +16948,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>DSPTRNINDNO</t>
@@ -16658,7 +16971,6 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -16677,7 +16989,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>RNWTRNINDSO</t>
@@ -16701,7 +17012,6 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -16720,7 +17030,6 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>RNWRPOINDSO</t>
@@ -16744,7 +17053,6 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -16763,7 +17071,6 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>RNWNLIINDSO</t>
@@ -16787,7 +17094,6 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -16806,7 +17112,6 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>PWRTRNINDSO</t>
@@ -16830,7 +17135,6 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -16849,7 +17153,6 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>TRNRPOINDSO</t>
@@ -16873,7 +17176,6 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -16892,7 +17194,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>TRNNLIINDSO</t>
@@ -16916,7 +17217,6 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -16935,7 +17235,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>DSPTRNINDSO</t>
@@ -16959,7 +17258,6 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -16978,7 +17276,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>DSPTRNINDSO</t>
@@ -17002,7 +17299,6 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -17021,7 +17317,6 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>RNWTRNINDWE</t>
@@ -17045,7 +17340,6 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -17064,7 +17358,6 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>RNWRPOINDWE</t>
@@ -17088,7 +17381,6 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -17107,7 +17399,6 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>RNWNLIINDWE</t>
@@ -17131,7 +17422,6 @@
       <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -17150,7 +17440,6 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>PWRTRNINDWE</t>
@@ -17174,7 +17463,6 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -17193,7 +17481,6 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>TRNRPOINDWE</t>
@@ -17217,7 +17504,6 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -17236,7 +17522,6 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>TRNNLIINDWE</t>
@@ -17260,7 +17545,6 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -17279,7 +17563,6 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>DSPTRNINDWE</t>
@@ -17303,7 +17586,6 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -17322,7 +17604,6 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>DSPTRNINDWE</t>
@@ -17346,7 +17627,6 @@
       <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -17365,7 +17645,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>RNWTRNNPLXX</t>
@@ -17389,7 +17668,6 @@
       <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -17408,7 +17686,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>RNWRPONPLXX</t>
@@ -17432,7 +17709,6 @@
       <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -17451,7 +17727,6 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>RNWNLINPLXX</t>
@@ -17475,7 +17750,6 @@
       <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -17494,7 +17768,6 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>PWRTRNNPLXX</t>
@@ -17518,7 +17791,6 @@
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -17537,7 +17809,6 @@
       <c r="D62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>TRNRPONPLXX</t>
@@ -17561,7 +17832,6 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -17580,7 +17850,6 @@
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>TRNNLINPLXX</t>
@@ -17604,7 +17873,6 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -17623,7 +17891,6 @@
       <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>DSPTRNNPLXX</t>
@@ -17647,7 +17914,6 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -17666,7 +17932,6 @@
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>DSPTRNNPLXX</t>
@@ -17690,7 +17955,6 @@
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -17709,7 +17973,6 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>RNWTRNLKAXX</t>
@@ -17733,7 +17996,6 @@
       <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -17752,7 +18014,6 @@
       <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>RNWRPOLKAXX</t>
@@ -17776,7 +18037,6 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -17795,7 +18055,6 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>RNWNLILKAXX</t>
@@ -17819,7 +18078,6 @@
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -17838,7 +18096,6 @@
       <c r="D69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>PWRTRNLKAXX</t>
@@ -17862,7 +18119,6 @@
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -17881,7 +18137,6 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>TRNRPOLKAXX</t>
@@ -17905,7 +18160,6 @@
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -17924,7 +18178,6 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>TRNNLILKAXX</t>
@@ -17948,7 +18201,6 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -17967,7 +18219,6 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>DSPTRNLKAXX</t>
@@ -17991,7 +18242,6 @@
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -18010,7 +18260,6 @@
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>DSPTRNLKAXX</t>
@@ -18034,7 +18283,6 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -18053,7 +18301,6 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>RNWTRNMDVXX</t>
@@ -18077,7 +18324,6 @@
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -18096,7 +18342,6 @@
       <c r="D75" t="n">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>RNWRPOMDVXX</t>
@@ -18120,7 +18365,6 @@
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -18139,7 +18383,6 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>RNWNLIMDVXX</t>
@@ -18163,7 +18406,6 @@
       <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -18182,7 +18424,6 @@
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>PWRTRNMDVXX</t>
@@ -18206,7 +18447,6 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -18225,7 +18465,6 @@
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>TRNRPOMDVXX</t>
@@ -18249,7 +18488,6 @@
       <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -18268,7 +18506,6 @@
       <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>TRNNLIMDVXX</t>
@@ -18292,7 +18529,6 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -18311,7 +18547,6 @@
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>DSPTRNMDVXX</t>
@@ -18335,7 +18570,6 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -18354,7 +18588,6 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>DSPTRNMDVXX</t>
@@ -18378,7 +18611,6 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Techs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribution Transport" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport Groups" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Primary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Secondary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Demand Techs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Distribution Transport" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transport" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Transport Groups" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_BAU/A-O_AR_Model_Base_Year.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Primary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Secondary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Demand Techs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Distribution Transport" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transport" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Transport Groups" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Techs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribution Transport" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport Groups" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
